--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.27</v>
+        <v>4.56</v>
       </c>
       <c r="F14" t="n">
-        <v>16.66</v>
+        <v>15.52</v>
       </c>
       <c r="G14" t="n">
-        <v>165.8</v>
+        <v>162</v>
       </c>
       <c r="H14" t="n">
-        <v>69.2</v>
+        <v>61.8</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-274.51</v>
+        <v>-196.38</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.63</v>
+        <v>-28.26</v>
       </c>
       <c r="L14" t="n">
-        <v>275.71</v>
+        <v>198.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:21</t>
+          <t>04:44:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.61</v>
+        <v>5.11</v>
       </c>
       <c r="F15" t="n">
-        <v>17.18</v>
+        <v>15.82</v>
       </c>
       <c r="G15" t="n">
-        <v>158.7</v>
+        <v>159.8</v>
       </c>
       <c r="H15" t="n">
-        <v>65.8</v>
+        <v>73.3</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-54.68</v>
+        <v>268.48</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.75</v>
+        <v>210.05</v>
       </c>
       <c r="L15" t="n">
-        <v>57.49</v>
+        <v>340.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:48:22</t>
+          <t>04:46:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.03</v>
+        <v>5.63</v>
       </c>
       <c r="F16" t="n">
-        <v>16.71</v>
+        <v>16.22</v>
       </c>
       <c r="G16" t="n">
-        <v>139.5</v>
+        <v>159.5</v>
       </c>
       <c r="H16" t="n">
-        <v>68.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>149.86</v>
+        <v>-114.65</v>
       </c>
       <c r="K16" t="n">
-        <v>130.32</v>
+        <v>51.29</v>
       </c>
       <c r="L16" t="n">
-        <v>198.6</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:54:33</t>
+          <t>04:52:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.95</v>
+        <v>4.35</v>
       </c>
       <c r="F17" t="n">
-        <v>16.38</v>
+        <v>16.23</v>
       </c>
       <c r="G17" t="n">
-        <v>154.1</v>
+        <v>155.1</v>
       </c>
       <c r="H17" t="n">
-        <v>75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>98.19</v>
+        <v>-79.95999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-62.38</v>
+        <v>-297.04</v>
       </c>
       <c r="L17" t="n">
-        <v>116.32</v>
+        <v>307.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:55:34</t>
+          <t>04:53:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.94</v>
+        <v>5.09</v>
       </c>
       <c r="F18" t="n">
-        <v>16.39</v>
+        <v>16.32</v>
       </c>
       <c r="G18" t="n">
-        <v>138.3</v>
+        <v>169.5</v>
       </c>
       <c r="H18" t="n">
-        <v>70.2</v>
+        <v>71.2</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-273.27</v>
+        <v>409.67</v>
       </c>
       <c r="K18" t="n">
-        <v>-220.8</v>
+        <v>-188.39</v>
       </c>
       <c r="L18" t="n">
-        <v>351.33</v>
+        <v>450.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:56:43</t>
+          <t>04:56:06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>6.05</v>
+        <v>5.34</v>
       </c>
       <c r="F19" t="n">
-        <v>16.02</v>
+        <v>15.67</v>
       </c>
       <c r="G19" t="n">
-        <v>156.7</v>
+        <v>157.3</v>
       </c>
       <c r="H19" t="n">
-        <v>65.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>332.54</v>
+        <v>167.04</v>
       </c>
       <c r="K19" t="n">
-        <v>53.33</v>
+        <v>-2.16</v>
       </c>
       <c r="L19" t="n">
-        <v>336.79</v>
+        <v>167.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:37</t>
+          <t>05:00:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.06</v>
+        <v>6.23</v>
       </c>
       <c r="F20" t="n">
-        <v>15.61</v>
+        <v>16.36</v>
       </c>
       <c r="G20" t="n">
-        <v>168.4</v>
+        <v>152.4</v>
       </c>
       <c r="H20" t="n">
-        <v>63.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-263.86</v>
+        <v>-728.83</v>
       </c>
       <c r="K20" t="n">
-        <v>-313</v>
+        <v>-504.32</v>
       </c>
       <c r="L20" t="n">
-        <v>409.38</v>
+        <v>886.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:19</t>
+          <t>05:02:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.94</v>
+        <v>6.11</v>
       </c>
       <c r="F21" t="n">
-        <v>16.15</v>
+        <v>16.08</v>
       </c>
       <c r="G21" t="n">
-        <v>153.1</v>
+        <v>155</v>
       </c>
       <c r="H21" t="n">
-        <v>66.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-602.86</v>
+        <v>560.89</v>
       </c>
       <c r="K21" t="n">
-        <v>146.97</v>
+        <v>653.2</v>
       </c>
       <c r="L21" t="n">
-        <v>620.52</v>
+        <v>860.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:03:22</t>
+          <t>05:05:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.36</v>
+        <v>5.15</v>
       </c>
       <c r="F22" t="n">
-        <v>15.7</v>
+        <v>16.24</v>
       </c>
       <c r="G22" t="n">
-        <v>142.5</v>
+        <v>166.4</v>
       </c>
       <c r="H22" t="n">
-        <v>74.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>159.02</v>
+        <v>-287.46</v>
       </c>
       <c r="K22" t="n">
-        <v>82.90000000000001</v>
+        <v>-400.51</v>
       </c>
       <c r="L22" t="n">
-        <v>179.33</v>
+        <v>492.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:08:25</t>
+          <t>05:09:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.36</v>
+        <v>6.9</v>
       </c>
       <c r="F23" t="n">
-        <v>16.01</v>
+        <v>17.03</v>
       </c>
       <c r="G23" t="n">
-        <v>153.4</v>
+        <v>151.6</v>
       </c>
       <c r="H23" t="n">
-        <v>68.5</v>
+        <v>67.5</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-251.84</v>
+        <v>212.14</v>
       </c>
       <c r="K23" t="n">
-        <v>194</v>
+        <v>-485.97</v>
       </c>
       <c r="L23" t="n">
-        <v>317.9</v>
+        <v>530.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:10:49</t>
+          <t>05:12:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.37</v>
+        <v>4.95</v>
       </c>
       <c r="F24" t="n">
-        <v>15.57</v>
+        <v>16.44</v>
       </c>
       <c r="G24" t="n">
-        <v>165.5</v>
+        <v>149.8</v>
       </c>
       <c r="H24" t="n">
-        <v>74.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-654.0599999999999</v>
+        <v>-90.09</v>
       </c>
       <c r="K24" t="n">
-        <v>-292.24</v>
+        <v>-419.06</v>
       </c>
       <c r="L24" t="n">
-        <v>716.37</v>
+        <v>428.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:13:18</t>
+          <t>05:13:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.67</v>
+        <v>6.09</v>
       </c>
       <c r="F25" t="n">
         <v>16.65</v>
       </c>
       <c r="G25" t="n">
-        <v>149.7</v>
+        <v>141.7</v>
       </c>
       <c r="H25" t="n">
-        <v>68.90000000000001</v>
+        <v>64</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-186.12</v>
+        <v>568.36</v>
       </c>
       <c r="K25" t="n">
-        <v>15.24</v>
+        <v>-142.22</v>
       </c>
       <c r="L25" t="n">
-        <v>186.74</v>
+        <v>585.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:18:00</t>
+          <t>05:19:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.61</v>
+        <v>5.8</v>
       </c>
       <c r="F26" t="n">
-        <v>16.08</v>
+        <v>15.81</v>
       </c>
       <c r="G26" t="n">
-        <v>153.7</v>
+        <v>153.9</v>
       </c>
       <c r="H26" t="n">
-        <v>67.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>-494.62</v>
+        <v>422.67</v>
       </c>
       <c r="K26" t="n">
-        <v>-493.64</v>
+        <v>-398.57</v>
       </c>
       <c r="L26" t="n">
-        <v>698.8</v>
+        <v>580.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:20:26</t>
+          <t>05:21:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.27</v>
+        <v>5.24</v>
       </c>
       <c r="F27" t="n">
-        <v>15.5</v>
+        <v>15.77</v>
       </c>
       <c r="G27" t="n">
-        <v>150.8</v>
+        <v>148</v>
       </c>
       <c r="H27" t="n">
-        <v>68.8</v>
+        <v>63.9</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>56.65</v>
+        <v>239.68</v>
       </c>
       <c r="K27" t="n">
-        <v>-370.94</v>
+        <v>-685.65</v>
       </c>
       <c r="L27" t="n">
-        <v>375.24</v>
+        <v>726.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:22:28</t>
+          <t>05:23:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.51</v>
+        <v>5.87</v>
       </c>
       <c r="F28" t="n">
-        <v>16.82</v>
+        <v>15.83</v>
       </c>
       <c r="G28" t="n">
-        <v>156.3</v>
+        <v>165.8</v>
       </c>
       <c r="H28" t="n">
-        <v>70.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>213.07</v>
+        <v>384.57</v>
       </c>
       <c r="K28" t="n">
-        <v>-1103.84</v>
+        <v>-187.47</v>
       </c>
       <c r="L28" t="n">
-        <v>1124.22</v>
+        <v>427.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:35:40</t>
+          <t>05:35:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>7.01</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>15.42</v>
+        <v>16.87</v>
       </c>
       <c r="G29" t="n">
-        <v>147</v>
+        <v>151.4</v>
       </c>
       <c r="H29" t="n">
-        <v>66.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>164.67</v>
+        <v>207.21</v>
       </c>
       <c r="K29" t="n">
-        <v>6.95</v>
+        <v>-122.97</v>
       </c>
       <c r="L29" t="n">
-        <v>164.82</v>
+        <v>240.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:37:00</t>
+          <t>05:36:42</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.66</v>
+        <v>5.56</v>
       </c>
       <c r="F30" t="n">
-        <v>15.85</v>
+        <v>16.28</v>
       </c>
       <c r="G30" t="n">
-        <v>160.8</v>
+        <v>153.3</v>
       </c>
       <c r="H30" t="n">
-        <v>75.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>129.12</v>
+        <v>-281.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-70.72</v>
+        <v>-445.24</v>
       </c>
       <c r="L30" t="n">
-        <v>147.22</v>
+        <v>526.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:38:22</t>
+          <t>05:38:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.14</v>
+        <v>4.96</v>
       </c>
       <c r="F31" t="n">
-        <v>16.67</v>
+        <v>16.81</v>
       </c>
       <c r="G31" t="n">
-        <v>155.6</v>
+        <v>147.1</v>
       </c>
       <c r="H31" t="n">
-        <v>76.3</v>
+        <v>65.7</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.87</v>
+        <v>-66.83</v>
       </c>
       <c r="K31" t="n">
-        <v>42.71</v>
+        <v>271.27</v>
       </c>
       <c r="L31" t="n">
-        <v>43.43</v>
+        <v>279.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:44:25</t>
+          <t>05:44:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.92</v>
+        <v>6.18</v>
       </c>
       <c r="F32" t="n">
-        <v>15.94</v>
+        <v>16.65</v>
       </c>
       <c r="G32" t="n">
-        <v>158.9</v>
+        <v>146.7</v>
       </c>
       <c r="H32" t="n">
-        <v>62.3</v>
+        <v>62.6</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-34.51</v>
+        <v>-217.7</v>
       </c>
       <c r="K32" t="n">
-        <v>341.07</v>
+        <v>-120.72</v>
       </c>
       <c r="L32" t="n">
-        <v>342.82</v>
+        <v>248.93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:45:41</t>
+          <t>05:45:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.95</v>
+        <v>6.09</v>
       </c>
       <c r="F33" t="n">
-        <v>15.95</v>
+        <v>16.74</v>
       </c>
       <c r="G33" t="n">
-        <v>167.9</v>
+        <v>154.6</v>
       </c>
       <c r="H33" t="n">
-        <v>70.2</v>
+        <v>66.7</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-222.79</v>
+        <v>66.78</v>
       </c>
       <c r="K33" t="n">
-        <v>258.45</v>
+        <v>-176.15</v>
       </c>
       <c r="L33" t="n">
-        <v>341.22</v>
+        <v>188.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:47:06</t>
+          <t>05:47:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>6.11</v>
+        <v>6.09</v>
       </c>
       <c r="F34" t="n">
-        <v>16.06</v>
+        <v>16.66</v>
       </c>
       <c r="G34" t="n">
-        <v>157.8</v>
+        <v>154.9</v>
       </c>
       <c r="H34" t="n">
-        <v>71.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>48.22</v>
+        <v>-141.66</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.56</v>
+        <v>36.38</v>
       </c>
       <c r="L34" t="n">
-        <v>49.16</v>
+        <v>146.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:51:45</t>
+          <t>05:53:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.24</v>
+        <v>5.75</v>
       </c>
       <c r="F35" t="n">
-        <v>16.59</v>
+        <v>15.89</v>
       </c>
       <c r="G35" t="n">
-        <v>149.8</v>
+        <v>152.9</v>
       </c>
       <c r="H35" t="n">
-        <v>67.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-31.17</v>
+        <v>-319.04</v>
       </c>
       <c r="K35" t="n">
-        <v>-59.47</v>
+        <v>255.05</v>
       </c>
       <c r="L35" t="n">
-        <v>67.14</v>
+        <v>408.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:52:51</t>
+          <t>05:55:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.52</v>
+        <v>5.06</v>
       </c>
       <c r="F36" t="n">
-        <v>16.56</v>
+        <v>16.75</v>
       </c>
       <c r="G36" t="n">
-        <v>154.4</v>
+        <v>151.2</v>
       </c>
       <c r="H36" t="n">
-        <v>72</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-98.34</v>
+        <v>-184.48</v>
       </c>
       <c r="K36" t="n">
-        <v>-283.66</v>
+        <v>-264.67</v>
       </c>
       <c r="L36" t="n">
-        <v>300.22</v>
+        <v>322.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:54:43</t>
+          <t>05:56:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.66</v>
+        <v>5.74</v>
       </c>
       <c r="F37" t="n">
-        <v>16.35</v>
+        <v>16.25</v>
       </c>
       <c r="G37" t="n">
-        <v>170.3</v>
+        <v>155</v>
       </c>
       <c r="H37" t="n">
-        <v>71.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>87.25</v>
+        <v>-222.66</v>
       </c>
       <c r="K37" t="n">
-        <v>55.3</v>
+        <v>417.09</v>
       </c>
       <c r="L37" t="n">
-        <v>103.3</v>
+        <v>472.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:59:17</t>
+          <t>05:59:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.72</v>
+        <v>5.6</v>
       </c>
       <c r="F38" t="n">
-        <v>16.36</v>
+        <v>15.8</v>
       </c>
       <c r="G38" t="n">
-        <v>149.8</v>
+        <v>160</v>
       </c>
       <c r="H38" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-374.77</v>
+        <v>1008.63</v>
       </c>
       <c r="K38" t="n">
-        <v>-101.92</v>
+        <v>597.45</v>
       </c>
       <c r="L38" t="n">
-        <v>388.38</v>
+        <v>1172.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:01:44</t>
+          <t>06:00:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.74</v>
+        <v>5.67</v>
       </c>
       <c r="F39" t="n">
-        <v>16.53</v>
+        <v>16.07</v>
       </c>
       <c r="G39" t="n">
-        <v>167.8</v>
+        <v>156.2</v>
       </c>
       <c r="H39" t="n">
-        <v>65.40000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>18.61</v>
+        <v>331.08</v>
       </c>
       <c r="K39" t="n">
-        <v>-207.14</v>
+        <v>-558.22</v>
       </c>
       <c r="L39" t="n">
-        <v>207.97</v>
+        <v>649.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:04:00</t>
+          <t>06:01:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.42</v>
+        <v>5.74</v>
       </c>
       <c r="F40" t="n">
-        <v>16.61</v>
+        <v>16.5</v>
       </c>
       <c r="G40" t="n">
-        <v>141.7</v>
+        <v>170.2</v>
       </c>
       <c r="H40" t="n">
-        <v>69.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>-48.2</v>
+        <v>256.73</v>
       </c>
       <c r="K40" t="n">
-        <v>-173.05</v>
+        <v>-741.58</v>
       </c>
       <c r="L40" t="n">
-        <v>179.63</v>
+        <v>784.76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:08:01</t>
+          <t>06:06:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.43</v>
+        <v>5.28</v>
       </c>
       <c r="F41" t="n">
-        <v>15.77</v>
+        <v>16.44</v>
       </c>
       <c r="G41" t="n">
-        <v>152.6</v>
+        <v>164.7</v>
       </c>
       <c r="H41" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-34.64</v>
+        <v>545.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-544.9299999999999</v>
+        <v>-1051.14</v>
       </c>
       <c r="L41" t="n">
-        <v>546.03</v>
+        <v>1184.44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:10:09</t>
+          <t>06:09:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6.4</v>
+        <v>5.29</v>
       </c>
       <c r="F42" t="n">
-        <v>16.45</v>
+        <v>15.49</v>
       </c>
       <c r="G42" t="n">
-        <v>156.6</v>
+        <v>154.2</v>
       </c>
       <c r="H42" t="n">
-        <v>66.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>507.58</v>
+        <v>25.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-534.02</v>
+        <v>-432.59</v>
       </c>
       <c r="L42" t="n">
-        <v>736.76</v>
+        <v>433.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:11:16</t>
+          <t>06:10:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.03</v>
+        <v>5.17</v>
       </c>
       <c r="F43" t="n">
-        <v>16.71</v>
+        <v>16.73</v>
       </c>
       <c r="G43" t="n">
-        <v>156.4</v>
+        <v>157.9</v>
       </c>
       <c r="H43" t="n">
-        <v>64.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-175.95</v>
+        <v>302.98</v>
       </c>
       <c r="K43" t="n">
-        <v>337.63</v>
+        <v>631.5599999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>380.73</v>
+        <v>700.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:23:03</t>
+          <t>06:19:41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.3</v>
+        <v>5.61</v>
       </c>
       <c r="F44" t="n">
-        <v>16.51</v>
+        <v>16.56</v>
       </c>
       <c r="G44" t="n">
-        <v>151.9</v>
+        <v>161.5</v>
       </c>
       <c r="H44" t="n">
-        <v>66.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-68.95999999999999</v>
+        <v>-47.21</v>
       </c>
       <c r="K44" t="n">
-        <v>-90.87</v>
+        <v>-335.91</v>
       </c>
       <c r="L44" t="n">
-        <v>114.08</v>
+        <v>339.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:25:33</t>
+          <t>06:21:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.94</v>
+        <v>5.67</v>
       </c>
       <c r="F45" t="n">
-        <v>16.53</v>
+        <v>15.92</v>
       </c>
       <c r="G45" t="n">
-        <v>147.7</v>
+        <v>169.4</v>
       </c>
       <c r="H45" t="n">
-        <v>65.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>81.95999999999999</v>
+        <v>-254.54</v>
       </c>
       <c r="K45" t="n">
-        <v>-39.92</v>
+        <v>-151.35</v>
       </c>
       <c r="L45" t="n">
-        <v>91.16</v>
+        <v>296.14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:27:39</t>
+          <t>06:23:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.93</v>
+        <v>6.27</v>
       </c>
       <c r="F46" t="n">
-        <v>16.31</v>
+        <v>16.54</v>
       </c>
       <c r="G46" t="n">
-        <v>154.3</v>
+        <v>160.1</v>
       </c>
       <c r="H46" t="n">
-        <v>69.3</v>
+        <v>64.7</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.06</v>
+        <v>-390.71</v>
       </c>
       <c r="K46" t="n">
-        <v>124.95</v>
+        <v>-184.66</v>
       </c>
       <c r="L46" t="n">
-        <v>125.85</v>
+        <v>432.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:33:43</t>
+          <t>06:29:49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.6</v>
+        <v>6.08</v>
       </c>
       <c r="F47" t="n">
-        <v>15.89</v>
+        <v>16.16</v>
       </c>
       <c r="G47" t="n">
-        <v>158.1</v>
+        <v>157.8</v>
       </c>
       <c r="H47" t="n">
-        <v>66.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-141.36</v>
+        <v>-197.14</v>
       </c>
       <c r="K47" t="n">
-        <v>190.33</v>
+        <v>501.35</v>
       </c>
       <c r="L47" t="n">
-        <v>237.08</v>
+        <v>538.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:35:45</t>
+          <t>06:31:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.14</v>
+        <v>5.57</v>
       </c>
       <c r="F48" t="n">
-        <v>15.75</v>
+        <v>16.55</v>
       </c>
       <c r="G48" t="n">
-        <v>171.2</v>
+        <v>157.8</v>
       </c>
       <c r="H48" t="n">
-        <v>66.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>314.7</v>
+        <v>-159.49</v>
       </c>
       <c r="K48" t="n">
-        <v>-228.33</v>
+        <v>296.11</v>
       </c>
       <c r="L48" t="n">
-        <v>388.81</v>
+        <v>336.33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:37:05</t>
+          <t>06:33:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.84</v>
+        <v>6.18</v>
       </c>
       <c r="F49" t="n">
-        <v>16.24</v>
+        <v>15.59</v>
       </c>
       <c r="G49" t="n">
-        <v>153.1</v>
+        <v>165.4</v>
       </c>
       <c r="H49" t="n">
-        <v>69.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>185.88</v>
+        <v>-3.6</v>
       </c>
       <c r="K49" t="n">
-        <v>-46.38</v>
+        <v>-194.03</v>
       </c>
       <c r="L49" t="n">
-        <v>191.58</v>
+        <v>194.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:42:39</t>
+          <t>06:38:14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.68</v>
+        <v>5.48</v>
       </c>
       <c r="F50" t="n">
-        <v>16.66</v>
+        <v>15.97</v>
       </c>
       <c r="G50" t="n">
-        <v>153</v>
+        <v>173.7</v>
       </c>
       <c r="H50" t="n">
-        <v>68</v>
+        <v>71.5</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-181.94</v>
+        <v>116.91</v>
       </c>
       <c r="K50" t="n">
-        <v>-403.61</v>
+        <v>274.54</v>
       </c>
       <c r="L50" t="n">
-        <v>442.72</v>
+        <v>298.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:44:14</t>
+          <t>06:40:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.84</v>
+        <v>6.49</v>
       </c>
       <c r="F51" t="n">
-        <v>16.41</v>
+        <v>16.65</v>
       </c>
       <c r="G51" t="n">
-        <v>166.8</v>
+        <v>157.9</v>
       </c>
       <c r="H51" t="n">
-        <v>64.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>441.87</v>
+        <v>-420.42</v>
       </c>
       <c r="K51" t="n">
-        <v>161.59</v>
+        <v>230.74</v>
       </c>
       <c r="L51" t="n">
-        <v>470.49</v>
+        <v>479.58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:45:10</t>
+          <t>06:42:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="F52" t="n">
         <v>16.08</v>
       </c>
       <c r="G52" t="n">
-        <v>159.3</v>
+        <v>155</v>
       </c>
       <c r="H52" t="n">
-        <v>67</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-14.31</v>
+        <v>-315.45</v>
       </c>
       <c r="K52" t="n">
-        <v>50.98</v>
+        <v>-430.69</v>
       </c>
       <c r="L52" t="n">
-        <v>52.95</v>
+        <v>533.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:51:23</t>
+          <t>06:47:44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.34</v>
+        <v>7.47</v>
       </c>
       <c r="F53" t="n">
-        <v>16.07</v>
+        <v>16.33</v>
       </c>
       <c r="G53" t="n">
-        <v>158.8</v>
+        <v>151.2</v>
       </c>
       <c r="H53" t="n">
-        <v>71.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-699.45</v>
+        <v>190.74</v>
       </c>
       <c r="K53" t="n">
-        <v>159.48</v>
+        <v>507.46</v>
       </c>
       <c r="L53" t="n">
-        <v>717.4</v>
+        <v>542.12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:53:50</t>
+          <t>06:49:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.68</v>
+        <v>6.17</v>
       </c>
       <c r="F54" t="n">
-        <v>15.67</v>
+        <v>16.5</v>
       </c>
       <c r="G54" t="n">
-        <v>162</v>
+        <v>153.2</v>
       </c>
       <c r="H54" t="n">
-        <v>66.7</v>
+        <v>68.8</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-150.66</v>
+        <v>128.26</v>
       </c>
       <c r="K54" t="n">
-        <v>-67.01000000000001</v>
+        <v>451.65</v>
       </c>
       <c r="L54" t="n">
-        <v>164.89</v>
+        <v>469.51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:54:30</t>
+          <t>06:50:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6.12</v>
+        <v>4.87</v>
       </c>
       <c r="F55" t="n">
-        <v>16.47</v>
+        <v>16.2</v>
       </c>
       <c r="G55" t="n">
-        <v>159.3</v>
+        <v>161.2</v>
       </c>
       <c r="H55" t="n">
-        <v>73.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>508.17</v>
+        <v>224.36</v>
       </c>
       <c r="K55" t="n">
-        <v>166.11</v>
+        <v>-20.35</v>
       </c>
       <c r="L55" t="n">
-        <v>534.63</v>
+        <v>225.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:59:07</t>
+          <t>06:55:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.86</v>
+        <v>5.1</v>
       </c>
       <c r="F56" t="n">
-        <v>16.41</v>
+        <v>15.76</v>
       </c>
       <c r="G56" t="n">
-        <v>154.7</v>
+        <v>170</v>
       </c>
       <c r="H56" t="n">
-        <v>68.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>75.29000000000001</v>
+        <v>-559</v>
       </c>
       <c r="K56" t="n">
-        <v>-560.41</v>
+        <v>-820.76</v>
       </c>
       <c r="L56" t="n">
-        <v>565.45</v>
+        <v>993.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:59:47</t>
+          <t>06:56:52</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.01</v>
+        <v>5.24</v>
       </c>
       <c r="F57" t="n">
-        <v>16.03</v>
+        <v>16.22</v>
       </c>
       <c r="G57" t="n">
-        <v>167.9</v>
+        <v>160.5</v>
       </c>
       <c r="H57" t="n">
-        <v>59.4</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-25.2</v>
+        <v>-126.36</v>
       </c>
       <c r="K57" t="n">
-        <v>542.36</v>
+        <v>-725.29</v>
       </c>
       <c r="L57" t="n">
-        <v>542.9400000000001</v>
+        <v>736.21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:01:19</t>
+          <t>06:59:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.09</v>
+        <v>6.75</v>
       </c>
       <c r="F58" t="n">
-        <v>15.68</v>
+        <v>15.93</v>
       </c>
       <c r="G58" t="n">
-        <v>160.2</v>
+        <v>152.5</v>
       </c>
       <c r="H58" t="n">
-        <v>68.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>16.03</v>
+        <v>869.88</v>
       </c>
       <c r="K58" t="n">
-        <v>292.41</v>
+        <v>-162.3</v>
       </c>
       <c r="L58" t="n">
-        <v>292.85</v>
+        <v>884.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:12:02</t>
+          <t>07:09:37</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.07</v>
+        <v>5.64</v>
       </c>
       <c r="F59" t="n">
-        <v>15.38</v>
+        <v>15.99</v>
       </c>
       <c r="G59" t="n">
-        <v>149.1</v>
+        <v>157.8</v>
       </c>
       <c r="H59" t="n">
-        <v>68.90000000000001</v>
+        <v>64</v>
       </c>
       <c r="I59" t="n">
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.49</v>
+        <v>-482.9</v>
       </c>
       <c r="K59" t="n">
-        <v>132.25</v>
+        <v>-168.37</v>
       </c>
       <c r="L59" t="n">
-        <v>135.08</v>
+        <v>511.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:12:59</t>
+          <t>07:11:39</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="F60" t="n">
-        <v>16.02</v>
+        <v>16.48</v>
       </c>
       <c r="G60" t="n">
-        <v>161.1</v>
+        <v>157.1</v>
       </c>
       <c r="H60" t="n">
-        <v>70.7</v>
+        <v>63.5</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>141.46</v>
+        <v>-69.56999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-21.94</v>
+        <v>-79.23999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>143.15</v>
+        <v>105.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:15:09</t>
+          <t>07:14:09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.73</v>
+        <v>5.14</v>
       </c>
       <c r="F61" t="n">
-        <v>15.39</v>
+        <v>15.58</v>
       </c>
       <c r="G61" t="n">
-        <v>149</v>
+        <v>159.8</v>
       </c>
       <c r="H61" t="n">
-        <v>70</v>
+        <v>68.7</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-251.64</v>
+        <v>210.73</v>
       </c>
       <c r="K61" t="n">
-        <v>27.24</v>
+        <v>20.78</v>
       </c>
       <c r="L61" t="n">
-        <v>253.11</v>
+        <v>211.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:19:51</t>
+          <t>07:17:28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.72</v>
+        <v>6.2</v>
       </c>
       <c r="F62" t="n">
-        <v>16.43</v>
+        <v>16.19</v>
       </c>
       <c r="G62" t="n">
-        <v>163.1</v>
+        <v>150.2</v>
       </c>
       <c r="H62" t="n">
-        <v>77.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>117.45</v>
+        <v>-0.21</v>
       </c>
       <c r="K62" t="n">
-        <v>-47.31</v>
+        <v>275.37</v>
       </c>
       <c r="L62" t="n">
-        <v>126.62</v>
+        <v>275.37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:21:14</t>
+          <t>07:18:53</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="F63" t="n">
-        <v>16.69</v>
+        <v>15.99</v>
       </c>
       <c r="G63" t="n">
-        <v>161.7</v>
+        <v>165.1</v>
       </c>
       <c r="H63" t="n">
-        <v>67.2</v>
+        <v>66.2</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>47.7</v>
+        <v>-424.21</v>
       </c>
       <c r="K63" t="n">
-        <v>286.83</v>
+        <v>530.95</v>
       </c>
       <c r="L63" t="n">
-        <v>290.77</v>
+        <v>679.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:22:36</t>
+          <t>07:20:49</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.46</v>
+        <v>6.49</v>
       </c>
       <c r="F64" t="n">
-        <v>15.64</v>
+        <v>16.07</v>
       </c>
       <c r="G64" t="n">
-        <v>148.2</v>
+        <v>149.4</v>
       </c>
       <c r="H64" t="n">
-        <v>69.7</v>
+        <v>78.7</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>121.56</v>
+        <v>-52.09</v>
       </c>
       <c r="K64" t="n">
-        <v>-164.22</v>
+        <v>-59.8</v>
       </c>
       <c r="L64" t="n">
-        <v>204.32</v>
+        <v>79.31</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:27:12</t>
+          <t>07:24:42</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.67</v>
+        <v>6.42</v>
       </c>
       <c r="F65" t="n">
-        <v>16.58</v>
+        <v>15.98</v>
       </c>
       <c r="G65" t="n">
-        <v>150.2</v>
+        <v>162</v>
       </c>
       <c r="H65" t="n">
-        <v>68.2</v>
+        <v>58.4</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-266.14</v>
+        <v>4.94</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.94</v>
+        <v>-315.14</v>
       </c>
       <c r="L65" t="n">
-        <v>266.23</v>
+        <v>315.18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:27:58</t>
+          <t>07:26:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.74</v>
+        <v>5.47</v>
       </c>
       <c r="F66" t="n">
-        <v>16.08</v>
+        <v>16.12</v>
       </c>
       <c r="G66" t="n">
-        <v>169.9</v>
+        <v>168.5</v>
       </c>
       <c r="H66" t="n">
-        <v>69.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-217.56</v>
+        <v>-408.26</v>
       </c>
       <c r="K66" t="n">
-        <v>-411.91</v>
+        <v>-564.3099999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>465.84</v>
+        <v>696.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:30:06</t>
+          <t>07:28:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.52</v>
+        <v>6.44</v>
       </c>
       <c r="F67" t="n">
-        <v>16.17</v>
+        <v>16.45</v>
       </c>
       <c r="G67" t="n">
-        <v>161.3</v>
+        <v>148.1</v>
       </c>
       <c r="H67" t="n">
-        <v>63.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>266.17</v>
+        <v>-436.69</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.36</v>
+        <v>293.37</v>
       </c>
       <c r="L67" t="n">
-        <v>266.23</v>
+        <v>526.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:34:50</t>
+          <t>07:33:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>6.46</v>
+        <v>6.64</v>
       </c>
       <c r="F68" t="n">
-        <v>15.42</v>
+        <v>16.43</v>
       </c>
       <c r="G68" t="n">
-        <v>142.6</v>
+        <v>148.8</v>
       </c>
       <c r="H68" t="n">
-        <v>70.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-220.99</v>
+        <v>-336.98</v>
       </c>
       <c r="K68" t="n">
-        <v>153.55</v>
+        <v>934.71</v>
       </c>
       <c r="L68" t="n">
-        <v>269.1</v>
+        <v>993.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:36:17</t>
+          <t>07:34:43</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.27</v>
+        <v>6.16</v>
       </c>
       <c r="F69" t="n">
-        <v>16.48</v>
+        <v>16.02</v>
       </c>
       <c r="G69" t="n">
-        <v>149.2</v>
+        <v>147.5</v>
       </c>
       <c r="H69" t="n">
-        <v>71.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>212.52</v>
+        <v>-337.52</v>
       </c>
       <c r="K69" t="n">
-        <v>-542.72</v>
+        <v>524.27</v>
       </c>
       <c r="L69" t="n">
-        <v>582.84</v>
+        <v>623.52</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:37:59</t>
+          <t>07:35:42</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.14</v>
+        <v>5.64</v>
       </c>
       <c r="F70" t="n">
-        <v>16.21</v>
+        <v>16.61</v>
       </c>
       <c r="G70" t="n">
-        <v>146.9</v>
+        <v>146.5</v>
       </c>
       <c r="H70" t="n">
-        <v>74.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>191.79</v>
+        <v>356.78</v>
       </c>
       <c r="K70" t="n">
-        <v>28.61</v>
+        <v>374.27</v>
       </c>
       <c r="L70" t="n">
-        <v>193.92</v>
+        <v>517.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:42:08</t>
+          <t>07:40:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.13</v>
+        <v>5.89</v>
       </c>
       <c r="F71" t="n">
-        <v>15.98</v>
+        <v>16.26</v>
       </c>
       <c r="G71" t="n">
-        <v>154</v>
+        <v>159.8</v>
       </c>
       <c r="H71" t="n">
-        <v>67.8</v>
+        <v>65</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-157.18</v>
+        <v>674.73</v>
       </c>
       <c r="K71" t="n">
-        <v>-363.12</v>
+        <v>-78.65000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>395.67</v>
+        <v>679.29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:43:26</t>
+          <t>07:42:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.06</v>
+        <v>6.23</v>
       </c>
       <c r="F72" t="n">
-        <v>16.47</v>
+        <v>15.63</v>
       </c>
       <c r="G72" t="n">
-        <v>150.4</v>
+        <v>160.8</v>
       </c>
       <c r="H72" t="n">
-        <v>72.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-114.57</v>
+        <v>-456.34</v>
       </c>
       <c r="K72" t="n">
-        <v>242.69</v>
+        <v>-243.01</v>
       </c>
       <c r="L72" t="n">
-        <v>268.38</v>
+        <v>517.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:46:00</t>
+          <t>07:44:16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.23</v>
+        <v>5.25</v>
       </c>
       <c r="F73" t="n">
-        <v>16.6</v>
+        <v>16.38</v>
       </c>
       <c r="G73" t="n">
-        <v>158.7</v>
+        <v>152</v>
       </c>
       <c r="H73" t="n">
-        <v>67</v>
+        <v>77.8</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>375.87</v>
+        <v>-485.12</v>
       </c>
       <c r="K73" t="n">
-        <v>-143.51</v>
+        <v>183.81</v>
       </c>
       <c r="L73" t="n">
-        <v>402.33</v>
+        <v>518.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:57:25</t>
+          <t>07:52:45</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.99</v>
+        <v>6.49</v>
       </c>
       <c r="F74" t="n">
-        <v>16.51</v>
+        <v>16.14</v>
       </c>
       <c r="G74" t="n">
-        <v>154.3</v>
+        <v>146.7</v>
       </c>
       <c r="H74" t="n">
-        <v>67.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-141.62</v>
+        <v>6.56</v>
       </c>
       <c r="K74" t="n">
-        <v>-35.17</v>
+        <v>608.85</v>
       </c>
       <c r="L74" t="n">
-        <v>145.92</v>
+        <v>608.88</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:59:20</t>
+          <t>07:54:43</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>7.22</v>
+        <v>6.03</v>
       </c>
       <c r="F75" t="n">
-        <v>17.22</v>
+        <v>15.91</v>
       </c>
       <c r="G75" t="n">
-        <v>153.6</v>
+        <v>154.9</v>
       </c>
       <c r="H75" t="n">
-        <v>71.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>262.86</v>
+        <v>473.73</v>
       </c>
       <c r="K75" t="n">
-        <v>145.29</v>
+        <v>60.45</v>
       </c>
       <c r="L75" t="n">
-        <v>300.34</v>
+        <v>477.57</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:59:56</t>
+          <t>07:56:39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.67</v>
+        <v>6.03</v>
       </c>
       <c r="F76" t="n">
-        <v>16.26</v>
+        <v>15.7</v>
       </c>
       <c r="G76" t="n">
-        <v>159</v>
+        <v>161.6</v>
       </c>
       <c r="H76" t="n">
-        <v>67.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-120.56</v>
+        <v>-269.5</v>
       </c>
       <c r="K76" t="n">
-        <v>-111.04</v>
+        <v>103</v>
       </c>
       <c r="L76" t="n">
-        <v>163.9</v>
+        <v>288.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:04:48</t>
+          <t>08:01:04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.66</v>
+        <v>7.16</v>
       </c>
       <c r="F77" t="n">
         <v>16.56</v>
       </c>
       <c r="G77" t="n">
-        <v>139.7</v>
+        <v>160.6</v>
       </c>
       <c r="H77" t="n">
-        <v>65.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="I77" t="n">
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>432.15</v>
+        <v>446.01</v>
       </c>
       <c r="K77" t="n">
-        <v>-337.39</v>
+        <v>-61.44</v>
       </c>
       <c r="L77" t="n">
-        <v>548.26</v>
+        <v>450.22</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:07:14</t>
+          <t>08:03:09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.85</v>
+        <v>5.81</v>
       </c>
       <c r="F78" t="n">
-        <v>16.04</v>
+        <v>15.66</v>
       </c>
       <c r="G78" t="n">
-        <v>156</v>
+        <v>160.6</v>
       </c>
       <c r="H78" t="n">
-        <v>73.2</v>
+        <v>67.2</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>40.65</v>
+        <v>163.86</v>
       </c>
       <c r="K78" t="n">
-        <v>-103.67</v>
+        <v>-199.61</v>
       </c>
       <c r="L78" t="n">
-        <v>111.35</v>
+        <v>258.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:09:20</t>
+          <t>08:04:24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.94</v>
+        <v>6.35</v>
       </c>
       <c r="F79" t="n">
-        <v>15.6</v>
+        <v>16.58</v>
       </c>
       <c r="G79" t="n">
-        <v>161.5</v>
+        <v>141.6</v>
       </c>
       <c r="H79" t="n">
-        <v>71.8</v>
+        <v>66.3</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-163.78</v>
+        <v>-60.81</v>
       </c>
       <c r="K79" t="n">
-        <v>358.59</v>
+        <v>-228.66</v>
       </c>
       <c r="L79" t="n">
-        <v>394.23</v>
+        <v>236.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:15:06</t>
+          <t>08:09:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>7.43</v>
+        <v>6.46</v>
       </c>
       <c r="F80" t="n">
-        <v>16.8</v>
+        <v>16.18</v>
       </c>
       <c r="G80" t="n">
-        <v>159.6</v>
+        <v>152.4</v>
       </c>
       <c r="H80" t="n">
-        <v>69.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>575.09</v>
+        <v>570.17</v>
       </c>
       <c r="K80" t="n">
-        <v>426.09</v>
+        <v>58.33</v>
       </c>
       <c r="L80" t="n">
-        <v>715.74</v>
+        <v>573.14</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:16:37</t>
+          <t>08:11:22</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.14</v>
+        <v>5.67</v>
       </c>
       <c r="F81" t="n">
-        <v>16.26</v>
+        <v>16.17</v>
       </c>
       <c r="G81" t="n">
-        <v>154.5</v>
+        <v>142</v>
       </c>
       <c r="H81" t="n">
-        <v>67.2</v>
+        <v>61.4</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-229.46</v>
+        <v>-77.75</v>
       </c>
       <c r="K81" t="n">
-        <v>42.91</v>
+        <v>288.26</v>
       </c>
       <c r="L81" t="n">
-        <v>233.44</v>
+        <v>298.56</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:17:44</t>
+          <t>08:12:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.75</v>
+        <v>5.71</v>
       </c>
       <c r="F82" t="n">
-        <v>15.86</v>
+        <v>16.18</v>
       </c>
       <c r="G82" t="n">
-        <v>144.6</v>
+        <v>151.9</v>
       </c>
       <c r="H82" t="n">
-        <v>71.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-143.02</v>
+        <v>-644.67</v>
       </c>
       <c r="K82" t="n">
-        <v>-337.23</v>
+        <v>-836.55</v>
       </c>
       <c r="L82" t="n">
-        <v>366.3</v>
+        <v>1056.13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:22:57</t>
+          <t>08:18:04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.98</v>
+        <v>6.28</v>
       </c>
       <c r="F83" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="G83" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I83" t="n">
         <v>16</v>
       </c>
-      <c r="G83" t="n">
-        <v>156.4</v>
-      </c>
-      <c r="H83" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="I83" t="n">
-        <v>21</v>
-      </c>
       <c r="J83" t="n">
-        <v>-28.44</v>
+        <v>161.07</v>
       </c>
       <c r="K83" t="n">
-        <v>-734.0599999999999</v>
+        <v>-1277.52</v>
       </c>
       <c r="L83" t="n">
-        <v>734.61</v>
+        <v>1287.64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:24:47</t>
+          <t>08:20:06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
       <c r="F84" t="n">
-        <v>16.43</v>
+        <v>15.75</v>
       </c>
       <c r="G84" t="n">
-        <v>164.8</v>
+        <v>153.3</v>
       </c>
       <c r="H84" t="n">
-        <v>65.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-109.47</v>
+        <v>339.4</v>
       </c>
       <c r="K84" t="n">
-        <v>-65.34999999999999</v>
+        <v>364.22</v>
       </c>
       <c r="L84" t="n">
-        <v>127.49</v>
+        <v>497.84</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:26:22</t>
+          <t>08:21:40</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.84</v>
+        <v>5.89</v>
       </c>
       <c r="F85" t="n">
-        <v>15.96</v>
+        <v>17.14</v>
       </c>
       <c r="G85" t="n">
-        <v>166.5</v>
+        <v>154</v>
       </c>
       <c r="H85" t="n">
-        <v>67.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-155.84</v>
+        <v>-991.39</v>
       </c>
       <c r="K85" t="n">
-        <v>-105.98</v>
+        <v>-94.97</v>
       </c>
       <c r="L85" t="n">
-        <v>188.46</v>
+        <v>995.9299999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:31:13</t>
+          <t>08:25:50</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.44</v>
+        <v>6.44</v>
       </c>
       <c r="F86" t="n">
-        <v>15.86</v>
+        <v>15.82</v>
       </c>
       <c r="G86" t="n">
-        <v>155.8</v>
+        <v>162.1</v>
       </c>
       <c r="H86" t="n">
-        <v>63.7</v>
+        <v>65</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-171.93</v>
+        <v>-676.3</v>
       </c>
       <c r="K86" t="n">
-        <v>859.5</v>
+        <v>-538.65</v>
       </c>
       <c r="L86" t="n">
-        <v>876.53</v>
+        <v>864.59</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:32:31</t>
+          <t>08:27:09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.27</v>
+        <v>6.74</v>
       </c>
       <c r="F87" t="n">
-        <v>15.53</v>
+        <v>15.88</v>
       </c>
       <c r="G87" t="n">
-        <v>152.4</v>
+        <v>157.5</v>
       </c>
       <c r="H87" t="n">
-        <v>62.1</v>
+        <v>69.3</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-576.54</v>
+        <v>475.74</v>
       </c>
       <c r="K87" t="n">
-        <v>-92.54000000000001</v>
+        <v>929.62</v>
       </c>
       <c r="L87" t="n">
-        <v>583.92</v>
+        <v>1044.28</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:33:22</t>
+          <t>08:28:19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.73</v>
+        <v>6.57</v>
       </c>
       <c r="F88" t="n">
-        <v>16.84</v>
+        <v>16.39</v>
       </c>
       <c r="G88" t="n">
-        <v>166.5</v>
+        <v>163.8</v>
       </c>
       <c r="H88" t="n">
-        <v>71.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-48.07</v>
+        <v>757.58</v>
       </c>
       <c r="K88" t="n">
-        <v>-608.77</v>
+        <v>923.91</v>
       </c>
       <c r="L88" t="n">
-        <v>610.66</v>
+        <v>1194.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-196.38</v>
+        <v>-266.12</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.26</v>
+        <v>-38.3</v>
       </c>
       <c r="L14" t="n">
-        <v>198.4</v>
+        <v>268.86</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>268.48</v>
+        <v>311.91</v>
       </c>
       <c r="K15" t="n">
-        <v>210.05</v>
+        <v>244.03</v>
       </c>
       <c r="L15" t="n">
-        <v>340.88</v>
+        <v>396.03</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-114.65</v>
+        <v>-228.07</v>
       </c>
       <c r="K16" t="n">
-        <v>51.29</v>
+        <v>102.03</v>
       </c>
       <c r="L16" t="n">
-        <v>125.6</v>
+        <v>249.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-79.95999999999999</v>
+        <v>-103.41</v>
       </c>
       <c r="K17" t="n">
-        <v>-297.04</v>
+        <v>-384.16</v>
       </c>
       <c r="L17" t="n">
-        <v>307.62</v>
+        <v>397.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>409.67</v>
+        <v>478.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-188.39</v>
+        <v>-219.97</v>
       </c>
       <c r="L18" t="n">
-        <v>450.91</v>
+        <v>526.49</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>167.04</v>
+        <v>278.36</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.16</v>
+        <v>-3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>167.05</v>
+        <v>278.38</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-728.83</v>
+        <v>-912.74</v>
       </c>
       <c r="K20" t="n">
-        <v>-504.32</v>
+        <v>-631.5700000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>886.3</v>
+        <v>1109.95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>560.89</v>
+        <v>732.0599999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>653.2</v>
+        <v>852.55</v>
       </c>
       <c r="L21" t="n">
-        <v>860.97</v>
+        <v>1123.72</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-287.46</v>
+        <v>-374.14</v>
       </c>
       <c r="K22" t="n">
-        <v>-400.51</v>
+        <v>-521.28</v>
       </c>
       <c r="L22" t="n">
-        <v>492.99</v>
+        <v>641.65</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>212.14</v>
+        <v>416.64</v>
       </c>
       <c r="K23" t="n">
-        <v>-485.97</v>
+        <v>-954.4299999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>530.26</v>
+        <v>1041.41</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-90.09</v>
+        <v>-147.33</v>
       </c>
       <c r="K24" t="n">
-        <v>-419.06</v>
+        <v>-685.29</v>
       </c>
       <c r="L24" t="n">
-        <v>428.63</v>
+        <v>700.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>568.36</v>
+        <v>928.66</v>
       </c>
       <c r="K25" t="n">
-        <v>-142.22</v>
+        <v>-232.38</v>
       </c>
       <c r="L25" t="n">
-        <v>585.88</v>
+        <v>957.29</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>422.67</v>
+        <v>823.12</v>
       </c>
       <c r="K26" t="n">
-        <v>-398.57</v>
+        <v>-776.1900000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>580.95</v>
+        <v>1131.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>239.68</v>
+        <v>394.56</v>
       </c>
       <c r="K27" t="n">
-        <v>-685.65</v>
+        <v>-1128.7</v>
       </c>
       <c r="L27" t="n">
-        <v>726.33</v>
+        <v>1195.68</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>384.57</v>
+        <v>844.47</v>
       </c>
       <c r="K28" t="n">
-        <v>-187.47</v>
+        <v>-411.66</v>
       </c>
       <c r="L28" t="n">
-        <v>427.83</v>
+        <v>939.47</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>207.21</v>
+        <v>291.54</v>
       </c>
       <c r="K29" t="n">
-        <v>-122.97</v>
+        <v>-173.01</v>
       </c>
       <c r="L29" t="n">
-        <v>240.95</v>
+        <v>339.01</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-281.2</v>
+        <v>-328.16</v>
       </c>
       <c r="K30" t="n">
-        <v>-445.24</v>
+        <v>-519.61</v>
       </c>
       <c r="L30" t="n">
-        <v>526.6</v>
+        <v>614.5599999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-66.83</v>
+        <v>-87</v>
       </c>
       <c r="K31" t="n">
-        <v>271.27</v>
+        <v>353.13</v>
       </c>
       <c r="L31" t="n">
-        <v>279.39</v>
+        <v>363.69</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-217.7</v>
+        <v>-370.02</v>
       </c>
       <c r="K32" t="n">
-        <v>-120.72</v>
+        <v>-205.19</v>
       </c>
       <c r="L32" t="n">
-        <v>248.93</v>
+        <v>423.11</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>66.78</v>
+        <v>121.52</v>
       </c>
       <c r="K33" t="n">
-        <v>-176.15</v>
+        <v>-320.53</v>
       </c>
       <c r="L33" t="n">
-        <v>188.38</v>
+        <v>342.79</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-141.66</v>
+        <v>-285.58</v>
       </c>
       <c r="K34" t="n">
-        <v>36.38</v>
+        <v>73.34</v>
       </c>
       <c r="L34" t="n">
-        <v>146.26</v>
+        <v>294.84</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-319.04</v>
+        <v>-513.89</v>
       </c>
       <c r="K35" t="n">
-        <v>255.05</v>
+        <v>410.81</v>
       </c>
       <c r="L35" t="n">
-        <v>408.46</v>
+        <v>657.91</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-184.48</v>
+        <v>-281.77</v>
       </c>
       <c r="K36" t="n">
-        <v>-264.67</v>
+        <v>-404.24</v>
       </c>
       <c r="L36" t="n">
-        <v>322.62</v>
+        <v>492.75</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-222.66</v>
+        <v>-309.43</v>
       </c>
       <c r="K37" t="n">
-        <v>417.09</v>
+        <v>579.62</v>
       </c>
       <c r="L37" t="n">
-        <v>472.8</v>
+        <v>657.04</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>1008.63</v>
+        <v>1335.55</v>
       </c>
       <c r="K38" t="n">
-        <v>597.45</v>
+        <v>791.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1172.29</v>
+        <v>1552.26</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>331.08</v>
+        <v>528.34</v>
       </c>
       <c r="K39" t="n">
-        <v>-558.22</v>
+        <v>-890.8099999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>649.02</v>
+        <v>1035.7</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>256.73</v>
+        <v>388.48</v>
       </c>
       <c r="K40" t="n">
-        <v>-741.58</v>
+        <v>-1122.16</v>
       </c>
       <c r="L40" t="n">
-        <v>784.76</v>
+        <v>1187.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>545.9</v>
+        <v>818.4</v>
       </c>
       <c r="K41" t="n">
-        <v>-1051.14</v>
+        <v>-1575.85</v>
       </c>
       <c r="L41" t="n">
-        <v>1184.44</v>
+        <v>1775.69</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>25.06</v>
+        <v>52.46</v>
       </c>
       <c r="K42" t="n">
-        <v>-432.59</v>
+        <v>-905.63</v>
       </c>
       <c r="L42" t="n">
-        <v>433.31</v>
+        <v>907.15</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>302.98</v>
+        <v>525.6799999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>631.5599999999999</v>
+        <v>1095.77</v>
       </c>
       <c r="L43" t="n">
-        <v>700.47</v>
+        <v>1215.34</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-47.21</v>
+        <v>-63.44</v>
       </c>
       <c r="K44" t="n">
-        <v>-335.91</v>
+        <v>-451.4</v>
       </c>
       <c r="L44" t="n">
-        <v>339.21</v>
+        <v>455.83</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-254.54</v>
+        <v>-359.65</v>
       </c>
       <c r="K45" t="n">
-        <v>-151.35</v>
+        <v>-213.85</v>
       </c>
       <c r="L45" t="n">
-        <v>296.14</v>
+        <v>418.43</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-390.71</v>
+        <v>-484.38</v>
       </c>
       <c r="K46" t="n">
-        <v>-184.66</v>
+        <v>-228.93</v>
       </c>
       <c r="L46" t="n">
-        <v>432.15</v>
+        <v>535.76</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-197.14</v>
+        <v>-255.2</v>
       </c>
       <c r="K47" t="n">
-        <v>501.35</v>
+        <v>649.01</v>
       </c>
       <c r="L47" t="n">
-        <v>538.72</v>
+        <v>697.38</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-159.49</v>
+        <v>-217.54</v>
       </c>
       <c r="K48" t="n">
-        <v>296.11</v>
+        <v>403.9</v>
       </c>
       <c r="L48" t="n">
-        <v>336.33</v>
+        <v>458.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.6</v>
+        <v>-6.54</v>
       </c>
       <c r="K49" t="n">
-        <v>-194.03</v>
+        <v>-352.31</v>
       </c>
       <c r="L49" t="n">
-        <v>194.07</v>
+        <v>352.37</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>116.91</v>
+        <v>208.45</v>
       </c>
       <c r="K50" t="n">
-        <v>274.54</v>
+        <v>489.48</v>
       </c>
       <c r="L50" t="n">
-        <v>298.4</v>
+        <v>532.02</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-420.42</v>
+        <v>-665.55</v>
       </c>
       <c r="K51" t="n">
-        <v>230.74</v>
+        <v>365.27</v>
       </c>
       <c r="L51" t="n">
-        <v>479.58</v>
+        <v>759.1900000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-315.45</v>
+        <v>-439.94</v>
       </c>
       <c r="K52" t="n">
-        <v>-430.69</v>
+        <v>-600.65</v>
       </c>
       <c r="L52" t="n">
-        <v>533.86</v>
+        <v>744.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>190.74</v>
+        <v>352.25</v>
       </c>
       <c r="K53" t="n">
-        <v>507.46</v>
+        <v>937.15</v>
       </c>
       <c r="L53" t="n">
-        <v>542.12</v>
+        <v>1001.17</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>128.26</v>
+        <v>249.19</v>
       </c>
       <c r="K54" t="n">
-        <v>451.65</v>
+        <v>877.46</v>
       </c>
       <c r="L54" t="n">
-        <v>469.51</v>
+        <v>912.16</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>224.36</v>
+        <v>493.44</v>
       </c>
       <c r="K55" t="n">
-        <v>-20.35</v>
+        <v>-44.77</v>
       </c>
       <c r="L55" t="n">
-        <v>225.29</v>
+        <v>495.46</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-559</v>
+        <v>-862.74</v>
       </c>
       <c r="K56" t="n">
-        <v>-820.76</v>
+        <v>-1266.74</v>
       </c>
       <c r="L56" t="n">
-        <v>993.03</v>
+        <v>1532.63</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-126.36</v>
+        <v>-217.43</v>
       </c>
       <c r="K57" t="n">
-        <v>-725.29</v>
+        <v>-1248</v>
       </c>
       <c r="L57" t="n">
-        <v>736.21</v>
+        <v>1266.8</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>869.88</v>
+        <v>1617.24</v>
       </c>
       <c r="K58" t="n">
-        <v>-162.3</v>
+        <v>-301.74</v>
       </c>
       <c r="L58" t="n">
-        <v>884.89</v>
+        <v>1645.15</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-482.9</v>
+        <v>-534.47</v>
       </c>
       <c r="K59" t="n">
-        <v>-168.37</v>
+        <v>-186.35</v>
       </c>
       <c r="L59" t="n">
-        <v>511.41</v>
+        <v>566.02</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-69.56999999999999</v>
+        <v>-160.73</v>
       </c>
       <c r="K60" t="n">
-        <v>-79.23999999999999</v>
+        <v>-183.08</v>
       </c>
       <c r="L60" t="n">
-        <v>105.45</v>
+        <v>243.62</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>210.73</v>
+        <v>314.13</v>
       </c>
       <c r="K61" t="n">
-        <v>20.78</v>
+        <v>30.98</v>
       </c>
       <c r="L61" t="n">
-        <v>211.75</v>
+        <v>315.65</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.21</v>
+        <v>-0.34</v>
       </c>
       <c r="K62" t="n">
-        <v>275.37</v>
+        <v>445.2</v>
       </c>
       <c r="L62" t="n">
-        <v>275.37</v>
+        <v>445.2</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-424.21</v>
+        <v>-507.31</v>
       </c>
       <c r="K63" t="n">
-        <v>530.95</v>
+        <v>634.95</v>
       </c>
       <c r="L63" t="n">
-        <v>679.6</v>
+        <v>812.73</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-52.09</v>
+        <v>-168.26</v>
       </c>
       <c r="K64" t="n">
-        <v>-59.8</v>
+        <v>-193.16</v>
       </c>
       <c r="L64" t="n">
-        <v>79.31</v>
+        <v>256.17</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>4.94</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-315.14</v>
+        <v>-533.98</v>
       </c>
       <c r="L65" t="n">
-        <v>315.18</v>
+        <v>534.05</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-408.26</v>
+        <v>-544.77</v>
       </c>
       <c r="K66" t="n">
-        <v>-564.3099999999999</v>
+        <v>-753</v>
       </c>
       <c r="L66" t="n">
-        <v>696.5</v>
+        <v>929.4</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-436.69</v>
+        <v>-686.72</v>
       </c>
       <c r="K67" t="n">
-        <v>293.37</v>
+        <v>461.33</v>
       </c>
       <c r="L67" t="n">
-        <v>526.08</v>
+        <v>827.29</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-336.98</v>
+        <v>-520.6900000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>934.71</v>
+        <v>1444.29</v>
       </c>
       <c r="L68" t="n">
-        <v>993.6</v>
+        <v>1535.28</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-337.52</v>
+        <v>-579.97</v>
       </c>
       <c r="K69" t="n">
-        <v>524.27</v>
+        <v>900.86</v>
       </c>
       <c r="L69" t="n">
-        <v>623.52</v>
+        <v>1071.41</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>356.78</v>
+        <v>596.17</v>
       </c>
       <c r="K70" t="n">
-        <v>374.27</v>
+        <v>625.4</v>
       </c>
       <c r="L70" t="n">
-        <v>517.08</v>
+        <v>864.03</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>674.73</v>
+        <v>1267.46</v>
       </c>
       <c r="K71" t="n">
-        <v>-78.65000000000001</v>
+        <v>-147.74</v>
       </c>
       <c r="L71" t="n">
-        <v>679.29</v>
+        <v>1276.04</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-456.34</v>
+        <v>-994.26</v>
       </c>
       <c r="K72" t="n">
-        <v>-243.01</v>
+        <v>-529.48</v>
       </c>
       <c r="L72" t="n">
-        <v>517.01</v>
+        <v>1126.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-485.12</v>
+        <v>-877.11</v>
       </c>
       <c r="K73" t="n">
-        <v>183.81</v>
+        <v>332.33</v>
       </c>
       <c r="L73" t="n">
-        <v>518.77</v>
+        <v>937.96</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>6.56</v>
+        <v>8.1</v>
       </c>
       <c r="K74" t="n">
-        <v>608.85</v>
+        <v>751.96</v>
       </c>
       <c r="L74" t="n">
-        <v>608.88</v>
+        <v>752</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>473.73</v>
+        <v>574.99</v>
       </c>
       <c r="K75" t="n">
-        <v>60.45</v>
+        <v>73.37</v>
       </c>
       <c r="L75" t="n">
-        <v>477.57</v>
+        <v>579.66</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-269.5</v>
+        <v>-398.13</v>
       </c>
       <c r="K76" t="n">
-        <v>103</v>
+        <v>152.16</v>
       </c>
       <c r="L76" t="n">
-        <v>288.51</v>
+        <v>426.21</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>446.01</v>
+        <v>597.58</v>
       </c>
       <c r="K77" t="n">
-        <v>-61.44</v>
+        <v>-82.31999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>450.22</v>
+        <v>603.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>163.86</v>
+        <v>264.94</v>
       </c>
       <c r="K78" t="n">
-        <v>-199.61</v>
+        <v>-322.76</v>
       </c>
       <c r="L78" t="n">
-        <v>258.25</v>
+        <v>417.57</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-60.81</v>
+        <v>-105.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-228.66</v>
+        <v>-395.25</v>
       </c>
       <c r="L79" t="n">
-        <v>236.61</v>
+        <v>408.98</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>570.17</v>
+        <v>810.47</v>
       </c>
       <c r="K80" t="n">
-        <v>58.33</v>
+        <v>82.91</v>
       </c>
       <c r="L80" t="n">
-        <v>573.14</v>
+        <v>814.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-77.75</v>
+        <v>-141.41</v>
       </c>
       <c r="K81" t="n">
-        <v>288.26</v>
+        <v>524.25</v>
       </c>
       <c r="L81" t="n">
-        <v>298.56</v>
+        <v>542.99</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-644.67</v>
+        <v>-770.9299999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-836.55</v>
+        <v>-1000.39</v>
       </c>
       <c r="L82" t="n">
-        <v>1056.13</v>
+        <v>1262.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>161.07</v>
+        <v>228.47</v>
       </c>
       <c r="K83" t="n">
-        <v>-1277.52</v>
+        <v>-1812.1</v>
       </c>
       <c r="L83" t="n">
-        <v>1287.64</v>
+        <v>1826.45</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>339.4</v>
+        <v>625.23</v>
       </c>
       <c r="K84" t="n">
-        <v>364.22</v>
+        <v>670.95</v>
       </c>
       <c r="L84" t="n">
-        <v>497.84</v>
+        <v>917.11</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-991.39</v>
+        <v>-1453.71</v>
       </c>
       <c r="K85" t="n">
-        <v>-94.97</v>
+        <v>-139.26</v>
       </c>
       <c r="L85" t="n">
-        <v>995.9299999999999</v>
+        <v>1460.37</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-676.3</v>
+        <v>-1235.31</v>
       </c>
       <c r="K86" t="n">
-        <v>-538.65</v>
+        <v>-983.88</v>
       </c>
       <c r="L86" t="n">
-        <v>864.59</v>
+        <v>1579.25</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>475.74</v>
+        <v>835.42</v>
       </c>
       <c r="K87" t="n">
-        <v>929.62</v>
+        <v>1632.43</v>
       </c>
       <c r="L87" t="n">
-        <v>1044.28</v>
+        <v>1833.78</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>757.58</v>
+        <v>1260.44</v>
       </c>
       <c r="K88" t="n">
-        <v>923.91</v>
+        <v>1537.16</v>
       </c>
       <c r="L88" t="n">
-        <v>1194.8</v>
+        <v>1987.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-266.12</v>
+        <v>-166.31</v>
       </c>
       <c r="K14" t="n">
-        <v>-38.3</v>
+        <v>-23.94</v>
       </c>
       <c r="L14" t="n">
-        <v>268.86</v>
+        <v>168.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>311.91</v>
+        <v>201.69</v>
       </c>
       <c r="K15" t="n">
-        <v>244.03</v>
+        <v>157.79</v>
       </c>
       <c r="L15" t="n">
-        <v>396.03</v>
+        <v>256.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-228.07</v>
+        <v>-134.88</v>
       </c>
       <c r="K16" t="n">
-        <v>102.03</v>
+        <v>60.34</v>
       </c>
       <c r="L16" t="n">
-        <v>249.86</v>
+        <v>147.77</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-103.41</v>
+        <v>-59.15</v>
       </c>
       <c r="K17" t="n">
-        <v>-384.16</v>
+        <v>-219.73</v>
       </c>
       <c r="L17" t="n">
-        <v>397.84</v>
+        <v>227.55</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>478.34</v>
+        <v>289.86</v>
       </c>
       <c r="K18" t="n">
-        <v>-219.97</v>
+        <v>-133.3</v>
       </c>
       <c r="L18" t="n">
-        <v>526.49</v>
+        <v>319.04</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>278.36</v>
+        <v>172.13</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.6</v>
+        <v>-2.23</v>
       </c>
       <c r="L19" t="n">
-        <v>278.38</v>
+        <v>172.14</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-912.74</v>
+        <v>-469.47</v>
       </c>
       <c r="K20" t="n">
-        <v>-631.5700000000001</v>
+        <v>-324.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1109.95</v>
+        <v>570.9</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>732.0599999999999</v>
+        <v>359.16</v>
       </c>
       <c r="K21" t="n">
-        <v>852.55</v>
+        <v>418.27</v>
       </c>
       <c r="L21" t="n">
-        <v>1123.72</v>
+        <v>551.3099999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-374.14</v>
+        <v>-202.29</v>
       </c>
       <c r="K22" t="n">
-        <v>-521.28</v>
+        <v>-281.85</v>
       </c>
       <c r="L22" t="n">
-        <v>641.65</v>
+        <v>346.93</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>416.64</v>
+        <v>175.1</v>
       </c>
       <c r="K23" t="n">
-        <v>-954.4299999999999</v>
+        <v>-401.11</v>
       </c>
       <c r="L23" t="n">
-        <v>1041.41</v>
+        <v>437.66</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-147.33</v>
+        <v>-69.22</v>
       </c>
       <c r="K24" t="n">
-        <v>-685.29</v>
+        <v>-321.95</v>
       </c>
       <c r="L24" t="n">
-        <v>700.95</v>
+        <v>329.31</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>928.66</v>
+        <v>425.21</v>
       </c>
       <c r="K25" t="n">
-        <v>-232.38</v>
+        <v>-106.4</v>
       </c>
       <c r="L25" t="n">
-        <v>957.29</v>
+        <v>438.32</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>823.12</v>
+        <v>327.51</v>
       </c>
       <c r="K26" t="n">
-        <v>-776.1900000000001</v>
+        <v>-308.84</v>
       </c>
       <c r="L26" t="n">
-        <v>1131.37</v>
+        <v>450.16</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>394.56</v>
+        <v>162.88</v>
       </c>
       <c r="K27" t="n">
-        <v>-1128.7</v>
+        <v>-465.96</v>
       </c>
       <c r="L27" t="n">
-        <v>1195.68</v>
+        <v>493.61</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>844.47</v>
+        <v>343.7</v>
       </c>
       <c r="K28" t="n">
-        <v>-411.66</v>
+        <v>-167.55</v>
       </c>
       <c r="L28" t="n">
-        <v>939.47</v>
+        <v>382.37</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>291.54</v>
+        <v>171.27</v>
       </c>
       <c r="K29" t="n">
-        <v>-173.01</v>
+        <v>-101.64</v>
       </c>
       <c r="L29" t="n">
-        <v>339.01</v>
+        <v>199.16</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-328.16</v>
+        <v>-194.39</v>
       </c>
       <c r="K30" t="n">
-        <v>-519.61</v>
+        <v>-307.79</v>
       </c>
       <c r="L30" t="n">
-        <v>614.5599999999999</v>
+        <v>364.03</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-87</v>
+        <v>-52.35</v>
       </c>
       <c r="K31" t="n">
-        <v>353.13</v>
+        <v>212.51</v>
       </c>
       <c r="L31" t="n">
-        <v>363.69</v>
+        <v>218.86</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-370.02</v>
+        <v>-203.55</v>
       </c>
       <c r="K32" t="n">
-        <v>-205.19</v>
+        <v>-112.88</v>
       </c>
       <c r="L32" t="n">
-        <v>423.11</v>
+        <v>232.76</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>121.52</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-320.53</v>
+        <v>-185.12</v>
       </c>
       <c r="L33" t="n">
-        <v>342.79</v>
+        <v>197.97</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-285.58</v>
+        <v>-169.16</v>
       </c>
       <c r="K34" t="n">
-        <v>73.34</v>
+        <v>43.44</v>
       </c>
       <c r="L34" t="n">
-        <v>294.84</v>
+        <v>174.65</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-513.89</v>
+        <v>-248.17</v>
       </c>
       <c r="K35" t="n">
-        <v>410.81</v>
+        <v>198.39</v>
       </c>
       <c r="L35" t="n">
-        <v>657.91</v>
+        <v>317.72</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-281.77</v>
+        <v>-148.67</v>
       </c>
       <c r="K36" t="n">
-        <v>-404.24</v>
+        <v>-213.3</v>
       </c>
       <c r="L36" t="n">
-        <v>492.75</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-309.43</v>
+        <v>-165.03</v>
       </c>
       <c r="K37" t="n">
-        <v>579.62</v>
+        <v>309.13</v>
       </c>
       <c r="L37" t="n">
-        <v>657.04</v>
+        <v>350.43</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>1335.55</v>
+        <v>602.11</v>
       </c>
       <c r="K38" t="n">
-        <v>791.1</v>
+        <v>356.65</v>
       </c>
       <c r="L38" t="n">
-        <v>1552.26</v>
+        <v>699.8099999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>528.34</v>
+        <v>232.18</v>
       </c>
       <c r="K39" t="n">
-        <v>-890.8099999999999</v>
+        <v>-391.47</v>
       </c>
       <c r="L39" t="n">
-        <v>1035.7</v>
+        <v>455.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>388.48</v>
+        <v>170.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-1122.16</v>
+        <v>-492.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1187.5</v>
+        <v>521.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>818.4</v>
+        <v>322.04</v>
       </c>
       <c r="K41" t="n">
-        <v>-1575.85</v>
+        <v>-620.09</v>
       </c>
       <c r="L41" t="n">
-        <v>1775.69</v>
+        <v>698.73</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>52.46</v>
+        <v>21.12</v>
       </c>
       <c r="K42" t="n">
-        <v>-905.63</v>
+        <v>-364.52</v>
       </c>
       <c r="L42" t="n">
-        <v>907.15</v>
+        <v>365.13</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>525.6799999999999</v>
+        <v>207.43</v>
       </c>
       <c r="K43" t="n">
-        <v>1095.77</v>
+        <v>432.39</v>
       </c>
       <c r="L43" t="n">
-        <v>1215.34</v>
+        <v>479.57</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-63.44</v>
+        <v>-36.69</v>
       </c>
       <c r="K44" t="n">
-        <v>-451.4</v>
+        <v>-261.04</v>
       </c>
       <c r="L44" t="n">
-        <v>455.83</v>
+        <v>263.6</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-359.65</v>
+        <v>-207.7</v>
       </c>
       <c r="K45" t="n">
-        <v>-213.85</v>
+        <v>-123.5</v>
       </c>
       <c r="L45" t="n">
-        <v>418.43</v>
+        <v>241.64</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-484.38</v>
+        <v>-297.16</v>
       </c>
       <c r="K46" t="n">
-        <v>-228.93</v>
+        <v>-140.45</v>
       </c>
       <c r="L46" t="n">
-        <v>535.76</v>
+        <v>328.68</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-255.2</v>
+        <v>-140.65</v>
       </c>
       <c r="K47" t="n">
-        <v>649.01</v>
+        <v>357.7</v>
       </c>
       <c r="L47" t="n">
-        <v>697.38</v>
+        <v>384.35</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-217.54</v>
+        <v>-127</v>
       </c>
       <c r="K48" t="n">
-        <v>403.9</v>
+        <v>235.79</v>
       </c>
       <c r="L48" t="n">
-        <v>458.76</v>
+        <v>267.81</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.54</v>
+        <v>-3.77</v>
       </c>
       <c r="K49" t="n">
-        <v>-352.31</v>
+        <v>-203.13</v>
       </c>
       <c r="L49" t="n">
-        <v>352.37</v>
+        <v>203.16</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>208.45</v>
+        <v>101.26</v>
       </c>
       <c r="K50" t="n">
-        <v>489.48</v>
+        <v>237.78</v>
       </c>
       <c r="L50" t="n">
-        <v>532.02</v>
+        <v>258.44</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-665.55</v>
+        <v>-324.36</v>
       </c>
       <c r="K51" t="n">
-        <v>365.27</v>
+        <v>178.01</v>
       </c>
       <c r="L51" t="n">
-        <v>759.1900000000001</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-439.94</v>
+        <v>-215.54</v>
       </c>
       <c r="K52" t="n">
-        <v>-600.65</v>
+        <v>-294.28</v>
       </c>
       <c r="L52" t="n">
-        <v>744.53</v>
+        <v>364.77</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>352.25</v>
+        <v>162.19</v>
       </c>
       <c r="K53" t="n">
-        <v>937.15</v>
+        <v>431.51</v>
       </c>
       <c r="L53" t="n">
-        <v>1001.17</v>
+        <v>460.98</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>249.19</v>
+        <v>105.98</v>
       </c>
       <c r="K54" t="n">
-        <v>877.46</v>
+        <v>373.19</v>
       </c>
       <c r="L54" t="n">
-        <v>912.16</v>
+        <v>387.95</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>493.44</v>
+        <v>232.33</v>
       </c>
       <c r="K55" t="n">
-        <v>-44.77</v>
+        <v>-21.08</v>
       </c>
       <c r="L55" t="n">
-        <v>495.46</v>
+        <v>233.29</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-862.74</v>
+        <v>-341.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-1266.74</v>
+        <v>-500.77</v>
       </c>
       <c r="L56" t="n">
-        <v>1532.63</v>
+        <v>605.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-217.43</v>
+        <v>-85.64</v>
       </c>
       <c r="K57" t="n">
-        <v>-1248</v>
+        <v>-491.58</v>
       </c>
       <c r="L57" t="n">
-        <v>1266.8</v>
+        <v>498.98</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>1617.24</v>
+        <v>618.37</v>
       </c>
       <c r="K58" t="n">
-        <v>-301.74</v>
+        <v>-115.38</v>
       </c>
       <c r="L58" t="n">
-        <v>1645.15</v>
+        <v>629.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-534.47</v>
+        <v>-341.04</v>
       </c>
       <c r="K59" t="n">
-        <v>-186.35</v>
+        <v>-118.91</v>
       </c>
       <c r="L59" t="n">
-        <v>566.02</v>
+        <v>361.17</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-160.73</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-183.08</v>
+        <v>-105.19</v>
       </c>
       <c r="L60" t="n">
-        <v>243.62</v>
+        <v>139.98</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>314.13</v>
+        <v>183.8</v>
       </c>
       <c r="K61" t="n">
-        <v>30.98</v>
+        <v>18.13</v>
       </c>
       <c r="L61" t="n">
-        <v>315.65</v>
+        <v>184.7</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
       <c r="K62" t="n">
-        <v>445.2</v>
+        <v>244.82</v>
       </c>
       <c r="L62" t="n">
-        <v>445.2</v>
+        <v>244.82</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-507.31</v>
+        <v>-303.67</v>
       </c>
       <c r="K63" t="n">
-        <v>634.95</v>
+        <v>380.08</v>
       </c>
       <c r="L63" t="n">
-        <v>812.73</v>
+        <v>486.5</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-168.26</v>
+        <v>-94.19</v>
       </c>
       <c r="K64" t="n">
-        <v>-193.16</v>
+        <v>-108.14</v>
       </c>
       <c r="L64" t="n">
-        <v>256.17</v>
+        <v>143.41</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>8.369999999999999</v>
+        <v>4.41</v>
       </c>
       <c r="K65" t="n">
-        <v>-533.98</v>
+        <v>-281.17</v>
       </c>
       <c r="L65" t="n">
-        <v>534.05</v>
+        <v>281.21</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-544.77</v>
+        <v>-264.7</v>
       </c>
       <c r="K66" t="n">
-        <v>-753</v>
+        <v>-365.87</v>
       </c>
       <c r="L66" t="n">
-        <v>929.4</v>
+        <v>451.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-686.72</v>
+        <v>-334.95</v>
       </c>
       <c r="K67" t="n">
-        <v>461.33</v>
+        <v>225.02</v>
       </c>
       <c r="L67" t="n">
-        <v>827.29</v>
+        <v>403.52</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-520.6900000000001</v>
+        <v>-219.7</v>
       </c>
       <c r="K68" t="n">
-        <v>1444.29</v>
+        <v>609.39</v>
       </c>
       <c r="L68" t="n">
-        <v>1535.28</v>
+        <v>647.79</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-579.97</v>
+        <v>-246.71</v>
       </c>
       <c r="K69" t="n">
-        <v>900.86</v>
+        <v>383.21</v>
       </c>
       <c r="L69" t="n">
-        <v>1071.41</v>
+        <v>455.76</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>596.17</v>
+        <v>268.54</v>
       </c>
       <c r="K70" t="n">
-        <v>625.4</v>
+        <v>281.71</v>
       </c>
       <c r="L70" t="n">
-        <v>864.03</v>
+        <v>389.2</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>1267.46</v>
+        <v>492</v>
       </c>
       <c r="K71" t="n">
-        <v>-147.74</v>
+        <v>-57.35</v>
       </c>
       <c r="L71" t="n">
-        <v>1276.04</v>
+        <v>495.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-994.26</v>
+        <v>-383.47</v>
       </c>
       <c r="K72" t="n">
-        <v>-529.48</v>
+        <v>-204.21</v>
       </c>
       <c r="L72" t="n">
-        <v>1126.45</v>
+        <v>434.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-877.11</v>
+        <v>-371.31</v>
       </c>
       <c r="K73" t="n">
-        <v>332.33</v>
+        <v>140.69</v>
       </c>
       <c r="L73" t="n">
-        <v>937.96</v>
+        <v>397.06</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>8.1</v>
+        <v>4.61</v>
       </c>
       <c r="K74" t="n">
-        <v>751.96</v>
+        <v>427.52</v>
       </c>
       <c r="L74" t="n">
-        <v>752</v>
+        <v>427.55</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>574.99</v>
+        <v>345.44</v>
       </c>
       <c r="K75" t="n">
-        <v>73.37</v>
+        <v>44.08</v>
       </c>
       <c r="L75" t="n">
-        <v>579.66</v>
+        <v>348.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-398.13</v>
+        <v>-228.22</v>
       </c>
       <c r="K76" t="n">
-        <v>152.16</v>
+        <v>87.22</v>
       </c>
       <c r="L76" t="n">
-        <v>426.21</v>
+        <v>244.31</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>597.58</v>
+        <v>357.42</v>
       </c>
       <c r="K77" t="n">
-        <v>-82.31999999999999</v>
+        <v>-49.24</v>
       </c>
       <c r="L77" t="n">
-        <v>603.22</v>
+        <v>360.79</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>264.94</v>
+        <v>146.81</v>
       </c>
       <c r="K78" t="n">
-        <v>-322.76</v>
+        <v>-178.84</v>
       </c>
       <c r="L78" t="n">
-        <v>417.57</v>
+        <v>231.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-105.11</v>
+        <v>-58.98</v>
       </c>
       <c r="K79" t="n">
-        <v>-395.25</v>
+        <v>-221.79</v>
       </c>
       <c r="L79" t="n">
-        <v>408.98</v>
+        <v>229.5</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>810.47</v>
+        <v>415.21</v>
       </c>
       <c r="K80" t="n">
-        <v>82.91</v>
+        <v>42.48</v>
       </c>
       <c r="L80" t="n">
-        <v>814.7</v>
+        <v>417.38</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-141.41</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>524.25</v>
+        <v>253.6</v>
       </c>
       <c r="L81" t="n">
-        <v>542.99</v>
+        <v>262.67</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-770.9299999999999</v>
+        <v>-390.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-1000.39</v>
+        <v>-506.76</v>
       </c>
       <c r="L82" t="n">
-        <v>1262.97</v>
+        <v>639.78</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>228.47</v>
+        <v>96.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-1812.1</v>
+        <v>-769.1900000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>1826.45</v>
+        <v>775.28</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>625.23</v>
+        <v>283.41</v>
       </c>
       <c r="K84" t="n">
-        <v>670.95</v>
+        <v>304.14</v>
       </c>
       <c r="L84" t="n">
-        <v>917.11</v>
+        <v>415.72</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-1453.71</v>
+        <v>-621.5700000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>-139.26</v>
+        <v>-59.54</v>
       </c>
       <c r="L85" t="n">
-        <v>1460.37</v>
+        <v>624.41</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-1235.31</v>
+        <v>-474.7</v>
       </c>
       <c r="K86" t="n">
-        <v>-983.88</v>
+        <v>-378.08</v>
       </c>
       <c r="L86" t="n">
-        <v>1579.25</v>
+        <v>606.86</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>835.42</v>
+        <v>319.48</v>
       </c>
       <c r="K87" t="n">
-        <v>1632.43</v>
+        <v>624.28</v>
       </c>
       <c r="L87" t="n">
-        <v>1833.78</v>
+        <v>701.28</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>1260.44</v>
+        <v>483.32</v>
       </c>
       <c r="K88" t="n">
-        <v>1537.16</v>
+        <v>589.4299999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>1987.85</v>
+        <v>762.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-166.31</v>
+        <v>-175.85</v>
       </c>
       <c r="K14" t="n">
-        <v>-23.94</v>
+        <v>-25.31</v>
       </c>
       <c r="L14" t="n">
-        <v>168.03</v>
+        <v>177.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>201.69</v>
+        <v>216.28</v>
       </c>
       <c r="K15" t="n">
-        <v>157.79</v>
+        <v>169.21</v>
       </c>
       <c r="L15" t="n">
-        <v>256.08</v>
+        <v>274.61</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-134.88</v>
+        <v>-146.84</v>
       </c>
       <c r="K16" t="n">
-        <v>60.34</v>
+        <v>65.69</v>
       </c>
       <c r="L16" t="n">
-        <v>147.77</v>
+        <v>160.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-59.15</v>
+        <v>-64.41</v>
       </c>
       <c r="K17" t="n">
-        <v>-219.73</v>
+        <v>-239.27</v>
       </c>
       <c r="L17" t="n">
-        <v>227.55</v>
+        <v>247.79</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>289.86</v>
+        <v>311.88</v>
       </c>
       <c r="K18" t="n">
-        <v>-133.3</v>
+        <v>-143.42</v>
       </c>
       <c r="L18" t="n">
-        <v>319.04</v>
+        <v>343.27</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>172.13</v>
+        <v>184.42</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.23</v>
+        <v>-2.38</v>
       </c>
       <c r="L19" t="n">
-        <v>172.14</v>
+        <v>184.43</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-469.47</v>
+        <v>-525.65</v>
       </c>
       <c r="K20" t="n">
-        <v>-324.85</v>
+        <v>-363.73</v>
       </c>
       <c r="L20" t="n">
-        <v>570.9</v>
+        <v>639.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>359.16</v>
+        <v>406.38</v>
       </c>
       <c r="K21" t="n">
-        <v>418.27</v>
+        <v>473.26</v>
       </c>
       <c r="L21" t="n">
-        <v>551.3099999999999</v>
+        <v>623.8</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-202.29</v>
+        <v>-225.72</v>
       </c>
       <c r="K22" t="n">
-        <v>-281.85</v>
+        <v>-314.48</v>
       </c>
       <c r="L22" t="n">
-        <v>346.93</v>
+        <v>387.1</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>175.1</v>
+        <v>200.92</v>
       </c>
       <c r="K23" t="n">
-        <v>-401.11</v>
+        <v>-460.27</v>
       </c>
       <c r="L23" t="n">
-        <v>437.66</v>
+        <v>502.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-69.22</v>
+        <v>-79.47</v>
       </c>
       <c r="K24" t="n">
-        <v>-321.95</v>
+        <v>-369.63</v>
       </c>
       <c r="L24" t="n">
-        <v>329.31</v>
+        <v>378.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>425.21</v>
+        <v>481.41</v>
       </c>
       <c r="K25" t="n">
-        <v>-106.4</v>
+        <v>-120.46</v>
       </c>
       <c r="L25" t="n">
-        <v>438.32</v>
+        <v>496.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>327.51</v>
+        <v>385.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-308.84</v>
+        <v>-363.24</v>
       </c>
       <c r="L26" t="n">
-        <v>450.16</v>
+        <v>529.46</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>162.88</v>
+        <v>190.62</v>
       </c>
       <c r="K27" t="n">
-        <v>-465.96</v>
+        <v>-545.3</v>
       </c>
       <c r="L27" t="n">
-        <v>493.61</v>
+        <v>577.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>343.7</v>
+        <v>403.43</v>
       </c>
       <c r="K28" t="n">
-        <v>-167.55</v>
+        <v>-196.67</v>
       </c>
       <c r="L28" t="n">
-        <v>382.37</v>
+        <v>448.82</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>171.27</v>
+        <v>186.19</v>
       </c>
       <c r="K29" t="n">
-        <v>-101.64</v>
+        <v>-110.49</v>
       </c>
       <c r="L29" t="n">
-        <v>199.16</v>
+        <v>216.51</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-194.39</v>
+        <v>-213.23</v>
       </c>
       <c r="K30" t="n">
-        <v>-307.79</v>
+        <v>-337.62</v>
       </c>
       <c r="L30" t="n">
-        <v>364.03</v>
+        <v>399.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-52.35</v>
+        <v>-56.17</v>
       </c>
       <c r="K31" t="n">
-        <v>212.51</v>
+        <v>227.99</v>
       </c>
       <c r="L31" t="n">
-        <v>218.86</v>
+        <v>234.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-203.55</v>
+        <v>-220.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-112.88</v>
+        <v>-122.52</v>
       </c>
       <c r="L32" t="n">
-        <v>232.76</v>
+        <v>252.64</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>70.18000000000001</v>
+        <v>75.95</v>
       </c>
       <c r="K33" t="n">
-        <v>-185.12</v>
+        <v>-200.34</v>
       </c>
       <c r="L33" t="n">
-        <v>197.97</v>
+        <v>214.26</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-169.16</v>
+        <v>-181.55</v>
       </c>
       <c r="K34" t="n">
-        <v>43.44</v>
+        <v>46.63</v>
       </c>
       <c r="L34" t="n">
-        <v>174.65</v>
+        <v>187.44</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-248.17</v>
+        <v>-280.49</v>
       </c>
       <c r="K35" t="n">
-        <v>198.39</v>
+        <v>224.23</v>
       </c>
       <c r="L35" t="n">
-        <v>317.72</v>
+        <v>359.1</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-148.67</v>
+        <v>-165.35</v>
       </c>
       <c r="K36" t="n">
-        <v>-213.3</v>
+        <v>-237.21</v>
       </c>
       <c r="L36" t="n">
-        <v>260</v>
+        <v>289.15</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-165.03</v>
+        <v>-182.95</v>
       </c>
       <c r="K37" t="n">
-        <v>309.13</v>
+        <v>342.7</v>
       </c>
       <c r="L37" t="n">
-        <v>350.43</v>
+        <v>388.47</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>602.11</v>
+        <v>692.86</v>
       </c>
       <c r="K38" t="n">
-        <v>356.65</v>
+        <v>410.41</v>
       </c>
       <c r="L38" t="n">
-        <v>699.8099999999999</v>
+        <v>805.29</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>232.18</v>
+        <v>266.81</v>
       </c>
       <c r="K39" t="n">
-        <v>-391.47</v>
+        <v>-449.86</v>
       </c>
       <c r="L39" t="n">
-        <v>455.14</v>
+        <v>523.03</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>170.47</v>
+        <v>195.42</v>
       </c>
       <c r="K40" t="n">
-        <v>-492.4</v>
+        <v>-564.5</v>
       </c>
       <c r="L40" t="n">
-        <v>521.08</v>
+        <v>597.37</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>322.04</v>
+        <v>383.11</v>
       </c>
       <c r="K41" t="n">
-        <v>-620.09</v>
+        <v>-737.7</v>
       </c>
       <c r="L41" t="n">
-        <v>698.73</v>
+        <v>831.25</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>21.12</v>
+        <v>25.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-364.52</v>
+        <v>-432.55</v>
       </c>
       <c r="L42" t="n">
-        <v>365.13</v>
+        <v>433.28</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>207.43</v>
+        <v>248.47</v>
       </c>
       <c r="K43" t="n">
-        <v>432.39</v>
+        <v>517.92</v>
       </c>
       <c r="L43" t="n">
-        <v>479.57</v>
+        <v>574.4400000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.69</v>
+        <v>-39.9</v>
       </c>
       <c r="K44" t="n">
-        <v>-261.04</v>
+        <v>-283.93</v>
       </c>
       <c r="L44" t="n">
-        <v>263.6</v>
+        <v>286.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-207.7</v>
+        <v>-226.65</v>
       </c>
       <c r="K45" t="n">
-        <v>-123.5</v>
+        <v>-134.77</v>
       </c>
       <c r="L45" t="n">
-        <v>241.64</v>
+        <v>263.7</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-297.16</v>
+        <v>-319.66</v>
       </c>
       <c r="K46" t="n">
-        <v>-140.45</v>
+        <v>-151.08</v>
       </c>
       <c r="L46" t="n">
-        <v>328.68</v>
+        <v>353.57</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-140.65</v>
+        <v>-154.61</v>
       </c>
       <c r="K47" t="n">
-        <v>357.7</v>
+        <v>393.2</v>
       </c>
       <c r="L47" t="n">
-        <v>384.35</v>
+        <v>422.51</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-127</v>
+        <v>-137.16</v>
       </c>
       <c r="K48" t="n">
-        <v>235.79</v>
+        <v>254.66</v>
       </c>
       <c r="L48" t="n">
-        <v>267.81</v>
+        <v>289.24</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.77</v>
+        <v>-4.11</v>
       </c>
       <c r="K49" t="n">
-        <v>-203.13</v>
+        <v>-221.49</v>
       </c>
       <c r="L49" t="n">
-        <v>203.16</v>
+        <v>221.53</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>101.26</v>
+        <v>114.54</v>
       </c>
       <c r="K50" t="n">
-        <v>237.78</v>
+        <v>268.97</v>
       </c>
       <c r="L50" t="n">
-        <v>258.44</v>
+        <v>292.34</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-324.36</v>
+        <v>-363.06</v>
       </c>
       <c r="K51" t="n">
-        <v>178.01</v>
+        <v>199.25</v>
       </c>
       <c r="L51" t="n">
-        <v>370</v>
+        <v>414.14</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-215.54</v>
+        <v>-244.6</v>
       </c>
       <c r="K52" t="n">
-        <v>-294.28</v>
+        <v>-333.96</v>
       </c>
       <c r="L52" t="n">
-        <v>364.77</v>
+        <v>413.96</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>162.19</v>
+        <v>183.09</v>
       </c>
       <c r="K53" t="n">
-        <v>431.51</v>
+        <v>487.11</v>
       </c>
       <c r="L53" t="n">
-        <v>460.98</v>
+        <v>520.38</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>105.98</v>
+        <v>122.2</v>
       </c>
       <c r="K54" t="n">
-        <v>373.19</v>
+        <v>430.3</v>
       </c>
       <c r="L54" t="n">
-        <v>387.95</v>
+        <v>447.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>232.33</v>
+        <v>267.17</v>
       </c>
       <c r="K55" t="n">
-        <v>-21.08</v>
+        <v>-24.24</v>
       </c>
       <c r="L55" t="n">
-        <v>233.29</v>
+        <v>268.27</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-341.06</v>
+        <v>-406.85</v>
       </c>
       <c r="K56" t="n">
-        <v>-500.77</v>
+        <v>-597.36</v>
       </c>
       <c r="L56" t="n">
-        <v>605.88</v>
+        <v>722.75</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-85.64</v>
+        <v>-101.6</v>
       </c>
       <c r="K57" t="n">
-        <v>-491.58</v>
+        <v>-583.1900000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>498.98</v>
+        <v>591.97</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>618.37</v>
+        <v>730.74</v>
       </c>
       <c r="K58" t="n">
-        <v>-115.38</v>
+        <v>-136.34</v>
       </c>
       <c r="L58" t="n">
-        <v>629.05</v>
+        <v>743.35</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-341.04</v>
+        <v>-363.08</v>
       </c>
       <c r="K59" t="n">
-        <v>-118.91</v>
+        <v>-126.6</v>
       </c>
       <c r="L59" t="n">
-        <v>361.17</v>
+        <v>384.52</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-92.34999999999999</v>
+        <v>-100.11</v>
       </c>
       <c r="K60" t="n">
-        <v>-105.19</v>
+        <v>-114.03</v>
       </c>
       <c r="L60" t="n">
-        <v>139.98</v>
+        <v>151.74</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>183.8</v>
+        <v>199.19</v>
       </c>
       <c r="K61" t="n">
-        <v>18.13</v>
+        <v>19.65</v>
       </c>
       <c r="L61" t="n">
-        <v>184.7</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="K62" t="n">
-        <v>244.82</v>
+        <v>269.51</v>
       </c>
       <c r="L62" t="n">
-        <v>244.82</v>
+        <v>269.51</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-303.67</v>
+        <v>-327.51</v>
       </c>
       <c r="K63" t="n">
-        <v>380.08</v>
+        <v>409.92</v>
       </c>
       <c r="L63" t="n">
-        <v>486.5</v>
+        <v>524.6900000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-94.19</v>
+        <v>-104.28</v>
       </c>
       <c r="K64" t="n">
-        <v>-108.14</v>
+        <v>-119.71</v>
       </c>
       <c r="L64" t="n">
-        <v>143.41</v>
+        <v>158.76</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>4.41</v>
+        <v>4.82</v>
       </c>
       <c r="K65" t="n">
-        <v>-281.17</v>
+        <v>-307.35</v>
       </c>
       <c r="L65" t="n">
-        <v>281.21</v>
+        <v>307.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-264.7</v>
+        <v>-298.13</v>
       </c>
       <c r="K66" t="n">
-        <v>-365.87</v>
+        <v>-412.08</v>
       </c>
       <c r="L66" t="n">
-        <v>451.58</v>
+        <v>508.61</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-334.95</v>
+        <v>-374.31</v>
       </c>
       <c r="K67" t="n">
-        <v>225.02</v>
+        <v>251.46</v>
       </c>
       <c r="L67" t="n">
-        <v>403.52</v>
+        <v>450.93</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-219.7</v>
+        <v>-254.38</v>
       </c>
       <c r="K68" t="n">
-        <v>609.39</v>
+        <v>705.59</v>
       </c>
       <c r="L68" t="n">
-        <v>647.79</v>
+        <v>750.04</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-246.71</v>
+        <v>-283.36</v>
       </c>
       <c r="K69" t="n">
-        <v>383.21</v>
+        <v>440.13</v>
       </c>
       <c r="L69" t="n">
-        <v>455.76</v>
+        <v>523.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>268.54</v>
+        <v>306.28</v>
       </c>
       <c r="K70" t="n">
-        <v>281.71</v>
+        <v>321.3</v>
       </c>
       <c r="L70" t="n">
-        <v>389.2</v>
+        <v>443.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>492</v>
+        <v>577.2</v>
       </c>
       <c r="K71" t="n">
-        <v>-57.35</v>
+        <v>-67.28</v>
       </c>
       <c r="L71" t="n">
-        <v>495.33</v>
+        <v>581.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-383.47</v>
+        <v>-451.83</v>
       </c>
       <c r="K72" t="n">
-        <v>-204.21</v>
+        <v>-240.61</v>
       </c>
       <c r="L72" t="n">
-        <v>434.45</v>
+        <v>511.9</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-371.31</v>
+        <v>-440.87</v>
       </c>
       <c r="K73" t="n">
-        <v>140.69</v>
+        <v>167.04</v>
       </c>
       <c r="L73" t="n">
-        <v>397.06</v>
+        <v>471.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>4.61</v>
+        <v>5.11</v>
       </c>
       <c r="K74" t="n">
-        <v>427.52</v>
+        <v>474.03</v>
       </c>
       <c r="L74" t="n">
-        <v>427.55</v>
+        <v>474.05</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>345.44</v>
+        <v>374.61</v>
       </c>
       <c r="K75" t="n">
-        <v>44.08</v>
+        <v>47.8</v>
       </c>
       <c r="L75" t="n">
-        <v>348.25</v>
+        <v>377.65</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-228.22</v>
+        <v>-248.44</v>
       </c>
       <c r="K76" t="n">
-        <v>87.22</v>
+        <v>94.95</v>
       </c>
       <c r="L76" t="n">
-        <v>244.31</v>
+        <v>265.97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>357.42</v>
+        <v>387.31</v>
       </c>
       <c r="K77" t="n">
-        <v>-49.24</v>
+        <v>-53.36</v>
       </c>
       <c r="L77" t="n">
-        <v>360.79</v>
+        <v>390.97</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>146.81</v>
+        <v>159.95</v>
       </c>
       <c r="K78" t="n">
-        <v>-178.84</v>
+        <v>-194.85</v>
       </c>
       <c r="L78" t="n">
-        <v>231.38</v>
+        <v>252.1</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-58.98</v>
+        <v>-64.16</v>
       </c>
       <c r="K79" t="n">
-        <v>-221.79</v>
+        <v>-241.27</v>
       </c>
       <c r="L79" t="n">
-        <v>229.5</v>
+        <v>249.65</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>415.21</v>
+        <v>464.09</v>
       </c>
       <c r="K80" t="n">
-        <v>42.48</v>
+        <v>47.48</v>
       </c>
       <c r="L80" t="n">
-        <v>417.38</v>
+        <v>466.51</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-68.40000000000001</v>
+        <v>-76.31999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>253.6</v>
+        <v>282.96</v>
       </c>
       <c r="L81" t="n">
-        <v>262.67</v>
+        <v>293.07</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-390.52</v>
+        <v>-435.06</v>
       </c>
       <c r="K82" t="n">
-        <v>-506.76</v>
+        <v>-564.5599999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>639.78</v>
+        <v>712.74</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>96.98</v>
+        <v>112.23</v>
       </c>
       <c r="K83" t="n">
-        <v>-769.1900000000001</v>
+        <v>-890.17</v>
       </c>
       <c r="L83" t="n">
-        <v>775.28</v>
+        <v>897.22</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>283.41</v>
+        <v>325.59</v>
       </c>
       <c r="K84" t="n">
-        <v>304.14</v>
+        <v>349.4</v>
       </c>
       <c r="L84" t="n">
-        <v>415.72</v>
+        <v>477.59</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-621.5700000000001</v>
+        <v>-718.22</v>
       </c>
       <c r="K85" t="n">
-        <v>-59.54</v>
+        <v>-68.8</v>
       </c>
       <c r="L85" t="n">
-        <v>624.41</v>
+        <v>721.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-474.7</v>
+        <v>-554.1799999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>-378.08</v>
+        <v>-441.38</v>
       </c>
       <c r="L86" t="n">
-        <v>606.86</v>
+        <v>708.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>319.48</v>
+        <v>374.27</v>
       </c>
       <c r="K87" t="n">
-        <v>624.28</v>
+        <v>731.34</v>
       </c>
       <c r="L87" t="n">
-        <v>701.28</v>
+        <v>821.55</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>483.32</v>
+        <v>563.34</v>
       </c>
       <c r="K88" t="n">
-        <v>589.4299999999999</v>
+        <v>687.02</v>
       </c>
       <c r="L88" t="n">
-        <v>762.24</v>
+        <v>888.45</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-175.85</v>
+        <v>-72.06</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.31</v>
+        <v>-10.37</v>
       </c>
       <c r="L14" t="n">
-        <v>177.66</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>216.28</v>
+        <v>86.63</v>
       </c>
       <c r="K15" t="n">
-        <v>169.21</v>
+        <v>67.78</v>
       </c>
       <c r="L15" t="n">
-        <v>274.61</v>
+        <v>109.99</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-146.84</v>
+        <v>-59.43</v>
       </c>
       <c r="K16" t="n">
-        <v>65.69</v>
+        <v>26.59</v>
       </c>
       <c r="L16" t="n">
-        <v>160.87</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-64.41</v>
+        <v>-28.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-239.27</v>
+        <v>-104.97</v>
       </c>
       <c r="L17" t="n">
-        <v>247.79</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>311.88</v>
+        <v>131.22</v>
       </c>
       <c r="K18" t="n">
-        <v>-143.42</v>
+        <v>-60.34</v>
       </c>
       <c r="L18" t="n">
-        <v>343.27</v>
+        <v>144.43</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>184.42</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.38</v>
+        <v>-1.01</v>
       </c>
       <c r="L19" t="n">
-        <v>184.43</v>
+        <v>78.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-525.65</v>
+        <v>-251.78</v>
       </c>
       <c r="K20" t="n">
-        <v>-363.73</v>
+        <v>-174.22</v>
       </c>
       <c r="L20" t="n">
-        <v>639.23</v>
+        <v>306.18</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>406.38</v>
+        <v>194.61</v>
       </c>
       <c r="K21" t="n">
-        <v>473.26</v>
+        <v>226.64</v>
       </c>
       <c r="L21" t="n">
-        <v>623.8</v>
+        <v>298.72</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-225.72</v>
+        <v>-107.85</v>
       </c>
       <c r="K22" t="n">
-        <v>-314.48</v>
+        <v>-150.27</v>
       </c>
       <c r="L22" t="n">
-        <v>387.1</v>
+        <v>184.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>200.92</v>
+        <v>96.56</v>
       </c>
       <c r="K23" t="n">
-        <v>-460.27</v>
+        <v>-221.19</v>
       </c>
       <c r="L23" t="n">
-        <v>502.22</v>
+        <v>241.34</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-79.47</v>
+        <v>-35.01</v>
       </c>
       <c r="K24" t="n">
-        <v>-369.63</v>
+        <v>-162.86</v>
       </c>
       <c r="L24" t="n">
-        <v>378.08</v>
+        <v>166.58</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>481.41</v>
+        <v>224.63</v>
       </c>
       <c r="K25" t="n">
-        <v>-120.46</v>
+        <v>-56.21</v>
       </c>
       <c r="L25" t="n">
-        <v>496.25</v>
+        <v>231.55</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>385.2</v>
+        <v>209.91</v>
       </c>
       <c r="K26" t="n">
-        <v>-363.24</v>
+        <v>-197.94</v>
       </c>
       <c r="L26" t="n">
-        <v>529.46</v>
+        <v>288.51</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>190.62</v>
+        <v>102.27</v>
       </c>
       <c r="K27" t="n">
-        <v>-545.3</v>
+        <v>-292.56</v>
       </c>
       <c r="L27" t="n">
-        <v>577.66</v>
+        <v>309.92</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>403.43</v>
+        <v>220.23</v>
       </c>
       <c r="K28" t="n">
-        <v>-196.67</v>
+        <v>-107.36</v>
       </c>
       <c r="L28" t="n">
-        <v>448.82</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>186.19</v>
+        <v>74.39</v>
       </c>
       <c r="K29" t="n">
-        <v>-110.49</v>
+        <v>-44.15</v>
       </c>
       <c r="L29" t="n">
-        <v>216.51</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-213.23</v>
+        <v>-86.18000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-337.62</v>
+        <v>-136.46</v>
       </c>
       <c r="L30" t="n">
-        <v>399.31</v>
+        <v>161.4</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-56.17</v>
+        <v>-22.42</v>
       </c>
       <c r="K31" t="n">
-        <v>227.99</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>234.81</v>
+        <v>93.73</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-220.95</v>
+        <v>-96.37</v>
       </c>
       <c r="K32" t="n">
-        <v>-122.52</v>
+        <v>-53.44</v>
       </c>
       <c r="L32" t="n">
-        <v>252.64</v>
+        <v>110.19</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>75.95</v>
+        <v>33.05</v>
       </c>
       <c r="K33" t="n">
-        <v>-200.34</v>
+        <v>-87.17</v>
       </c>
       <c r="L33" t="n">
-        <v>214.26</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-181.55</v>
+        <v>-78.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>46.63</v>
+        <v>20.29</v>
       </c>
       <c r="L34" t="n">
-        <v>187.44</v>
+        <v>81.56</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-280.49</v>
+        <v>-134.22</v>
       </c>
       <c r="K35" t="n">
-        <v>224.23</v>
+        <v>107.3</v>
       </c>
       <c r="L35" t="n">
-        <v>359.1</v>
+        <v>171.84</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-165.35</v>
+        <v>-78.98999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-237.21</v>
+        <v>-113.32</v>
       </c>
       <c r="L36" t="n">
-        <v>289.15</v>
+        <v>138.13</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-182.95</v>
+        <v>-87.54000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>342.7</v>
+        <v>163.98</v>
       </c>
       <c r="L37" t="n">
-        <v>388.47</v>
+        <v>185.89</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>692.86</v>
+        <v>316.3</v>
       </c>
       <c r="K38" t="n">
-        <v>410.41</v>
+        <v>187.36</v>
       </c>
       <c r="L38" t="n">
-        <v>805.29</v>
+        <v>367.63</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>266.81</v>
+        <v>122.21</v>
       </c>
       <c r="K39" t="n">
-        <v>-449.86</v>
+        <v>-206.06</v>
       </c>
       <c r="L39" t="n">
-        <v>523.03</v>
+        <v>239.57</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>195.42</v>
+        <v>89.81</v>
       </c>
       <c r="K40" t="n">
-        <v>-564.5</v>
+        <v>-259.41</v>
       </c>
       <c r="L40" t="n">
-        <v>597.37</v>
+        <v>274.52</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>383.11</v>
+        <v>205.79</v>
       </c>
       <c r="K41" t="n">
-        <v>-737.7</v>
+        <v>-396.26</v>
       </c>
       <c r="L41" t="n">
-        <v>831.25</v>
+        <v>446.51</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>25.06</v>
+        <v>13.46</v>
       </c>
       <c r="K42" t="n">
-        <v>-432.55</v>
+        <v>-232.42</v>
       </c>
       <c r="L42" t="n">
-        <v>433.28</v>
+        <v>232.81</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>248.47</v>
+        <v>133.01</v>
       </c>
       <c r="K43" t="n">
-        <v>517.92</v>
+        <v>277.27</v>
       </c>
       <c r="L43" t="n">
-        <v>574.4400000000001</v>
+        <v>307.52</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-39.9</v>
+        <v>-16.14</v>
       </c>
       <c r="K44" t="n">
-        <v>-283.93</v>
+        <v>-114.87</v>
       </c>
       <c r="L44" t="n">
-        <v>286.72</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-226.65</v>
+        <v>-91.79000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-134.77</v>
+        <v>-54.58</v>
       </c>
       <c r="L45" t="n">
-        <v>263.7</v>
+        <v>106.79</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-319.66</v>
+        <v>-130.67</v>
       </c>
       <c r="K46" t="n">
-        <v>-151.08</v>
+        <v>-61.76</v>
       </c>
       <c r="L46" t="n">
-        <v>353.57</v>
+        <v>144.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-154.61</v>
+        <v>-67.25</v>
       </c>
       <c r="K47" t="n">
-        <v>393.2</v>
+        <v>171.04</v>
       </c>
       <c r="L47" t="n">
-        <v>422.51</v>
+        <v>183.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-137.16</v>
+        <v>-58.74</v>
       </c>
       <c r="K48" t="n">
-        <v>254.66</v>
+        <v>109.07</v>
       </c>
       <c r="L48" t="n">
-        <v>289.24</v>
+        <v>123.88</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.11</v>
+        <v>-1.79</v>
       </c>
       <c r="K49" t="n">
-        <v>-221.49</v>
+        <v>-96.61</v>
       </c>
       <c r="L49" t="n">
-        <v>221.53</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>114.54</v>
+        <v>54.78</v>
       </c>
       <c r="K50" t="n">
-        <v>268.97</v>
+        <v>128.63</v>
       </c>
       <c r="L50" t="n">
-        <v>292.34</v>
+        <v>139.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-363.06</v>
+        <v>-173.98</v>
       </c>
       <c r="K51" t="n">
-        <v>199.25</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>414.14</v>
+        <v>198.46</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-244.6</v>
+        <v>-116.87</v>
       </c>
       <c r="K52" t="n">
-        <v>-333.96</v>
+        <v>-159.57</v>
       </c>
       <c r="L52" t="n">
-        <v>413.96</v>
+        <v>197.79</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>183.09</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>487.11</v>
+        <v>238.1</v>
       </c>
       <c r="L53" t="n">
-        <v>520.38</v>
+        <v>254.36</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>122.2</v>
+        <v>57.2</v>
       </c>
       <c r="K54" t="n">
-        <v>430.3</v>
+        <v>201.43</v>
       </c>
       <c r="L54" t="n">
-        <v>447.31</v>
+        <v>209.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>267.17</v>
+        <v>117.13</v>
       </c>
       <c r="K55" t="n">
-        <v>-24.24</v>
+        <v>-10.63</v>
       </c>
       <c r="L55" t="n">
-        <v>268.27</v>
+        <v>117.61</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-406.85</v>
+        <v>-217.32</v>
       </c>
       <c r="K56" t="n">
-        <v>-597.36</v>
+        <v>-319.09</v>
       </c>
       <c r="L56" t="n">
-        <v>722.75</v>
+        <v>386.06</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-101.6</v>
+        <v>-54.51</v>
       </c>
       <c r="K57" t="n">
-        <v>-583.1900000000001</v>
+        <v>-312.88</v>
       </c>
       <c r="L57" t="n">
-        <v>591.97</v>
+        <v>317.6</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>730.74</v>
+        <v>406.58</v>
       </c>
       <c r="K58" t="n">
-        <v>-136.34</v>
+        <v>-75.86</v>
       </c>
       <c r="L58" t="n">
-        <v>743.35</v>
+        <v>413.59</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-363.08</v>
+        <v>-146.97</v>
       </c>
       <c r="K59" t="n">
-        <v>-126.6</v>
+        <v>-51.24</v>
       </c>
       <c r="L59" t="n">
-        <v>384.52</v>
+        <v>155.64</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-100.11</v>
+        <v>-40.71</v>
       </c>
       <c r="K60" t="n">
-        <v>-114.03</v>
+        <v>-46.37</v>
       </c>
       <c r="L60" t="n">
-        <v>151.74</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>199.19</v>
+        <v>79.84</v>
       </c>
       <c r="K61" t="n">
-        <v>19.65</v>
+        <v>7.87</v>
       </c>
       <c r="L61" t="n">
-        <v>200.16</v>
+        <v>80.23</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.2</v>
+        <v>-0.09</v>
       </c>
       <c r="K62" t="n">
-        <v>269.51</v>
+        <v>117.61</v>
       </c>
       <c r="L62" t="n">
-        <v>269.51</v>
+        <v>117.61</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-327.51</v>
+        <v>-145.89</v>
       </c>
       <c r="K63" t="n">
-        <v>409.92</v>
+        <v>182.6</v>
       </c>
       <c r="L63" t="n">
-        <v>524.6900000000001</v>
+        <v>233.73</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-104.28</v>
+        <v>-25.8</v>
       </c>
       <c r="K64" t="n">
-        <v>-119.71</v>
+        <v>-29.62</v>
       </c>
       <c r="L64" t="n">
-        <v>158.76</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>4.82</v>
+        <v>2.31</v>
       </c>
       <c r="K65" t="n">
-        <v>-307.35</v>
+        <v>-147.27</v>
       </c>
       <c r="L65" t="n">
-        <v>307.39</v>
+        <v>147.29</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-298.13</v>
+        <v>-142.57</v>
       </c>
       <c r="K66" t="n">
-        <v>-412.08</v>
+        <v>-197.06</v>
       </c>
       <c r="L66" t="n">
-        <v>508.61</v>
+        <v>243.22</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-374.31</v>
+        <v>-179.36</v>
       </c>
       <c r="K67" t="n">
-        <v>251.46</v>
+        <v>120.49</v>
       </c>
       <c r="L67" t="n">
-        <v>450.93</v>
+        <v>216.07</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-254.38</v>
+        <v>-121.18</v>
       </c>
       <c r="K68" t="n">
-        <v>705.59</v>
+        <v>336.14</v>
       </c>
       <c r="L68" t="n">
-        <v>750.04</v>
+        <v>357.32</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-283.36</v>
+        <v>-132.59</v>
       </c>
       <c r="K69" t="n">
-        <v>440.13</v>
+        <v>205.95</v>
       </c>
       <c r="L69" t="n">
-        <v>523.46</v>
+        <v>244.94</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>306.28</v>
+        <v>140.09</v>
       </c>
       <c r="K70" t="n">
-        <v>321.3</v>
+        <v>146.96</v>
       </c>
       <c r="L70" t="n">
-        <v>443.89</v>
+        <v>203.03</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>577.2</v>
+        <v>315.23</v>
       </c>
       <c r="K71" t="n">
-        <v>-67.28</v>
+        <v>-36.74</v>
       </c>
       <c r="L71" t="n">
-        <v>581.11</v>
+        <v>317.37</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-451.83</v>
+        <v>-248.73</v>
       </c>
       <c r="K72" t="n">
-        <v>-240.61</v>
+        <v>-132.46</v>
       </c>
       <c r="L72" t="n">
-        <v>511.9</v>
+        <v>281.8</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-440.87</v>
+        <v>-236.6</v>
       </c>
       <c r="K73" t="n">
-        <v>167.04</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>471.46</v>
+        <v>253.02</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>5.11</v>
+        <v>2.09</v>
       </c>
       <c r="K74" t="n">
-        <v>474.03</v>
+        <v>194.34</v>
       </c>
       <c r="L74" t="n">
-        <v>474.05</v>
+        <v>194.35</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>374.61</v>
+        <v>152.6</v>
       </c>
       <c r="K75" t="n">
-        <v>47.8</v>
+        <v>19.47</v>
       </c>
       <c r="L75" t="n">
-        <v>377.65</v>
+        <v>153.84</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-248.44</v>
+        <v>-101.21</v>
       </c>
       <c r="K76" t="n">
-        <v>94.95</v>
+        <v>38.68</v>
       </c>
       <c r="L76" t="n">
-        <v>265.97</v>
+        <v>108.35</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>387.31</v>
+        <v>172.73</v>
       </c>
       <c r="K77" t="n">
-        <v>-53.36</v>
+        <v>-23.8</v>
       </c>
       <c r="L77" t="n">
-        <v>390.97</v>
+        <v>174.37</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>159.95</v>
+        <v>69.03</v>
       </c>
       <c r="K78" t="n">
-        <v>-194.85</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>252.1</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-64.16</v>
+        <v>-28.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-241.27</v>
+        <v>-105.7</v>
       </c>
       <c r="L79" t="n">
-        <v>249.65</v>
+        <v>109.37</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>464.09</v>
+        <v>222.39</v>
       </c>
       <c r="K80" t="n">
-        <v>47.48</v>
+        <v>22.75</v>
       </c>
       <c r="L80" t="n">
-        <v>466.51</v>
+        <v>223.55</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-76.31999999999999</v>
+        <v>-36.51</v>
       </c>
       <c r="K81" t="n">
-        <v>282.96</v>
+        <v>135.38</v>
       </c>
       <c r="L81" t="n">
-        <v>293.07</v>
+        <v>140.21</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-435.06</v>
+        <v>-208.17</v>
       </c>
       <c r="K82" t="n">
-        <v>-564.5599999999999</v>
+        <v>-270.13</v>
       </c>
       <c r="L82" t="n">
-        <v>712.74</v>
+        <v>341.03</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>112.23</v>
+        <v>52.77</v>
       </c>
       <c r="K83" t="n">
-        <v>-890.17</v>
+        <v>-418.51</v>
       </c>
       <c r="L83" t="n">
-        <v>897.22</v>
+        <v>421.83</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>325.59</v>
+        <v>155.33</v>
       </c>
       <c r="K84" t="n">
-        <v>349.4</v>
+        <v>166.68</v>
       </c>
       <c r="L84" t="n">
-        <v>477.59</v>
+        <v>227.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-718.22</v>
+        <v>-332.29</v>
       </c>
       <c r="K85" t="n">
-        <v>-68.8</v>
+        <v>-31.83</v>
       </c>
       <c r="L85" t="n">
-        <v>721.5</v>
+        <v>333.81</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-554.1799999999999</v>
+        <v>-306.45</v>
       </c>
       <c r="K86" t="n">
-        <v>-441.38</v>
+        <v>-244.07</v>
       </c>
       <c r="L86" t="n">
-        <v>708.48</v>
+        <v>391.77</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>374.27</v>
+        <v>208.2</v>
       </c>
       <c r="K87" t="n">
-        <v>731.34</v>
+        <v>406.83</v>
       </c>
       <c r="L87" t="n">
-        <v>821.55</v>
+        <v>457.01</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>563.34</v>
+        <v>312.34</v>
       </c>
       <c r="K88" t="n">
-        <v>687.02</v>
+        <v>380.91</v>
       </c>
       <c r="L88" t="n">
-        <v>888.45</v>
+        <v>492.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.06</v>
+        <v>-69.73</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.37</v>
+        <v>-10.04</v>
       </c>
       <c r="L14" t="n">
-        <v>72.8</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>86.63</v>
+        <v>74.62</v>
       </c>
       <c r="K15" t="n">
-        <v>67.78</v>
+        <v>58.38</v>
       </c>
       <c r="L15" t="n">
-        <v>109.99</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-59.43</v>
+        <v>-51.06</v>
       </c>
       <c r="K16" t="n">
-        <v>26.59</v>
+        <v>22.84</v>
       </c>
       <c r="L16" t="n">
-        <v>65.09999999999999</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-28.26</v>
+        <v>-26.9</v>
       </c>
       <c r="K17" t="n">
-        <v>-104.97</v>
+        <v>-99.94</v>
       </c>
       <c r="L17" t="n">
-        <v>108.7</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>131.22</v>
+        <v>113.75</v>
       </c>
       <c r="K18" t="n">
-        <v>-60.34</v>
+        <v>-52.31</v>
       </c>
       <c r="L18" t="n">
-        <v>144.43</v>
+        <v>125.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>78.34999999999999</v>
+        <v>70.53</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.01</v>
+        <v>-0.91</v>
       </c>
       <c r="L19" t="n">
-        <v>78.36</v>
+        <v>70.54000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-251.78</v>
+        <v>-231.86</v>
       </c>
       <c r="K20" t="n">
-        <v>-174.22</v>
+        <v>-160.44</v>
       </c>
       <c r="L20" t="n">
-        <v>306.18</v>
+        <v>281.96</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>194.61</v>
+        <v>179.97</v>
       </c>
       <c r="K21" t="n">
-        <v>226.64</v>
+        <v>209.6</v>
       </c>
       <c r="L21" t="n">
-        <v>298.72</v>
+        <v>276.26</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-107.85</v>
+        <v>-102.92</v>
       </c>
       <c r="K22" t="n">
-        <v>-150.27</v>
+        <v>-143.4</v>
       </c>
       <c r="L22" t="n">
-        <v>184.97</v>
+        <v>176.51</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>96.56</v>
+        <v>108.31</v>
       </c>
       <c r="K23" t="n">
-        <v>-221.19</v>
+        <v>-248.12</v>
       </c>
       <c r="L23" t="n">
-        <v>241.34</v>
+        <v>270.73</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-35.01</v>
+        <v>-37.71</v>
       </c>
       <c r="K24" t="n">
-        <v>-162.86</v>
+        <v>-175.39</v>
       </c>
       <c r="L24" t="n">
-        <v>166.58</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>224.63</v>
+        <v>244.02</v>
       </c>
       <c r="K25" t="n">
-        <v>-56.21</v>
+        <v>-61.06</v>
       </c>
       <c r="L25" t="n">
-        <v>231.55</v>
+        <v>251.54</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>209.91</v>
+        <v>252.61</v>
       </c>
       <c r="K26" t="n">
-        <v>-197.94</v>
+        <v>-238.2</v>
       </c>
       <c r="L26" t="n">
-        <v>288.51</v>
+        <v>347.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>102.27</v>
+        <v>117.32</v>
       </c>
       <c r="K27" t="n">
-        <v>-292.56</v>
+        <v>-335.61</v>
       </c>
       <c r="L27" t="n">
-        <v>309.92</v>
+        <v>355.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>220.23</v>
+        <v>272.25</v>
       </c>
       <c r="K28" t="n">
-        <v>-107.36</v>
+        <v>-132.72</v>
       </c>
       <c r="L28" t="n">
-        <v>245</v>
+        <v>302.87</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>74.39</v>
+        <v>67.63</v>
       </c>
       <c r="K29" t="n">
-        <v>-44.15</v>
+        <v>-40.14</v>
       </c>
       <c r="L29" t="n">
-        <v>86.5</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-86.18000000000001</v>
+        <v>-67.06999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-136.46</v>
+        <v>-106.2</v>
       </c>
       <c r="L30" t="n">
-        <v>161.4</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.42</v>
+        <v>-20.27</v>
       </c>
       <c r="K31" t="n">
-        <v>91.01000000000001</v>
+        <v>82.27</v>
       </c>
       <c r="L31" t="n">
-        <v>93.73</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-96.37</v>
+        <v>-82.23</v>
       </c>
       <c r="K32" t="n">
-        <v>-53.44</v>
+        <v>-45.6</v>
       </c>
       <c r="L32" t="n">
-        <v>110.19</v>
+        <v>94.02</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>33.05</v>
+        <v>28.81</v>
       </c>
       <c r="K33" t="n">
-        <v>-87.17</v>
+        <v>-75.98999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>93.22</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-78.98999999999999</v>
+        <v>-70.19</v>
       </c>
       <c r="K34" t="n">
-        <v>20.29</v>
+        <v>18.02</v>
       </c>
       <c r="L34" t="n">
-        <v>81.56</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-134.22</v>
+        <v>-131.19</v>
       </c>
       <c r="K35" t="n">
-        <v>107.3</v>
+        <v>104.88</v>
       </c>
       <c r="L35" t="n">
-        <v>171.84</v>
+        <v>167.96</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-78.98999999999999</v>
+        <v>-78.09</v>
       </c>
       <c r="K36" t="n">
-        <v>-113.32</v>
+        <v>-112.03</v>
       </c>
       <c r="L36" t="n">
-        <v>138.13</v>
+        <v>136.56</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-87.54000000000001</v>
+        <v>-84.01000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>163.98</v>
+        <v>157.37</v>
       </c>
       <c r="L37" t="n">
-        <v>185.89</v>
+        <v>178.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>316.3</v>
+        <v>323.72</v>
       </c>
       <c r="K38" t="n">
-        <v>187.36</v>
+        <v>191.75</v>
       </c>
       <c r="L38" t="n">
-        <v>367.63</v>
+        <v>376.25</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>122.21</v>
+        <v>130.81</v>
       </c>
       <c r="K39" t="n">
-        <v>-206.06</v>
+        <v>-220.55</v>
       </c>
       <c r="L39" t="n">
-        <v>239.57</v>
+        <v>256.42</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>89.81</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-259.41</v>
+        <v>-274.2</v>
       </c>
       <c r="L40" t="n">
-        <v>274.52</v>
+        <v>290.17</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>205.79</v>
+        <v>229.16</v>
       </c>
       <c r="K41" t="n">
-        <v>-396.26</v>
+        <v>-441.24</v>
       </c>
       <c r="L41" t="n">
-        <v>446.51</v>
+        <v>497.2</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>13.46</v>
+        <v>16.2</v>
       </c>
       <c r="K42" t="n">
-        <v>-232.42</v>
+        <v>-279.64</v>
       </c>
       <c r="L42" t="n">
-        <v>232.81</v>
+        <v>280.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>133.01</v>
+        <v>153.08</v>
       </c>
       <c r="K43" t="n">
-        <v>277.27</v>
+        <v>319.1</v>
       </c>
       <c r="L43" t="n">
-        <v>307.52</v>
+        <v>353.91</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-16.14</v>
+        <v>-12.88</v>
       </c>
       <c r="K44" t="n">
-        <v>-114.87</v>
+        <v>-91.62</v>
       </c>
       <c r="L44" t="n">
-        <v>115.99</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-91.79000000000001</v>
+        <v>-73.29000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-54.58</v>
+        <v>-43.58</v>
       </c>
       <c r="L45" t="n">
-        <v>106.79</v>
+        <v>85.27</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-130.67</v>
+        <v>-97.93000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.76</v>
+        <v>-46.29</v>
       </c>
       <c r="L46" t="n">
-        <v>144.53</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-67.25</v>
+        <v>-54.19</v>
       </c>
       <c r="K47" t="n">
-        <v>171.04</v>
+        <v>137.81</v>
       </c>
       <c r="L47" t="n">
-        <v>183.78</v>
+        <v>148.08</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.74</v>
+        <v>-49.47</v>
       </c>
       <c r="K48" t="n">
-        <v>109.07</v>
+        <v>91.86</v>
       </c>
       <c r="L48" t="n">
-        <v>123.88</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.79</v>
+        <v>-1.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-96.61</v>
+        <v>-83.93000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>96.62</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>54.78</v>
+        <v>54.93</v>
       </c>
       <c r="K50" t="n">
-        <v>128.63</v>
+        <v>128.98</v>
       </c>
       <c r="L50" t="n">
-        <v>139.8</v>
+        <v>140.19</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-173.98</v>
+        <v>-168.25</v>
       </c>
       <c r="K51" t="n">
-        <v>95.48999999999999</v>
+        <v>92.34</v>
       </c>
       <c r="L51" t="n">
-        <v>198.46</v>
+        <v>191.92</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-116.87</v>
+        <v>-111.76</v>
       </c>
       <c r="K52" t="n">
-        <v>-159.57</v>
+        <v>-152.58</v>
       </c>
       <c r="L52" t="n">
-        <v>197.79</v>
+        <v>189.13</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>89.48999999999999</v>
+        <v>100.8</v>
       </c>
       <c r="K53" t="n">
-        <v>238.1</v>
+        <v>268.19</v>
       </c>
       <c r="L53" t="n">
-        <v>254.36</v>
+        <v>286.51</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>57.2</v>
+        <v>63.85</v>
       </c>
       <c r="K54" t="n">
-        <v>201.43</v>
+        <v>224.84</v>
       </c>
       <c r="L54" t="n">
-        <v>209.39</v>
+        <v>233.73</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>117.13</v>
+        <v>132.87</v>
       </c>
       <c r="K55" t="n">
-        <v>-10.63</v>
+        <v>-12.05</v>
       </c>
       <c r="L55" t="n">
-        <v>117.61</v>
+        <v>133.42</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-217.32</v>
+        <v>-242.8</v>
       </c>
       <c r="K56" t="n">
-        <v>-319.09</v>
+        <v>-356.49</v>
       </c>
       <c r="L56" t="n">
-        <v>386.06</v>
+        <v>431.32</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-54.51</v>
+        <v>-62.78</v>
       </c>
       <c r="K57" t="n">
-        <v>-312.88</v>
+        <v>-360.35</v>
       </c>
       <c r="L57" t="n">
-        <v>317.6</v>
+        <v>365.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>406.58</v>
+        <v>492.82</v>
       </c>
       <c r="K58" t="n">
-        <v>-75.86</v>
+        <v>-91.95</v>
       </c>
       <c r="L58" t="n">
-        <v>413.59</v>
+        <v>501.32</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-146.97</v>
+        <v>-112.31</v>
       </c>
       <c r="K59" t="n">
-        <v>-51.24</v>
+        <v>-39.16</v>
       </c>
       <c r="L59" t="n">
-        <v>155.64</v>
+        <v>118.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-40.71</v>
+        <v>-34.57</v>
       </c>
       <c r="K60" t="n">
-        <v>-46.37</v>
+        <v>-39.37</v>
       </c>
       <c r="L60" t="n">
-        <v>61.7</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>79.84</v>
+        <v>71.2</v>
       </c>
       <c r="K61" t="n">
-        <v>7.87</v>
+        <v>7.02</v>
       </c>
       <c r="L61" t="n">
-        <v>80.23</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="K62" t="n">
-        <v>117.61</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>117.61</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-145.89</v>
+        <v>-112.5</v>
       </c>
       <c r="K63" t="n">
-        <v>182.6</v>
+        <v>140.81</v>
       </c>
       <c r="L63" t="n">
-        <v>233.73</v>
+        <v>180.23</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.8</v>
+        <v>-20.76</v>
       </c>
       <c r="K64" t="n">
-        <v>-29.62</v>
+        <v>-23.83</v>
       </c>
       <c r="L64" t="n">
-        <v>39.28</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="K65" t="n">
-        <v>-147.27</v>
+        <v>-145.82</v>
       </c>
       <c r="L65" t="n">
-        <v>147.29</v>
+        <v>145.84</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-142.57</v>
+        <v>-133.35</v>
       </c>
       <c r="K66" t="n">
-        <v>-197.06</v>
+        <v>-184.32</v>
       </c>
       <c r="L66" t="n">
-        <v>243.22</v>
+        <v>227.5</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-179.36</v>
+        <v>-162.76</v>
       </c>
       <c r="K67" t="n">
-        <v>120.49</v>
+        <v>109.34</v>
       </c>
       <c r="L67" t="n">
-        <v>216.07</v>
+        <v>196.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-121.18</v>
+        <v>-128.35</v>
       </c>
       <c r="K68" t="n">
-        <v>336.14</v>
+        <v>356</v>
       </c>
       <c r="L68" t="n">
-        <v>357.32</v>
+        <v>378.43</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-132.59</v>
+        <v>-143.87</v>
       </c>
       <c r="K69" t="n">
-        <v>205.95</v>
+        <v>223.47</v>
       </c>
       <c r="L69" t="n">
-        <v>244.94</v>
+        <v>265.77</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>140.09</v>
+        <v>151.68</v>
       </c>
       <c r="K70" t="n">
-        <v>146.96</v>
+        <v>159.12</v>
       </c>
       <c r="L70" t="n">
-        <v>203.03</v>
+        <v>219.83</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>315.23</v>
+        <v>375.5</v>
       </c>
       <c r="K71" t="n">
-        <v>-36.74</v>
+        <v>-43.77</v>
       </c>
       <c r="L71" t="n">
-        <v>317.37</v>
+        <v>378.04</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-248.73</v>
+        <v>-307.46</v>
       </c>
       <c r="K72" t="n">
-        <v>-132.46</v>
+        <v>-163.74</v>
       </c>
       <c r="L72" t="n">
-        <v>281.8</v>
+        <v>348.34</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-236.6</v>
+        <v>-277.67</v>
       </c>
       <c r="K73" t="n">
-        <v>89.65000000000001</v>
+        <v>105.21</v>
       </c>
       <c r="L73" t="n">
-        <v>253.02</v>
+        <v>296.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="K74" t="n">
-        <v>194.34</v>
+        <v>142.01</v>
       </c>
       <c r="L74" t="n">
-        <v>194.35</v>
+        <v>142.02</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>152.6</v>
+        <v>114.68</v>
       </c>
       <c r="K75" t="n">
-        <v>19.47</v>
+        <v>14.63</v>
       </c>
       <c r="L75" t="n">
-        <v>153.84</v>
+        <v>115.61</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-101.21</v>
+        <v>-79.20999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>38.68</v>
+        <v>30.27</v>
       </c>
       <c r="L76" t="n">
-        <v>108.35</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>172.73</v>
+        <v>137.5</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.8</v>
+        <v>-18.94</v>
       </c>
       <c r="L77" t="n">
-        <v>174.37</v>
+        <v>138.8</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>69.03</v>
+        <v>59.24</v>
       </c>
       <c r="K78" t="n">
-        <v>-84.09999999999999</v>
+        <v>-72.17</v>
       </c>
       <c r="L78" t="n">
-        <v>108.8</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-28.11</v>
+        <v>-23.99</v>
       </c>
       <c r="K79" t="n">
-        <v>-105.7</v>
+        <v>-90.20999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>109.37</v>
+        <v>93.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>222.39</v>
+        <v>211.4</v>
       </c>
       <c r="K80" t="n">
-        <v>22.75</v>
+        <v>21.63</v>
       </c>
       <c r="L80" t="n">
-        <v>223.55</v>
+        <v>212.51</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-36.51</v>
+        <v>-36.65</v>
       </c>
       <c r="K81" t="n">
-        <v>135.38</v>
+        <v>135.86</v>
       </c>
       <c r="L81" t="n">
-        <v>140.21</v>
+        <v>140.72</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-208.17</v>
+        <v>-190.15</v>
       </c>
       <c r="K82" t="n">
-        <v>-270.13</v>
+        <v>-246.75</v>
       </c>
       <c r="L82" t="n">
-        <v>341.03</v>
+        <v>311.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>52.77</v>
+        <v>54.74</v>
       </c>
       <c r="K83" t="n">
-        <v>-418.51</v>
+        <v>-434.13</v>
       </c>
       <c r="L83" t="n">
-        <v>421.83</v>
+        <v>437.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>155.33</v>
+        <v>173.71</v>
       </c>
       <c r="K84" t="n">
-        <v>166.68</v>
+        <v>186.41</v>
       </c>
       <c r="L84" t="n">
-        <v>227.84</v>
+        <v>254.8</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-332.29</v>
+        <v>-347.43</v>
       </c>
       <c r="K85" t="n">
-        <v>-31.83</v>
+        <v>-33.28</v>
       </c>
       <c r="L85" t="n">
-        <v>333.81</v>
+        <v>349.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-306.45</v>
+        <v>-368</v>
       </c>
       <c r="K86" t="n">
-        <v>-244.07</v>
+        <v>-293.09</v>
       </c>
       <c r="L86" t="n">
-        <v>391.77</v>
+        <v>470.45</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>208.2</v>
+        <v>249.04</v>
       </c>
       <c r="K87" t="n">
-        <v>406.83</v>
+        <v>486.63</v>
       </c>
       <c r="L87" t="n">
-        <v>457.01</v>
+        <v>546.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>312.34</v>
+        <v>367.64</v>
       </c>
       <c r="K88" t="n">
-        <v>380.91</v>
+        <v>448.35</v>
       </c>
       <c r="L88" t="n">
-        <v>492.59</v>
+        <v>579.8099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-69.73</v>
+        <v>-70.03</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.04</v>
+        <v>-10.08</v>
       </c>
       <c r="L14" t="n">
-        <v>70.45</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>74.62</v>
+        <v>71.66</v>
       </c>
       <c r="K15" t="n">
-        <v>58.38</v>
+        <v>56.06</v>
       </c>
       <c r="L15" t="n">
-        <v>94.73999999999999</v>
+        <v>90.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-51.06</v>
+        <v>-54.23</v>
       </c>
       <c r="K16" t="n">
-        <v>22.84</v>
+        <v>24.26</v>
       </c>
       <c r="L16" t="n">
-        <v>55.94</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-26.9</v>
+        <v>-26.34</v>
       </c>
       <c r="K17" t="n">
-        <v>-99.94</v>
+        <v>-97.86</v>
       </c>
       <c r="L17" t="n">
-        <v>103.5</v>
+        <v>101.34</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>113.75</v>
+        <v>108.32</v>
       </c>
       <c r="K18" t="n">
-        <v>-52.31</v>
+        <v>-49.81</v>
       </c>
       <c r="L18" t="n">
-        <v>125.2</v>
+        <v>119.22</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>70.53</v>
+        <v>73.45</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.91</v>
+        <v>-0.95</v>
       </c>
       <c r="L19" t="n">
-        <v>70.54000000000001</v>
+        <v>73.45999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-231.86</v>
+        <v>-217.27</v>
       </c>
       <c r="K20" t="n">
-        <v>-160.44</v>
+        <v>-150.34</v>
       </c>
       <c r="L20" t="n">
-        <v>281.96</v>
+        <v>264.21</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>179.97</v>
+        <v>169.42</v>
       </c>
       <c r="K21" t="n">
-        <v>209.6</v>
+        <v>197.3</v>
       </c>
       <c r="L21" t="n">
-        <v>276.26</v>
+        <v>260.06</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-102.92</v>
+        <v>-99.93000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-143.4</v>
+        <v>-139.23</v>
       </c>
       <c r="L22" t="n">
-        <v>176.51</v>
+        <v>171.38</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>108.31</v>
+        <v>112.26</v>
       </c>
       <c r="K23" t="n">
-        <v>-248.12</v>
+        <v>-257.17</v>
       </c>
       <c r="L23" t="n">
-        <v>270.73</v>
+        <v>280.6</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-37.71</v>
+        <v>-38.47</v>
       </c>
       <c r="K24" t="n">
-        <v>-175.39</v>
+        <v>-178.94</v>
       </c>
       <c r="L24" t="n">
-        <v>179.4</v>
+        <v>183.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>244.02</v>
+        <v>246.41</v>
       </c>
       <c r="K25" t="n">
-        <v>-61.06</v>
+        <v>-61.66</v>
       </c>
       <c r="L25" t="n">
-        <v>251.54</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>252.61</v>
+        <v>262.71</v>
       </c>
       <c r="K26" t="n">
-        <v>-238.2</v>
+        <v>-247.73</v>
       </c>
       <c r="L26" t="n">
-        <v>347.21</v>
+        <v>361.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>117.32</v>
+        <v>118.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-335.61</v>
+        <v>-337.92</v>
       </c>
       <c r="L27" t="n">
-        <v>355.53</v>
+        <v>357.97</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>272.25</v>
+        <v>290.71</v>
       </c>
       <c r="K28" t="n">
-        <v>-132.72</v>
+        <v>-141.71</v>
       </c>
       <c r="L28" t="n">
-        <v>302.87</v>
+        <v>323.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>67.63</v>
+        <v>67.48</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.14</v>
+        <v>-40.05</v>
       </c>
       <c r="L29" t="n">
-        <v>78.65000000000001</v>
+        <v>78.47</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-67.06999999999999</v>
+        <v>-62.86</v>
       </c>
       <c r="K30" t="n">
-        <v>-106.2</v>
+        <v>-99.53</v>
       </c>
       <c r="L30" t="n">
-        <v>125.6</v>
+        <v>117.71</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.27</v>
+        <v>-19.9</v>
       </c>
       <c r="K31" t="n">
-        <v>82.27</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>84.73</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-82.23</v>
+        <v>-83.06999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-45.6</v>
+        <v>-46.07</v>
       </c>
       <c r="L32" t="n">
-        <v>94.02</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>28.81</v>
+        <v>29.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-75.98999999999999</v>
+        <v>-78.33</v>
       </c>
       <c r="L33" t="n">
-        <v>81.27</v>
+        <v>83.77</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-70.19</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>18.02</v>
+        <v>18.94</v>
       </c>
       <c r="L34" t="n">
-        <v>72.45999999999999</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-131.19</v>
+        <v>-131.62</v>
       </c>
       <c r="K35" t="n">
-        <v>104.88</v>
+        <v>105.22</v>
       </c>
       <c r="L35" t="n">
-        <v>167.96</v>
+        <v>168.51</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-78.09</v>
+        <v>-78.92</v>
       </c>
       <c r="K36" t="n">
-        <v>-112.03</v>
+        <v>-113.22</v>
       </c>
       <c r="L36" t="n">
-        <v>136.56</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-84.01000000000001</v>
+        <v>-82.51000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>157.37</v>
+        <v>154.57</v>
       </c>
       <c r="L37" t="n">
-        <v>178.39</v>
+        <v>175.21</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>323.72</v>
+        <v>306.66</v>
       </c>
       <c r="K38" t="n">
-        <v>191.75</v>
+        <v>181.65</v>
       </c>
       <c r="L38" t="n">
-        <v>376.25</v>
+        <v>356.42</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>130.81</v>
+        <v>130.69</v>
       </c>
       <c r="K39" t="n">
-        <v>-220.55</v>
+        <v>-220.36</v>
       </c>
       <c r="L39" t="n">
-        <v>256.42</v>
+        <v>256.2</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>94.93000000000001</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-274.2</v>
+        <v>-269.63</v>
       </c>
       <c r="L40" t="n">
-        <v>290.17</v>
+        <v>285.33</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>229.16</v>
+        <v>222.25</v>
       </c>
       <c r="K41" t="n">
-        <v>-441.24</v>
+        <v>-427.95</v>
       </c>
       <c r="L41" t="n">
-        <v>497.2</v>
+        <v>482.22</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>16.2</v>
+        <v>17.15</v>
       </c>
       <c r="K42" t="n">
-        <v>-279.64</v>
+        <v>-296.14</v>
       </c>
       <c r="L42" t="n">
-        <v>280.11</v>
+        <v>296.63</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>153.08</v>
+        <v>155.19</v>
       </c>
       <c r="K43" t="n">
-        <v>319.1</v>
+        <v>323.48</v>
       </c>
       <c r="L43" t="n">
-        <v>353.91</v>
+        <v>358.78</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.88</v>
+        <v>-12.57</v>
       </c>
       <c r="K44" t="n">
-        <v>-91.62</v>
+        <v>-89.42</v>
       </c>
       <c r="L44" t="n">
-        <v>92.52</v>
+        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-73.29000000000001</v>
+        <v>-72.45999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-43.58</v>
+        <v>-43.09</v>
       </c>
       <c r="L45" t="n">
-        <v>85.27</v>
+        <v>84.31</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-97.93000000000001</v>
+        <v>-91.76000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-46.29</v>
+        <v>-43.37</v>
       </c>
       <c r="L46" t="n">
-        <v>108.32</v>
+        <v>101.49</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-54.19</v>
+        <v>-51.09</v>
       </c>
       <c r="K47" t="n">
-        <v>137.81</v>
+        <v>129.93</v>
       </c>
       <c r="L47" t="n">
-        <v>148.08</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-49.47</v>
+        <v>-48.23</v>
       </c>
       <c r="K48" t="n">
-        <v>91.86</v>
+        <v>89.55</v>
       </c>
       <c r="L48" t="n">
-        <v>104.33</v>
+        <v>101.71</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.56</v>
+        <v>-1.6</v>
       </c>
       <c r="K49" t="n">
-        <v>-83.93000000000001</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>83.95</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>54.93</v>
+        <v>56.57</v>
       </c>
       <c r="K50" t="n">
-        <v>128.98</v>
+        <v>132.84</v>
       </c>
       <c r="L50" t="n">
-        <v>140.19</v>
+        <v>144.39</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-168.25</v>
+        <v>-167.55</v>
       </c>
       <c r="K51" t="n">
-        <v>92.34</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>191.92</v>
+        <v>191.13</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-111.76</v>
+        <v>-108.75</v>
       </c>
       <c r="K52" t="n">
-        <v>-152.58</v>
+        <v>-148.48</v>
       </c>
       <c r="L52" t="n">
-        <v>189.13</v>
+        <v>184.04</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>100.8</v>
+        <v>104.4</v>
       </c>
       <c r="K53" t="n">
-        <v>268.19</v>
+        <v>277.75</v>
       </c>
       <c r="L53" t="n">
-        <v>286.51</v>
+        <v>296.73</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>63.85</v>
+        <v>66.38</v>
       </c>
       <c r="K54" t="n">
-        <v>224.84</v>
+        <v>233.72</v>
       </c>
       <c r="L54" t="n">
-        <v>233.73</v>
+        <v>242.97</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>132.87</v>
+        <v>143.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-12.05</v>
+        <v>-13.01</v>
       </c>
       <c r="L55" t="n">
-        <v>133.42</v>
+        <v>144.02</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-242.8</v>
+        <v>-238.49</v>
       </c>
       <c r="K56" t="n">
-        <v>-356.49</v>
+        <v>-350.17</v>
       </c>
       <c r="L56" t="n">
-        <v>431.32</v>
+        <v>423.67</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-62.78</v>
+        <v>-63.5</v>
       </c>
       <c r="K57" t="n">
-        <v>-360.35</v>
+        <v>-364.48</v>
       </c>
       <c r="L57" t="n">
-        <v>365.78</v>
+        <v>369.97</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>492.82</v>
+        <v>502.75</v>
       </c>
       <c r="K58" t="n">
-        <v>-91.95</v>
+        <v>-93.8</v>
       </c>
       <c r="L58" t="n">
-        <v>501.32</v>
+        <v>511.43</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-112.31</v>
+        <v>-104.63</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.16</v>
+        <v>-36.48</v>
       </c>
       <c r="L59" t="n">
-        <v>118.94</v>
+        <v>110.81</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-34.57</v>
+        <v>-36.61</v>
       </c>
       <c r="K60" t="n">
-        <v>-39.37</v>
+        <v>-41.7</v>
       </c>
       <c r="L60" t="n">
-        <v>52.39</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>71.2</v>
+        <v>71.69</v>
       </c>
       <c r="K61" t="n">
-        <v>7.02</v>
+        <v>7.07</v>
       </c>
       <c r="L61" t="n">
-        <v>71.55</v>
+        <v>72.04000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>99.06999999999999</v>
+        <v>98.75</v>
       </c>
       <c r="L62" t="n">
-        <v>99.06999999999999</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-112.5</v>
+        <v>-103.59</v>
       </c>
       <c r="K63" t="n">
-        <v>140.81</v>
+        <v>129.66</v>
       </c>
       <c r="L63" t="n">
-        <v>180.23</v>
+        <v>165.96</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-20.76</v>
+        <v>-22.05</v>
       </c>
       <c r="K64" t="n">
-        <v>-23.83</v>
+        <v>-25.32</v>
       </c>
       <c r="L64" t="n">
-        <v>31.61</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="K65" t="n">
-        <v>-145.82</v>
+        <v>-149.03</v>
       </c>
       <c r="L65" t="n">
-        <v>145.84</v>
+        <v>149.05</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-133.35</v>
+        <v>-126.69</v>
       </c>
       <c r="K66" t="n">
-        <v>-184.32</v>
+        <v>-175.12</v>
       </c>
       <c r="L66" t="n">
-        <v>227.5</v>
+        <v>216.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-162.76</v>
+        <v>-163.05</v>
       </c>
       <c r="K67" t="n">
-        <v>109.34</v>
+        <v>109.54</v>
       </c>
       <c r="L67" t="n">
-        <v>196.08</v>
+        <v>196.43</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-128.35</v>
+        <v>-124.87</v>
       </c>
       <c r="K68" t="n">
-        <v>356</v>
+        <v>346.37</v>
       </c>
       <c r="L68" t="n">
-        <v>378.43</v>
+        <v>368.19</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-143.87</v>
+        <v>-144.94</v>
       </c>
       <c r="K69" t="n">
-        <v>223.47</v>
+        <v>225.13</v>
       </c>
       <c r="L69" t="n">
-        <v>265.77</v>
+        <v>267.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>151.68</v>
+        <v>153.64</v>
       </c>
       <c r="K70" t="n">
-        <v>159.12</v>
+        <v>161.17</v>
       </c>
       <c r="L70" t="n">
-        <v>219.83</v>
+        <v>222.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>375.5</v>
+        <v>384.98</v>
       </c>
       <c r="K71" t="n">
-        <v>-43.77</v>
+        <v>-44.87</v>
       </c>
       <c r="L71" t="n">
-        <v>378.04</v>
+        <v>387.59</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-307.46</v>
+        <v>-324.89</v>
       </c>
       <c r="K72" t="n">
-        <v>-163.74</v>
+        <v>-173.01</v>
       </c>
       <c r="L72" t="n">
-        <v>348.34</v>
+        <v>368.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-277.67</v>
+        <v>-286.73</v>
       </c>
       <c r="K73" t="n">
-        <v>105.21</v>
+        <v>108.64</v>
       </c>
       <c r="L73" t="n">
-        <v>296.93</v>
+        <v>306.62</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="K74" t="n">
-        <v>142.01</v>
+        <v>130.22</v>
       </c>
       <c r="L74" t="n">
-        <v>142.02</v>
+        <v>130.23</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>114.68</v>
+        <v>106.58</v>
       </c>
       <c r="K75" t="n">
-        <v>14.63</v>
+        <v>13.6</v>
       </c>
       <c r="L75" t="n">
-        <v>115.61</v>
+        <v>107.44</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-79.20999999999999</v>
+        <v>-77.25</v>
       </c>
       <c r="K76" t="n">
-        <v>30.27</v>
+        <v>29.52</v>
       </c>
       <c r="L76" t="n">
-        <v>84.8</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>137.5</v>
+        <v>131.85</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.94</v>
+        <v>-18.16</v>
       </c>
       <c r="L77" t="n">
-        <v>138.8</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>59.24</v>
+        <v>59.52</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.17</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>93.37</v>
+        <v>93.81999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-23.99</v>
+        <v>-24.36</v>
       </c>
       <c r="K79" t="n">
-        <v>-90.20999999999999</v>
+        <v>-91.59999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>93.34</v>
+        <v>94.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>211.4</v>
+        <v>206.32</v>
       </c>
       <c r="K80" t="n">
-        <v>21.63</v>
+        <v>21.11</v>
       </c>
       <c r="L80" t="n">
-        <v>212.51</v>
+        <v>207.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-36.65</v>
+        <v>-37.83</v>
       </c>
       <c r="K81" t="n">
-        <v>135.86</v>
+        <v>140.24</v>
       </c>
       <c r="L81" t="n">
-        <v>140.72</v>
+        <v>145.26</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-190.15</v>
+        <v>-175.62</v>
       </c>
       <c r="K82" t="n">
-        <v>-246.75</v>
+        <v>-227.89</v>
       </c>
       <c r="L82" t="n">
-        <v>311.52</v>
+        <v>287.71</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>54.74</v>
+        <v>52.15</v>
       </c>
       <c r="K83" t="n">
-        <v>-434.13</v>
+        <v>-413.6</v>
       </c>
       <c r="L83" t="n">
-        <v>437.56</v>
+        <v>416.87</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>173.71</v>
+        <v>179.86</v>
       </c>
       <c r="K84" t="n">
-        <v>186.41</v>
+        <v>193.01</v>
       </c>
       <c r="L84" t="n">
-        <v>254.8</v>
+        <v>263.82</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-347.43</v>
+        <v>-336.34</v>
       </c>
       <c r="K85" t="n">
-        <v>-33.28</v>
+        <v>-32.22</v>
       </c>
       <c r="L85" t="n">
-        <v>349.02</v>
+        <v>337.88</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-368</v>
+        <v>-374.47</v>
       </c>
       <c r="K86" t="n">
-        <v>-293.09</v>
+        <v>-298.25</v>
       </c>
       <c r="L86" t="n">
-        <v>470.45</v>
+        <v>478.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>249.04</v>
+        <v>250.26</v>
       </c>
       <c r="K87" t="n">
-        <v>486.63</v>
+        <v>489.02</v>
       </c>
       <c r="L87" t="n">
-        <v>546.65</v>
+        <v>549.34</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>367.64</v>
+        <v>364.13</v>
       </c>
       <c r="K88" t="n">
-        <v>448.35</v>
+        <v>444.07</v>
       </c>
       <c r="L88" t="n">
-        <v>579.8099999999999</v>
+        <v>574.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="F14" t="n">
-        <v>15.52</v>
+        <v>9.16</v>
       </c>
       <c r="G14" t="n">
-        <v>162</v>
+        <v>155.5</v>
       </c>
       <c r="H14" t="n">
-        <v>61.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-70.03</v>
+        <v>-7.09</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.08</v>
+        <v>79.58</v>
       </c>
       <c r="L14" t="n">
-        <v>70.75</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:44:45</t>
+          <t>04:46:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.11</v>
+        <v>5.4</v>
       </c>
       <c r="F15" t="n">
-        <v>15.82</v>
+        <v>12.74</v>
       </c>
       <c r="G15" t="n">
-        <v>159.8</v>
+        <v>163.4</v>
       </c>
       <c r="H15" t="n">
-        <v>73.3</v>
+        <v>74.3</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>71.66</v>
+        <v>66.44</v>
       </c>
       <c r="K15" t="n">
-        <v>56.06</v>
+        <v>36.79</v>
       </c>
       <c r="L15" t="n">
-        <v>90.98</v>
+        <v>75.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:46:12</t>
+          <t>04:47:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.63</v>
+        <v>5.23</v>
       </c>
       <c r="F16" t="n">
-        <v>16.22</v>
+        <v>12.65</v>
       </c>
       <c r="G16" t="n">
-        <v>159.5</v>
+        <v>143.1</v>
       </c>
       <c r="H16" t="n">
-        <v>71.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-54.23</v>
+        <v>109.33</v>
       </c>
       <c r="K16" t="n">
-        <v>24.26</v>
+        <v>33.17</v>
       </c>
       <c r="L16" t="n">
-        <v>59.41</v>
+        <v>114.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:05</t>
+          <t>04:51:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.35</v>
+        <v>5.47</v>
       </c>
       <c r="F17" t="n">
-        <v>16.23</v>
+        <v>13.37</v>
       </c>
       <c r="G17" t="n">
-        <v>155.1</v>
+        <v>162.2</v>
       </c>
       <c r="H17" t="n">
-        <v>71.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-26.34</v>
+        <v>125.91</v>
       </c>
       <c r="K17" t="n">
-        <v>-97.86</v>
+        <v>12.71</v>
       </c>
       <c r="L17" t="n">
-        <v>101.34</v>
+        <v>126.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:53:47</t>
+          <t>04:53:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.09</v>
+        <v>3.95</v>
       </c>
       <c r="F18" t="n">
-        <v>16.32</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>169.5</v>
+        <v>157.6</v>
       </c>
       <c r="H18" t="n">
-        <v>71.2</v>
+        <v>70</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>108.32</v>
+        <v>12.15</v>
       </c>
       <c r="K18" t="n">
-        <v>-49.81</v>
+        <v>-3.63</v>
       </c>
       <c r="L18" t="n">
-        <v>119.22</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:56:06</t>
+          <t>04:54:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.34</v>
+        <v>4.56</v>
       </c>
       <c r="F19" t="n">
-        <v>15.67</v>
+        <v>12.84</v>
       </c>
       <c r="G19" t="n">
-        <v>157.3</v>
+        <v>148.2</v>
       </c>
       <c r="H19" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>73.45</v>
+        <v>-79.14</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.95</v>
+        <v>48.83</v>
       </c>
       <c r="L19" t="n">
-        <v>73.45999999999999</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:00:18</t>
+          <t>04:59:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>6.23</v>
+        <v>5.49</v>
       </c>
       <c r="F20" t="n">
-        <v>16.36</v>
+        <v>11.82</v>
       </c>
       <c r="G20" t="n">
-        <v>152.4</v>
+        <v>154.8</v>
       </c>
       <c r="H20" t="n">
-        <v>72.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-217.27</v>
+        <v>198.33</v>
       </c>
       <c r="K20" t="n">
-        <v>-150.34</v>
+        <v>-71.75</v>
       </c>
       <c r="L20" t="n">
-        <v>264.21</v>
+        <v>210.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:30</t>
+          <t>05:00:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>6.11</v>
+        <v>5.12</v>
       </c>
       <c r="F21" t="n">
-        <v>16.08</v>
+        <v>15.95</v>
       </c>
       <c r="G21" t="n">
-        <v>155</v>
+        <v>169.1</v>
       </c>
       <c r="H21" t="n">
-        <v>74.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>169.42</v>
+        <v>192.92</v>
       </c>
       <c r="K21" t="n">
-        <v>197.3</v>
+        <v>-31.83</v>
       </c>
       <c r="L21" t="n">
-        <v>260.06</v>
+        <v>195.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:05:01</t>
+          <t>05:02:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.15</v>
+        <v>4.94</v>
       </c>
       <c r="F22" t="n">
-        <v>16.24</v>
+        <v>10.64</v>
       </c>
       <c r="G22" t="n">
-        <v>166.4</v>
+        <v>156.9</v>
       </c>
       <c r="H22" t="n">
-        <v>73.5</v>
+        <v>77</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-99.93000000000001</v>
+        <v>143.82</v>
       </c>
       <c r="K22" t="n">
-        <v>-139.23</v>
+        <v>-97.25</v>
       </c>
       <c r="L22" t="n">
-        <v>171.38</v>
+        <v>173.61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:09:43</t>
+          <t>05:06:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>6.9</v>
+        <v>4.97</v>
       </c>
       <c r="F23" t="n">
-        <v>17.03</v>
+        <v>10.71</v>
       </c>
       <c r="G23" t="n">
-        <v>151.6</v>
+        <v>150.8</v>
       </c>
       <c r="H23" t="n">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>112.26</v>
+        <v>47.5</v>
       </c>
       <c r="K23" t="n">
-        <v>-257.17</v>
+        <v>-228.06</v>
       </c>
       <c r="L23" t="n">
-        <v>280.6</v>
+        <v>232.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:12:03</t>
+          <t>05:09:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.95</v>
+        <v>5.63</v>
       </c>
       <c r="F24" t="n">
-        <v>16.44</v>
+        <v>14.14</v>
       </c>
       <c r="G24" t="n">
-        <v>149.8</v>
+        <v>168.2</v>
       </c>
       <c r="H24" t="n">
-        <v>69.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-38.47</v>
+        <v>-112.18</v>
       </c>
       <c r="K24" t="n">
-        <v>-178.94</v>
+        <v>-327.57</v>
       </c>
       <c r="L24" t="n">
-        <v>183.02</v>
+        <v>346.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:13:34</t>
+          <t>05:11:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>6.09</v>
+        <v>4.36</v>
       </c>
       <c r="F25" t="n">
-        <v>16.65</v>
+        <v>12.88</v>
       </c>
       <c r="G25" t="n">
-        <v>141.7</v>
+        <v>163.2</v>
       </c>
       <c r="H25" t="n">
-        <v>64</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>246.41</v>
+        <v>11.44</v>
       </c>
       <c r="K25" t="n">
-        <v>-61.66</v>
+        <v>-185.08</v>
       </c>
       <c r="L25" t="n">
-        <v>254</v>
+        <v>185.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:19:30</t>
+          <t>05:15:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.8</v>
+        <v>4.85</v>
       </c>
       <c r="F26" t="n">
-        <v>15.81</v>
+        <v>13.61</v>
       </c>
       <c r="G26" t="n">
-        <v>153.9</v>
+        <v>154.5</v>
       </c>
       <c r="H26" t="n">
-        <v>69.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>262.71</v>
+        <v>215.97</v>
       </c>
       <c r="K26" t="n">
-        <v>-247.73</v>
+        <v>-389.01</v>
       </c>
       <c r="L26" t="n">
-        <v>361.1</v>
+        <v>444.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:21:24</t>
+          <t>05:18:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.24</v>
+        <v>4.8</v>
       </c>
       <c r="F27" t="n">
-        <v>15.77</v>
+        <v>12.32</v>
       </c>
       <c r="G27" t="n">
-        <v>148</v>
+        <v>164.1</v>
       </c>
       <c r="H27" t="n">
-        <v>63.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>118.13</v>
+        <v>196.34</v>
       </c>
       <c r="K27" t="n">
-        <v>-337.92</v>
+        <v>276.88</v>
       </c>
       <c r="L27" t="n">
-        <v>357.97</v>
+        <v>339.43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:23:53</t>
+          <t>05:19:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.87</v>
+        <v>4.91</v>
       </c>
       <c r="F28" t="n">
-        <v>15.83</v>
+        <v>13.72</v>
       </c>
       <c r="G28" t="n">
-        <v>165.8</v>
+        <v>149.7</v>
       </c>
       <c r="H28" t="n">
-        <v>71.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>290.71</v>
+        <v>269.34</v>
       </c>
       <c r="K28" t="n">
-        <v>-141.71</v>
+        <v>191.98</v>
       </c>
       <c r="L28" t="n">
-        <v>323.41</v>
+        <v>330.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:35:03</t>
+          <t>05:30:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="F29" t="n">
-        <v>16.87</v>
+        <v>13.17</v>
       </c>
       <c r="G29" t="n">
-        <v>151.4</v>
+        <v>158.1</v>
       </c>
       <c r="H29" t="n">
-        <v>72.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>67.48</v>
+        <v>111.35</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.05</v>
+        <v>-27.59</v>
       </c>
       <c r="L29" t="n">
-        <v>78.47</v>
+        <v>114.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:36:42</t>
+          <t>05:32:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="F30" t="n">
-        <v>16.28</v>
+        <v>12.31</v>
       </c>
       <c r="G30" t="n">
-        <v>153.3</v>
+        <v>148.8</v>
       </c>
       <c r="H30" t="n">
-        <v>77.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="I30" t="n">
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.86</v>
+        <v>94.47</v>
       </c>
       <c r="K30" t="n">
-        <v>-99.53</v>
+        <v>-53.02</v>
       </c>
       <c r="L30" t="n">
-        <v>117.71</v>
+        <v>108.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:38:58</t>
+          <t>05:33:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.96</v>
+        <v>4.82</v>
       </c>
       <c r="F31" t="n">
-        <v>16.81</v>
+        <v>11.8</v>
       </c>
       <c r="G31" t="n">
-        <v>147.1</v>
+        <v>167.2</v>
       </c>
       <c r="H31" t="n">
-        <v>65.7</v>
+        <v>75.2</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.9</v>
+        <v>-84.59</v>
       </c>
       <c r="K31" t="n">
-        <v>80.79000000000001</v>
+        <v>-65.72</v>
       </c>
       <c r="L31" t="n">
-        <v>83.2</v>
+        <v>107.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:44:39</t>
+          <t>05:38:29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.18</v>
+        <v>6.06</v>
       </c>
       <c r="F32" t="n">
-        <v>16.65</v>
+        <v>14.78</v>
       </c>
       <c r="G32" t="n">
-        <v>146.7</v>
+        <v>165.7</v>
       </c>
       <c r="H32" t="n">
-        <v>62.6</v>
+        <v>68</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-83.06999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-46.07</v>
+        <v>-99.73999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>94.98999999999999</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:45:32</t>
+          <t>05:40:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.09</v>
+        <v>5.35</v>
       </c>
       <c r="F33" t="n">
-        <v>16.74</v>
+        <v>16.4</v>
       </c>
       <c r="G33" t="n">
-        <v>154.6</v>
+        <v>165.5</v>
       </c>
       <c r="H33" t="n">
-        <v>66.7</v>
+        <v>67.3</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>29.7</v>
+        <v>-122.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-78.33</v>
+        <v>-31.23</v>
       </c>
       <c r="L33" t="n">
-        <v>83.77</v>
+        <v>126.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:47:56</t>
+          <t>05:42:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="F34" t="n">
-        <v>16.66</v>
+        <v>15.4</v>
       </c>
       <c r="G34" t="n">
-        <v>154.9</v>
+        <v>159.8</v>
       </c>
       <c r="H34" t="n">
-        <v>63.6</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-73.76000000000001</v>
+        <v>44.51</v>
       </c>
       <c r="K34" t="n">
-        <v>18.94</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>76.15000000000001</v>
+        <v>82.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:53:26</t>
+          <t>05:46:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.75</v>
+        <v>5.27</v>
       </c>
       <c r="F35" t="n">
-        <v>15.89</v>
+        <v>13.15</v>
       </c>
       <c r="G35" t="n">
-        <v>152.9</v>
+        <v>148.9</v>
       </c>
       <c r="H35" t="n">
-        <v>70.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="I35" t="n">
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-131.62</v>
+        <v>-35.46</v>
       </c>
       <c r="K35" t="n">
-        <v>105.22</v>
+        <v>-168.79</v>
       </c>
       <c r="L35" t="n">
-        <v>168.51</v>
+        <v>172.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:55:19</t>
+          <t>05:47:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.06</v>
+        <v>7.08</v>
       </c>
       <c r="F36" t="n">
-        <v>16.75</v>
+        <v>17.61</v>
       </c>
       <c r="G36" t="n">
-        <v>151.2</v>
+        <v>163.4</v>
       </c>
       <c r="H36" t="n">
-        <v>67.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-78.92</v>
+        <v>-15.46</v>
       </c>
       <c r="K36" t="n">
-        <v>-113.22</v>
+        <v>-176.98</v>
       </c>
       <c r="L36" t="n">
-        <v>138</v>
+        <v>177.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:56:00</t>
+          <t>05:49:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.74</v>
+        <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>16.25</v>
+        <v>13.67</v>
       </c>
       <c r="G37" t="n">
-        <v>155</v>
+        <v>161.1</v>
       </c>
       <c r="H37" t="n">
-        <v>68.7</v>
+        <v>69.5</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-82.51000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K37" t="n">
-        <v>154.57</v>
+        <v>-187.04</v>
       </c>
       <c r="L37" t="n">
-        <v>175.21</v>
+        <v>200.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:59:38</t>
+          <t>05:53:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="F38" t="n">
-        <v>15.8</v>
+        <v>17.49</v>
       </c>
       <c r="G38" t="n">
-        <v>160</v>
+        <v>153.9</v>
       </c>
       <c r="H38" t="n">
-        <v>71.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>306.66</v>
+        <v>-131.63</v>
       </c>
       <c r="K38" t="n">
-        <v>181.65</v>
+        <v>-179.25</v>
       </c>
       <c r="L38" t="n">
-        <v>356.42</v>
+        <v>222.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:00:50</t>
+          <t>05:55:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="F39" t="n">
-        <v>16.07</v>
+        <v>15.5</v>
       </c>
       <c r="G39" t="n">
-        <v>156.2</v>
+        <v>155.9</v>
       </c>
       <c r="H39" t="n">
-        <v>67.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>130.69</v>
+        <v>301.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-220.36</v>
+        <v>62.81</v>
       </c>
       <c r="L39" t="n">
-        <v>256.2</v>
+        <v>308.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:01:52</t>
+          <t>05:56:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.74</v>
+        <v>5.17</v>
       </c>
       <c r="F40" t="n">
-        <v>16.5</v>
+        <v>11.56</v>
       </c>
       <c r="G40" t="n">
-        <v>170.2</v>
+        <v>167.4</v>
       </c>
       <c r="H40" t="n">
-        <v>65.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>93.34999999999999</v>
+        <v>101.06</v>
       </c>
       <c r="K40" t="n">
-        <v>-269.63</v>
+        <v>168.21</v>
       </c>
       <c r="L40" t="n">
-        <v>285.33</v>
+        <v>196.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:06:53</t>
+          <t>06:00:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.28</v>
+        <v>5.91</v>
       </c>
       <c r="F41" t="n">
-        <v>16.44</v>
+        <v>17.44</v>
       </c>
       <c r="G41" t="n">
-        <v>164.7</v>
+        <v>156</v>
       </c>
       <c r="H41" t="n">
-        <v>70.5</v>
+        <v>66.7</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>222.25</v>
+        <v>-45.34</v>
       </c>
       <c r="K41" t="n">
-        <v>-427.95</v>
+        <v>-600.4400000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>482.22</v>
+        <v>602.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:09:02</t>
+          <t>06:01:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.29</v>
+        <v>4.6</v>
       </c>
       <c r="F42" t="n">
-        <v>15.49</v>
+        <v>11.57</v>
       </c>
       <c r="G42" t="n">
-        <v>154.2</v>
+        <v>148.2</v>
       </c>
       <c r="H42" t="n">
-        <v>71.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>17.15</v>
+        <v>341.77</v>
       </c>
       <c r="K42" t="n">
-        <v>-296.14</v>
+        <v>-46.55</v>
       </c>
       <c r="L42" t="n">
-        <v>296.63</v>
+        <v>344.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:10:03</t>
+          <t>06:03:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.17</v>
+        <v>6.85</v>
       </c>
       <c r="F43" t="n">
-        <v>16.73</v>
+        <v>18.63</v>
       </c>
       <c r="G43" t="n">
-        <v>157.9</v>
+        <v>153.8</v>
       </c>
       <c r="H43" t="n">
-        <v>74.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>155.19</v>
+        <v>539.28</v>
       </c>
       <c r="K43" t="n">
-        <v>323.48</v>
+        <v>-3.81</v>
       </c>
       <c r="L43" t="n">
-        <v>358.78</v>
+        <v>539.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:19:41</t>
+          <t>06:14:09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.61</v>
+        <v>5.54</v>
       </c>
       <c r="F44" t="n">
-        <v>16.56</v>
+        <v>14.93</v>
       </c>
       <c r="G44" t="n">
-        <v>161.5</v>
+        <v>158.7</v>
       </c>
       <c r="H44" t="n">
-        <v>67.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.57</v>
+        <v>106.39</v>
       </c>
       <c r="K44" t="n">
-        <v>-89.42</v>
+        <v>-50.78</v>
       </c>
       <c r="L44" t="n">
-        <v>90.29000000000001</v>
+        <v>117.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:21:43</t>
+          <t>06:16:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.67</v>
+        <v>4.86</v>
       </c>
       <c r="F45" t="n">
-        <v>15.92</v>
+        <v>12.13</v>
       </c>
       <c r="G45" t="n">
-        <v>169.4</v>
+        <v>147.5</v>
       </c>
       <c r="H45" t="n">
-        <v>69.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-72.45999999999999</v>
+        <v>48.9</v>
       </c>
       <c r="K45" t="n">
-        <v>-43.09</v>
+        <v>-88.72</v>
       </c>
       <c r="L45" t="n">
-        <v>84.31</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:23:48</t>
+          <t>06:17:54</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.27</v>
+        <v>4.76</v>
       </c>
       <c r="F46" t="n">
-        <v>16.54</v>
+        <v>14.02</v>
       </c>
       <c r="G46" t="n">
-        <v>160.1</v>
+        <v>150.8</v>
       </c>
       <c r="H46" t="n">
-        <v>64.7</v>
+        <v>70</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-91.76000000000001</v>
+        <v>31.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-43.37</v>
+        <v>-33.13</v>
       </c>
       <c r="L46" t="n">
-        <v>101.49</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:29:49</t>
+          <t>06:23:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.08</v>
+        <v>4.87</v>
       </c>
       <c r="F47" t="n">
-        <v>16.16</v>
+        <v>16.52</v>
       </c>
       <c r="G47" t="n">
-        <v>157.8</v>
+        <v>153.7</v>
       </c>
       <c r="H47" t="n">
-        <v>72.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-51.09</v>
+        <v>99.42</v>
       </c>
       <c r="K47" t="n">
-        <v>129.93</v>
+        <v>54.31</v>
       </c>
       <c r="L47" t="n">
-        <v>139.62</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:31:16</t>
+          <t>06:25:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.57</v>
+        <v>5.36</v>
       </c>
       <c r="F48" t="n">
-        <v>16.55</v>
+        <v>15.97</v>
       </c>
       <c r="G48" t="n">
-        <v>157.8</v>
+        <v>155.8</v>
       </c>
       <c r="H48" t="n">
-        <v>67.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-48.23</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>89.55</v>
+        <v>-113.93</v>
       </c>
       <c r="L48" t="n">
-        <v>101.71</v>
+        <v>138.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:33:01</t>
+          <t>06:25:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.18</v>
+        <v>5.76</v>
       </c>
       <c r="F49" t="n">
-        <v>15.59</v>
+        <v>14.76</v>
       </c>
       <c r="G49" t="n">
-        <v>165.4</v>
+        <v>161.1</v>
       </c>
       <c r="H49" t="n">
-        <v>71.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.6</v>
+        <v>-96.11</v>
       </c>
       <c r="K49" t="n">
-        <v>-86.43000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="L49" t="n">
-        <v>86.45</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:38:14</t>
+          <t>06:30:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.48</v>
+        <v>5.9</v>
       </c>
       <c r="F50" t="n">
-        <v>15.97</v>
+        <v>18.4</v>
       </c>
       <c r="G50" t="n">
-        <v>173.7</v>
+        <v>148</v>
       </c>
       <c r="H50" t="n">
-        <v>71.5</v>
+        <v>69.8</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>56.57</v>
+        <v>72.7</v>
       </c>
       <c r="K50" t="n">
-        <v>132.84</v>
+        <v>176.78</v>
       </c>
       <c r="L50" t="n">
-        <v>144.39</v>
+        <v>191.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:40:28</t>
+          <t>06:32:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.49</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>16.65</v>
+        <v>14.95</v>
       </c>
       <c r="G51" t="n">
-        <v>157.9</v>
+        <v>165.9</v>
       </c>
       <c r="H51" t="n">
-        <v>66.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-167.55</v>
+        <v>-35.57</v>
       </c>
       <c r="K51" t="n">
-        <v>91.95999999999999</v>
+        <v>170.77</v>
       </c>
       <c r="L51" t="n">
-        <v>191.13</v>
+        <v>174.44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:42:42</t>
+          <t>06:33:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.13</v>
+        <v>5.2</v>
       </c>
       <c r="F52" t="n">
-        <v>16.08</v>
+        <v>16.95</v>
       </c>
       <c r="G52" t="n">
-        <v>155</v>
+        <v>162.2</v>
       </c>
       <c r="H52" t="n">
-        <v>73.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="I52" t="n">
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-108.75</v>
+        <v>-1.6</v>
       </c>
       <c r="K52" t="n">
-        <v>-148.48</v>
+        <v>-184.23</v>
       </c>
       <c r="L52" t="n">
-        <v>184.04</v>
+        <v>184.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:47:44</t>
+          <t>06:38:05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7.47</v>
+        <v>5.94</v>
       </c>
       <c r="F53" t="n">
-        <v>16.33</v>
+        <v>16.64</v>
       </c>
       <c r="G53" t="n">
-        <v>151.2</v>
+        <v>148.4</v>
       </c>
       <c r="H53" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I53" t="n">
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>104.4</v>
+        <v>-114.88</v>
       </c>
       <c r="K53" t="n">
-        <v>277.75</v>
+        <v>198.56</v>
       </c>
       <c r="L53" t="n">
-        <v>296.73</v>
+        <v>229.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:49:03</t>
+          <t>06:40:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.17</v>
+        <v>6.03</v>
       </c>
       <c r="F54" t="n">
-        <v>16.5</v>
+        <v>18.27</v>
       </c>
       <c r="G54" t="n">
-        <v>153.2</v>
+        <v>152</v>
       </c>
       <c r="H54" t="n">
-        <v>68.8</v>
+        <v>61.9</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>66.38</v>
+        <v>230.77</v>
       </c>
       <c r="K54" t="n">
-        <v>233.72</v>
+        <v>104.82</v>
       </c>
       <c r="L54" t="n">
-        <v>242.97</v>
+        <v>253.46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:50:22</t>
+          <t>06:41:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.87</v>
+        <v>5.79</v>
       </c>
       <c r="F55" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="G55" t="n">
-        <v>161.2</v>
+        <v>154.4</v>
       </c>
       <c r="H55" t="n">
-        <v>70.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>143.43</v>
+        <v>289.92</v>
       </c>
       <c r="K55" t="n">
-        <v>-13.01</v>
+        <v>-230.19</v>
       </c>
       <c r="L55" t="n">
-        <v>144.02</v>
+        <v>370.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:55:48</t>
+          <t>06:46:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.1</v>
+        <v>6.23</v>
       </c>
       <c r="F56" t="n">
-        <v>15.76</v>
+        <v>15.08</v>
       </c>
       <c r="G56" t="n">
-        <v>170</v>
+        <v>161.6</v>
       </c>
       <c r="H56" t="n">
-        <v>70.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-238.49</v>
+        <v>-212.42</v>
       </c>
       <c r="K56" t="n">
-        <v>-350.17</v>
+        <v>88.25</v>
       </c>
       <c r="L56" t="n">
-        <v>423.67</v>
+        <v>230.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:56:52</t>
+          <t>06:47:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.24</v>
+        <v>5.84</v>
       </c>
       <c r="F57" t="n">
-        <v>16.22</v>
+        <v>15.62</v>
       </c>
       <c r="G57" t="n">
-        <v>160.5</v>
+        <v>168</v>
       </c>
       <c r="H57" t="n">
-        <v>68.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-63.5</v>
+        <v>-175.22</v>
       </c>
       <c r="K57" t="n">
-        <v>-364.48</v>
+        <v>-412.25</v>
       </c>
       <c r="L57" t="n">
-        <v>369.97</v>
+        <v>447.94</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:59:01</t>
+          <t>06:49:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.75</v>
+        <v>5.62</v>
       </c>
       <c r="F58" t="n">
-        <v>15.93</v>
+        <v>15.53</v>
       </c>
       <c r="G58" t="n">
-        <v>152.5</v>
+        <v>159.7</v>
       </c>
       <c r="H58" t="n">
-        <v>75.8</v>
+        <v>67.2</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>502.75</v>
+        <v>-448.79</v>
       </c>
       <c r="K58" t="n">
-        <v>-93.8</v>
+        <v>-90.72</v>
       </c>
       <c r="L58" t="n">
-        <v>511.43</v>
+        <v>457.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:09:37</t>
+          <t>07:02:14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.64</v>
+        <v>5.62</v>
       </c>
       <c r="F59" t="n">
-        <v>15.99</v>
+        <v>11.18</v>
       </c>
       <c r="G59" t="n">
-        <v>157.8</v>
+        <v>144.7</v>
       </c>
       <c r="H59" t="n">
-        <v>64</v>
+        <v>69.2</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-104.63</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.48</v>
+        <v>69.41</v>
       </c>
       <c r="L59" t="n">
-        <v>110.81</v>
+        <v>69.95999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:11:39</t>
+          <t>07:02:54</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.91</v>
+        <v>5.43</v>
       </c>
       <c r="F60" t="n">
-        <v>16.48</v>
+        <v>14.72</v>
       </c>
       <c r="G60" t="n">
-        <v>157.1</v>
+        <v>166.3</v>
       </c>
       <c r="H60" t="n">
-        <v>63.5</v>
+        <v>63.2</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-36.61</v>
+        <v>-28.71</v>
       </c>
       <c r="K60" t="n">
-        <v>-41.7</v>
+        <v>56.26</v>
       </c>
       <c r="L60" t="n">
-        <v>55.49</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:14:09</t>
+          <t>07:03:59</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="F61" t="n">
-        <v>15.58</v>
+        <v>15.92</v>
       </c>
       <c r="G61" t="n">
-        <v>159.8</v>
+        <v>154.2</v>
       </c>
       <c r="H61" t="n">
-        <v>68.7</v>
+        <v>71.2</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>71.69</v>
+        <v>-75.39</v>
       </c>
       <c r="K61" t="n">
-        <v>7.07</v>
+        <v>-8.67</v>
       </c>
       <c r="L61" t="n">
-        <v>72.04000000000001</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:17:28</t>
+          <t>07:08:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.2</v>
+        <v>6.79</v>
       </c>
       <c r="F62" t="n">
-        <v>16.19</v>
+        <v>18.63</v>
       </c>
       <c r="G62" t="n">
-        <v>150.2</v>
+        <v>160.6</v>
       </c>
       <c r="H62" t="n">
-        <v>72.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="I62" t="n">
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.07000000000000001</v>
+        <v>120.82</v>
       </c>
       <c r="K62" t="n">
-        <v>98.75</v>
+        <v>-75.22</v>
       </c>
       <c r="L62" t="n">
-        <v>98.75</v>
+        <v>142.32</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:18:53</t>
+          <t>07:09:38</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>7.1</v>
+        <v>7.56</v>
       </c>
       <c r="F63" t="n">
-        <v>15.99</v>
+        <v>18.63</v>
       </c>
       <c r="G63" t="n">
-        <v>165.1</v>
+        <v>175.4</v>
       </c>
       <c r="H63" t="n">
-        <v>66.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-103.59</v>
+        <v>-32.29</v>
       </c>
       <c r="K63" t="n">
-        <v>129.66</v>
+        <v>-160.27</v>
       </c>
       <c r="L63" t="n">
-        <v>165.96</v>
+        <v>163.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:20:49</t>
+          <t>07:11:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.49</v>
+        <v>5.86</v>
       </c>
       <c r="F64" t="n">
-        <v>16.07</v>
+        <v>17.77</v>
       </c>
       <c r="G64" t="n">
-        <v>149.4</v>
+        <v>152.7</v>
       </c>
       <c r="H64" t="n">
-        <v>78.7</v>
+        <v>79.2</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-22.05</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-25.32</v>
+        <v>-80.91</v>
       </c>
       <c r="L64" t="n">
-        <v>33.58</v>
+        <v>117.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:24:42</t>
+          <t>07:17:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.42</v>
+        <v>6.9</v>
       </c>
       <c r="F65" t="n">
-        <v>15.98</v>
+        <v>18.09</v>
       </c>
       <c r="G65" t="n">
-        <v>162</v>
+        <v>154.6</v>
       </c>
       <c r="H65" t="n">
-        <v>58.4</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>2.34</v>
+        <v>-8.16</v>
       </c>
       <c r="K65" t="n">
-        <v>-149.03</v>
+        <v>220.32</v>
       </c>
       <c r="L65" t="n">
-        <v>149.05</v>
+        <v>220.47</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:26:05</t>
+          <t>07:19:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="F66" t="n">
-        <v>16.12</v>
+        <v>16.11</v>
       </c>
       <c r="G66" t="n">
-        <v>168.5</v>
+        <v>154.7</v>
       </c>
       <c r="H66" t="n">
-        <v>68.3</v>
+        <v>67.5</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-126.69</v>
+        <v>-158.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-175.12</v>
+        <v>57.3</v>
       </c>
       <c r="L66" t="n">
-        <v>216.14</v>
+        <v>168.08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:28:19</t>
+          <t>07:19:31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.44</v>
+        <v>5.96</v>
       </c>
       <c r="F67" t="n">
-        <v>16.45</v>
+        <v>18.05</v>
       </c>
       <c r="G67" t="n">
-        <v>148.1</v>
+        <v>164.8</v>
       </c>
       <c r="H67" t="n">
-        <v>65.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-163.05</v>
+        <v>162.36</v>
       </c>
       <c r="K67" t="n">
-        <v>109.54</v>
+        <v>-46.34</v>
       </c>
       <c r="L67" t="n">
-        <v>196.43</v>
+        <v>168.84</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:33:35</t>
+          <t>07:23:28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>6.64</v>
+        <v>5.58</v>
       </c>
       <c r="F68" t="n">
-        <v>16.43</v>
+        <v>16.08</v>
       </c>
       <c r="G68" t="n">
-        <v>148.8</v>
+        <v>157</v>
       </c>
       <c r="H68" t="n">
-        <v>73.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-124.87</v>
+        <v>-216.86</v>
       </c>
       <c r="K68" t="n">
-        <v>346.37</v>
+        <v>-177.2</v>
       </c>
       <c r="L68" t="n">
-        <v>368.19</v>
+        <v>280.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:34:43</t>
+          <t>07:24:47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="F69" t="n">
-        <v>16.02</v>
+        <v>18.4</v>
       </c>
       <c r="G69" t="n">
-        <v>147.5</v>
+        <v>147.3</v>
       </c>
       <c r="H69" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-144.94</v>
+        <v>302.38</v>
       </c>
       <c r="K69" t="n">
-        <v>225.13</v>
+        <v>-19.07</v>
       </c>
       <c r="L69" t="n">
-        <v>267.75</v>
+        <v>302.98</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:35:42</t>
+          <t>07:26:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.64</v>
+        <v>6.36</v>
       </c>
       <c r="F70" t="n">
-        <v>16.61</v>
+        <v>17.36</v>
       </c>
       <c r="G70" t="n">
-        <v>146.5</v>
+        <v>151.8</v>
       </c>
       <c r="H70" t="n">
-        <v>64.7</v>
+        <v>75.3</v>
       </c>
       <c r="I70" t="n">
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>153.64</v>
+        <v>248.42</v>
       </c>
       <c r="K70" t="n">
-        <v>161.17</v>
+        <v>-91.83</v>
       </c>
       <c r="L70" t="n">
-        <v>222.67</v>
+        <v>264.85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:40:16</t>
+          <t>07:30:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.89</v>
+        <v>6.09</v>
       </c>
       <c r="F71" t="n">
-        <v>16.26</v>
+        <v>17.37</v>
       </c>
       <c r="G71" t="n">
-        <v>159.8</v>
+        <v>158.9</v>
       </c>
       <c r="H71" t="n">
-        <v>65</v>
+        <v>74.8</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>384.98</v>
+        <v>-293.58</v>
       </c>
       <c r="K71" t="n">
-        <v>-44.87</v>
+        <v>771.23</v>
       </c>
       <c r="L71" t="n">
-        <v>387.59</v>
+        <v>825.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:42:25</t>
+          <t>07:31:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.23</v>
+        <v>5.2</v>
       </c>
       <c r="F72" t="n">
-        <v>15.63</v>
+        <v>13.74</v>
       </c>
       <c r="G72" t="n">
-        <v>160.8</v>
+        <v>152</v>
       </c>
       <c r="H72" t="n">
-        <v>70.5</v>
+        <v>77.8</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-324.89</v>
+        <v>-112.98</v>
       </c>
       <c r="K72" t="n">
-        <v>-173.01</v>
+        <v>-419.78</v>
       </c>
       <c r="L72" t="n">
-        <v>368.08</v>
+        <v>434.72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:44:16</t>
+          <t>07:32:45</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.25</v>
+        <v>6.32</v>
       </c>
       <c r="F73" t="n">
-        <v>16.38</v>
+        <v>18.2</v>
       </c>
       <c r="G73" t="n">
-        <v>152</v>
+        <v>146.7</v>
       </c>
       <c r="H73" t="n">
-        <v>77.8</v>
+        <v>77</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-286.73</v>
+        <v>121.24</v>
       </c>
       <c r="K73" t="n">
-        <v>108.64</v>
+        <v>-373.78</v>
       </c>
       <c r="L73" t="n">
-        <v>306.62</v>
+        <v>392.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:52:45</t>
+          <t>07:44:16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.49</v>
+        <v>7.41</v>
       </c>
       <c r="F74" t="n">
-        <v>16.14</v>
+        <v>16.87</v>
       </c>
       <c r="G74" t="n">
-        <v>146.7</v>
+        <v>155.9</v>
       </c>
       <c r="H74" t="n">
-        <v>77</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>1.4</v>
+        <v>-53.91</v>
       </c>
       <c r="K74" t="n">
-        <v>130.22</v>
+        <v>-111.71</v>
       </c>
       <c r="L74" t="n">
-        <v>130.23</v>
+        <v>124.04</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:54:43</t>
+          <t>07:45:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.03</v>
+        <v>7.2</v>
       </c>
       <c r="F75" t="n">
-        <v>15.91</v>
+        <v>18.63</v>
       </c>
       <c r="G75" t="n">
-        <v>154.9</v>
+        <v>161.6</v>
       </c>
       <c r="H75" t="n">
-        <v>68.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>106.58</v>
+        <v>61.14</v>
       </c>
       <c r="K75" t="n">
-        <v>13.6</v>
+        <v>-95.81</v>
       </c>
       <c r="L75" t="n">
-        <v>107.44</v>
+        <v>113.66</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:56:39</t>
+          <t>07:45:58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.03</v>
+        <v>6.33</v>
       </c>
       <c r="F76" t="n">
-        <v>15.7</v>
+        <v>18.16</v>
       </c>
       <c r="G76" t="n">
-        <v>161.6</v>
+        <v>157.1</v>
       </c>
       <c r="H76" t="n">
-        <v>65.90000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-77.25</v>
+        <v>66.67</v>
       </c>
       <c r="K76" t="n">
-        <v>29.52</v>
+        <v>99.97</v>
       </c>
       <c r="L76" t="n">
-        <v>82.7</v>
+        <v>120.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:01:04</t>
+          <t>07:51:03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.16</v>
+        <v>6.9</v>
       </c>
       <c r="F77" t="n">
-        <v>16.56</v>
+        <v>18.57</v>
       </c>
       <c r="G77" t="n">
         <v>160.6</v>
       </c>
       <c r="H77" t="n">
-        <v>69.5</v>
+        <v>67.2</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>131.85</v>
+        <v>-124.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.16</v>
+        <v>57.04</v>
       </c>
       <c r="L77" t="n">
-        <v>133.09</v>
+        <v>136.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:03:09</t>
+          <t>07:52:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.81</v>
+        <v>5.78</v>
       </c>
       <c r="F78" t="n">
-        <v>15.66</v>
+        <v>15.14</v>
       </c>
       <c r="G78" t="n">
-        <v>160.6</v>
+        <v>150.6</v>
       </c>
       <c r="H78" t="n">
-        <v>67.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>59.52</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.51000000000001</v>
+        <v>-76.05</v>
       </c>
       <c r="L78" t="n">
-        <v>93.81999999999999</v>
+        <v>121.72</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:04:24</t>
+          <t>07:53:39</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.35</v>
+        <v>5.99</v>
       </c>
       <c r="F79" t="n">
-        <v>16.58</v>
+        <v>18</v>
       </c>
       <c r="G79" t="n">
-        <v>141.6</v>
+        <v>152.4</v>
       </c>
       <c r="H79" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>-24.36</v>
+        <v>44.69</v>
       </c>
       <c r="K79" t="n">
-        <v>-91.59999999999999</v>
+        <v>129.78</v>
       </c>
       <c r="L79" t="n">
-        <v>94.78</v>
+        <v>137.26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:09:33</t>
+          <t>07:56:54</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.46</v>
+        <v>6.29</v>
       </c>
       <c r="F80" t="n">
-        <v>16.18</v>
+        <v>18.42</v>
       </c>
       <c r="G80" t="n">
-        <v>152.4</v>
+        <v>140.8</v>
       </c>
       <c r="H80" t="n">
-        <v>71.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="I80" t="n">
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>206.32</v>
+        <v>85.72</v>
       </c>
       <c r="K80" t="n">
-        <v>21.11</v>
+        <v>-135.77</v>
       </c>
       <c r="L80" t="n">
-        <v>207.4</v>
+        <v>160.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:11:22</t>
+          <t>07:59:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.67</v>
+        <v>5.99</v>
       </c>
       <c r="F81" t="n">
-        <v>16.17</v>
+        <v>15.58</v>
       </c>
       <c r="G81" t="n">
-        <v>142</v>
+        <v>151.9</v>
       </c>
       <c r="H81" t="n">
-        <v>61.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-37.83</v>
+        <v>-77.56</v>
       </c>
       <c r="K81" t="n">
-        <v>140.24</v>
+        <v>-306.62</v>
       </c>
       <c r="L81" t="n">
-        <v>145.26</v>
+        <v>316.28</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:12:29</t>
+          <t>08:01:05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.71</v>
+        <v>4.82</v>
       </c>
       <c r="F82" t="n">
-        <v>16.18</v>
+        <v>11.92</v>
       </c>
       <c r="G82" t="n">
-        <v>151.9</v>
+        <v>161.8</v>
       </c>
       <c r="H82" t="n">
-        <v>66.09999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-175.62</v>
+        <v>-0.29</v>
       </c>
       <c r="K82" t="n">
-        <v>-227.89</v>
+        <v>-2.1</v>
       </c>
       <c r="L82" t="n">
-        <v>287.71</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:18:04</t>
+          <t>08:05:23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.28</v>
+        <v>6.31</v>
       </c>
       <c r="F83" t="n">
-        <v>16.16</v>
+        <v>18.63</v>
       </c>
       <c r="G83" t="n">
-        <v>169.2</v>
+        <v>153.3</v>
       </c>
       <c r="H83" t="n">
-        <v>71.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>52.15</v>
+        <v>377.49</v>
       </c>
       <c r="K83" t="n">
-        <v>-413.6</v>
+        <v>34.74</v>
       </c>
       <c r="L83" t="n">
-        <v>416.87</v>
+        <v>379.08</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:20:06</t>
+          <t>08:07:02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.68</v>
+        <v>6.63</v>
       </c>
       <c r="F84" t="n">
-        <v>15.75</v>
+        <v>18.63</v>
       </c>
       <c r="G84" t="n">
-        <v>153.3</v>
+        <v>156.8</v>
       </c>
       <c r="H84" t="n">
-        <v>76.7</v>
+        <v>65.2</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>179.86</v>
+        <v>512.48</v>
       </c>
       <c r="K84" t="n">
-        <v>193.01</v>
+        <v>37.08</v>
       </c>
       <c r="L84" t="n">
-        <v>263.82</v>
+        <v>513.8200000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:21:40</t>
+          <t>08:08:35</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.89</v>
+        <v>5.06</v>
       </c>
       <c r="F85" t="n">
-        <v>17.14</v>
+        <v>15.15</v>
       </c>
       <c r="G85" t="n">
-        <v>154</v>
+        <v>162.1</v>
       </c>
       <c r="H85" t="n">
-        <v>69.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-336.34</v>
+        <v>124.4</v>
       </c>
       <c r="K85" t="n">
-        <v>-32.22</v>
+        <v>-254.09</v>
       </c>
       <c r="L85" t="n">
-        <v>337.88</v>
+        <v>282.91</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:25:50</t>
+          <t>08:13:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.44</v>
+        <v>5.92</v>
       </c>
       <c r="F86" t="n">
-        <v>15.82</v>
+        <v>17.85</v>
       </c>
       <c r="G86" t="n">
-        <v>162.1</v>
+        <v>156.6</v>
       </c>
       <c r="H86" t="n">
-        <v>65</v>
+        <v>69.5</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-374.47</v>
+        <v>-189.72</v>
       </c>
       <c r="K86" t="n">
-        <v>-298.25</v>
+        <v>-564.88</v>
       </c>
       <c r="L86" t="n">
-        <v>478.73</v>
+        <v>595.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:27:09</t>
+          <t>08:15:40</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.74</v>
+        <v>6.5</v>
       </c>
       <c r="F87" t="n">
-        <v>15.88</v>
+        <v>18.63</v>
       </c>
       <c r="G87" t="n">
-        <v>157.5</v>
+        <v>163.8</v>
       </c>
       <c r="H87" t="n">
-        <v>69.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>250.26</v>
+        <v>422.3</v>
       </c>
       <c r="K87" t="n">
-        <v>489.02</v>
+        <v>314.77</v>
       </c>
       <c r="L87" t="n">
-        <v>549.34</v>
+        <v>526.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:28:19</t>
+          <t>08:17:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.57</v>
+        <v>7.03</v>
       </c>
       <c r="F88" t="n">
-        <v>16.39</v>
+        <v>18.13</v>
       </c>
       <c r="G88" t="n">
-        <v>163.8</v>
+        <v>149.4</v>
       </c>
       <c r="H88" t="n">
-        <v>64.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>364.13</v>
+        <v>528.77</v>
       </c>
       <c r="K88" t="n">
-        <v>444.07</v>
+        <v>-502.64</v>
       </c>
       <c r="L88" t="n">
-        <v>574.27</v>
+        <v>729.55</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.09</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>79.58</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>79.90000000000001</v>
+        <v>90.45999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>66.44</v>
+        <v>74.86</v>
       </c>
       <c r="K15" t="n">
-        <v>36.79</v>
+        <v>41.45</v>
       </c>
       <c r="L15" t="n">
-        <v>75.94</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>109.33</v>
+        <v>123.28</v>
       </c>
       <c r="K16" t="n">
-        <v>33.17</v>
+        <v>37.4</v>
       </c>
       <c r="L16" t="n">
-        <v>114.25</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>125.91</v>
+        <v>138.05</v>
       </c>
       <c r="K17" t="n">
-        <v>12.71</v>
+        <v>13.93</v>
       </c>
       <c r="L17" t="n">
-        <v>126.55</v>
+        <v>138.75</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>12.15</v>
+        <v>12.79</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.63</v>
+        <v>-3.82</v>
       </c>
       <c r="L18" t="n">
-        <v>12.68</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-79.14</v>
+        <v>-89.51000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>48.83</v>
+        <v>55.23</v>
       </c>
       <c r="L19" t="n">
-        <v>92.98999999999999</v>
+        <v>105.18</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>198.33</v>
+        <v>224.78</v>
       </c>
       <c r="K20" t="n">
-        <v>-71.75</v>
+        <v>-81.31</v>
       </c>
       <c r="L20" t="n">
-        <v>210.91</v>
+        <v>239.04</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>192.92</v>
+        <v>215.84</v>
       </c>
       <c r="K21" t="n">
-        <v>-31.83</v>
+        <v>-35.61</v>
       </c>
       <c r="L21" t="n">
-        <v>195.53</v>
+        <v>218.76</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>143.82</v>
+        <v>156.37</v>
       </c>
       <c r="K22" t="n">
-        <v>-97.25</v>
+        <v>-105.74</v>
       </c>
       <c r="L22" t="n">
-        <v>173.61</v>
+        <v>188.77</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>47.5</v>
+        <v>53.06</v>
       </c>
       <c r="K23" t="n">
-        <v>-228.06</v>
+        <v>-254.76</v>
       </c>
       <c r="L23" t="n">
-        <v>232.95</v>
+        <v>260.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-112.18</v>
+        <v>-129.01</v>
       </c>
       <c r="K24" t="n">
-        <v>-327.57</v>
+        <v>-376.73</v>
       </c>
       <c r="L24" t="n">
-        <v>346.25</v>
+        <v>398.21</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>11.44</v>
+        <v>12.68</v>
       </c>
       <c r="K25" t="n">
-        <v>-185.08</v>
+        <v>-205.17</v>
       </c>
       <c r="L25" t="n">
-        <v>185.43</v>
+        <v>205.56</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>215.97</v>
+        <v>232.18</v>
       </c>
       <c r="K26" t="n">
-        <v>-389.01</v>
+        <v>-418.21</v>
       </c>
       <c r="L26" t="n">
-        <v>444.94</v>
+        <v>478.34</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>196.34</v>
+        <v>224.23</v>
       </c>
       <c r="K27" t="n">
-        <v>276.88</v>
+        <v>316.22</v>
       </c>
       <c r="L27" t="n">
-        <v>339.43</v>
+        <v>387.65</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>269.34</v>
+        <v>311.95</v>
       </c>
       <c r="K28" t="n">
-        <v>191.98</v>
+        <v>222.35</v>
       </c>
       <c r="L28" t="n">
-        <v>330.75</v>
+        <v>383.09</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>111.35</v>
+        <v>125.64</v>
       </c>
       <c r="K29" t="n">
-        <v>-27.59</v>
+        <v>-31.13</v>
       </c>
       <c r="L29" t="n">
-        <v>114.72</v>
+        <v>129.44</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>94.47</v>
+        <v>104.97</v>
       </c>
       <c r="K30" t="n">
-        <v>-53.02</v>
+        <v>-58.91</v>
       </c>
       <c r="L30" t="n">
-        <v>108.34</v>
+        <v>120.38</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-84.59</v>
+        <v>-90.19</v>
       </c>
       <c r="K31" t="n">
-        <v>-65.72</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>107.12</v>
+        <v>114.21</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>-99.73999999999999</v>
+        <v>-102.15</v>
       </c>
       <c r="L32" t="n">
-        <v>99.81</v>
+        <v>102.22</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-122.55</v>
+        <v>-138.16</v>
       </c>
       <c r="K33" t="n">
-        <v>-31.23</v>
+        <v>-35.21</v>
       </c>
       <c r="L33" t="n">
-        <v>126.46</v>
+        <v>142.57</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>44.51</v>
+        <v>47.76</v>
       </c>
       <c r="K34" t="n">
-        <v>69.59999999999999</v>
+        <v>74.67</v>
       </c>
       <c r="L34" t="n">
-        <v>82.61</v>
+        <v>88.63</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-35.46</v>
+        <v>-40.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-168.79</v>
+        <v>-191.36</v>
       </c>
       <c r="L35" t="n">
-        <v>172.48</v>
+        <v>195.53</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.46</v>
+        <v>-16.25</v>
       </c>
       <c r="K36" t="n">
-        <v>-176.98</v>
+        <v>-185.97</v>
       </c>
       <c r="L36" t="n">
-        <v>177.66</v>
+        <v>186.68</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>72.5</v>
+        <v>81.06</v>
       </c>
       <c r="K37" t="n">
-        <v>-187.04</v>
+        <v>-209.14</v>
       </c>
       <c r="L37" t="n">
-        <v>200.6</v>
+        <v>224.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-131.63</v>
+        <v>-145.1</v>
       </c>
       <c r="K38" t="n">
-        <v>-179.25</v>
+        <v>-197.6</v>
       </c>
       <c r="L38" t="n">
-        <v>222.39</v>
+        <v>245.15</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>301.59</v>
+        <v>327.21</v>
       </c>
       <c r="K39" t="n">
-        <v>62.81</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>308.06</v>
+        <v>334.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>101.06</v>
+        <v>111.3</v>
       </c>
       <c r="K40" t="n">
-        <v>168.21</v>
+        <v>185.25</v>
       </c>
       <c r="L40" t="n">
-        <v>196.23</v>
+        <v>216.12</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-45.34</v>
+        <v>-49.8</v>
       </c>
       <c r="K41" t="n">
-        <v>-600.4400000000001</v>
+        <v>-659.5700000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>602.15</v>
+        <v>661.45</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>341.77</v>
+        <v>366.81</v>
       </c>
       <c r="K42" t="n">
-        <v>-46.55</v>
+        <v>-49.96</v>
       </c>
       <c r="L42" t="n">
-        <v>344.93</v>
+        <v>370.2</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>539.28</v>
+        <v>594.16</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.81</v>
+        <v>-4.2</v>
       </c>
       <c r="L43" t="n">
-        <v>539.29</v>
+        <v>594.17</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>106.39</v>
+        <v>114.86</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.78</v>
+        <v>-54.82</v>
       </c>
       <c r="L44" t="n">
-        <v>117.89</v>
+        <v>127.27</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>48.9</v>
+        <v>52.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-88.72</v>
+        <v>-96.06</v>
       </c>
       <c r="L45" t="n">
-        <v>101.31</v>
+        <v>109.69</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>31.72</v>
+        <v>33.83</v>
       </c>
       <c r="K46" t="n">
-        <v>-33.13</v>
+        <v>-35.34</v>
       </c>
       <c r="L46" t="n">
-        <v>45.87</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>99.42</v>
+        <v>112.3</v>
       </c>
       <c r="K47" t="n">
-        <v>54.31</v>
+        <v>61.34</v>
       </c>
       <c r="L47" t="n">
-        <v>113.29</v>
+        <v>127.96</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>78.43000000000001</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-113.93</v>
+        <v>-123.13</v>
       </c>
       <c r="L48" t="n">
-        <v>138.31</v>
+        <v>149.48</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-96.11</v>
+        <v>-106.22</v>
       </c>
       <c r="K49" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="L49" t="n">
-        <v>96.11</v>
+        <v>106.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>72.7</v>
+        <v>81.27</v>
       </c>
       <c r="K50" t="n">
-        <v>176.78</v>
+        <v>197.6</v>
       </c>
       <c r="L50" t="n">
-        <v>191.15</v>
+        <v>213.66</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-35.57</v>
+        <v>-39.8</v>
       </c>
       <c r="K51" t="n">
-        <v>170.77</v>
+        <v>191.09</v>
       </c>
       <c r="L51" t="n">
-        <v>174.44</v>
+        <v>195.19</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.6</v>
+        <v>-1.82</v>
       </c>
       <c r="K52" t="n">
-        <v>-184.23</v>
+        <v>-208.88</v>
       </c>
       <c r="L52" t="n">
-        <v>184.24</v>
+        <v>208.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-114.88</v>
+        <v>-124.79</v>
       </c>
       <c r="K53" t="n">
-        <v>198.56</v>
+        <v>215.68</v>
       </c>
       <c r="L53" t="n">
-        <v>229.4</v>
+        <v>249.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>230.77</v>
+        <v>265.61</v>
       </c>
       <c r="K54" t="n">
-        <v>104.82</v>
+        <v>120.64</v>
       </c>
       <c r="L54" t="n">
-        <v>253.46</v>
+        <v>291.73</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>289.92</v>
+        <v>309.71</v>
       </c>
       <c r="K55" t="n">
-        <v>-230.19</v>
+        <v>-245.89</v>
       </c>
       <c r="L55" t="n">
-        <v>370.19</v>
+        <v>395.45</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-212.42</v>
+        <v>-240.8</v>
       </c>
       <c r="K56" t="n">
-        <v>88.25</v>
+        <v>100.04</v>
       </c>
       <c r="L56" t="n">
-        <v>230.02</v>
+        <v>260.75</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-175.22</v>
+        <v>-189.3</v>
       </c>
       <c r="K57" t="n">
-        <v>-412.25</v>
+        <v>-445.36</v>
       </c>
       <c r="L57" t="n">
-        <v>447.94</v>
+        <v>483.92</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-448.79</v>
+        <v>-507.56</v>
       </c>
       <c r="K58" t="n">
-        <v>-90.72</v>
+        <v>-102.6</v>
       </c>
       <c r="L58" t="n">
-        <v>457.86</v>
+        <v>517.83</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>8.699999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>69.41</v>
+        <v>76.03</v>
       </c>
       <c r="L59" t="n">
-        <v>69.95999999999999</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-28.71</v>
+        <v>-30.53</v>
       </c>
       <c r="K60" t="n">
-        <v>56.26</v>
+        <v>59.83</v>
       </c>
       <c r="L60" t="n">
-        <v>63.16</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-75.39</v>
+        <v>-78.98</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.67</v>
+        <v>-9.08</v>
       </c>
       <c r="L61" t="n">
-        <v>75.89</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>120.82</v>
+        <v>132.71</v>
       </c>
       <c r="K62" t="n">
-        <v>-75.22</v>
+        <v>-82.62</v>
       </c>
       <c r="L62" t="n">
-        <v>142.32</v>
+        <v>156.33</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-32.29</v>
+        <v>-35.35</v>
       </c>
       <c r="K63" t="n">
-        <v>-160.27</v>
+        <v>-175.43</v>
       </c>
       <c r="L63" t="n">
-        <v>163.49</v>
+        <v>178.96</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>85.09999999999999</v>
+        <v>93.98</v>
       </c>
       <c r="K64" t="n">
-        <v>-80.91</v>
+        <v>-89.36</v>
       </c>
       <c r="L64" t="n">
-        <v>117.42</v>
+        <v>129.68</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.16</v>
+        <v>-9.24</v>
       </c>
       <c r="K65" t="n">
-        <v>220.32</v>
+        <v>249.37</v>
       </c>
       <c r="L65" t="n">
-        <v>220.47</v>
+        <v>249.54</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-158.02</v>
+        <v>-171.74</v>
       </c>
       <c r="K66" t="n">
-        <v>57.3</v>
+        <v>62.28</v>
       </c>
       <c r="L66" t="n">
-        <v>168.08</v>
+        <v>182.68</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>162.36</v>
+        <v>176.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-46.34</v>
+        <v>-50.32</v>
       </c>
       <c r="L67" t="n">
-        <v>168.84</v>
+        <v>183.36</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-216.86</v>
+        <v>-242.63</v>
       </c>
       <c r="K68" t="n">
-        <v>-177.2</v>
+        <v>-198.26</v>
       </c>
       <c r="L68" t="n">
-        <v>280.05</v>
+        <v>313.33</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>302.38</v>
+        <v>343.25</v>
       </c>
       <c r="K69" t="n">
-        <v>-19.07</v>
+        <v>-21.65</v>
       </c>
       <c r="L69" t="n">
-        <v>302.98</v>
+        <v>343.94</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>248.42</v>
+        <v>278.36</v>
       </c>
       <c r="K70" t="n">
-        <v>-91.83</v>
+        <v>-102.89</v>
       </c>
       <c r="L70" t="n">
-        <v>264.85</v>
+        <v>296.76</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-293.58</v>
+        <v>-322.71</v>
       </c>
       <c r="K71" t="n">
-        <v>771.23</v>
+        <v>847.73</v>
       </c>
       <c r="L71" t="n">
-        <v>825.22</v>
+        <v>907.08</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-112.98</v>
+        <v>-129.32</v>
       </c>
       <c r="K72" t="n">
-        <v>-419.78</v>
+        <v>-480.52</v>
       </c>
       <c r="L72" t="n">
-        <v>434.72</v>
+        <v>497.62</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>121.24</v>
+        <v>137.48</v>
       </c>
       <c r="K73" t="n">
-        <v>-373.78</v>
+        <v>-423.84</v>
       </c>
       <c r="L73" t="n">
-        <v>392.95</v>
+        <v>445.58</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-53.91</v>
+        <v>-56.46</v>
       </c>
       <c r="K74" t="n">
-        <v>-111.71</v>
+        <v>-116.98</v>
       </c>
       <c r="L74" t="n">
-        <v>124.04</v>
+        <v>129.89</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>61.14</v>
+        <v>61.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-95.81</v>
+        <v>-95.90000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>113.66</v>
+        <v>113.76</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>66.67</v>
+        <v>72.36</v>
       </c>
       <c r="K76" t="n">
-        <v>99.97</v>
+        <v>108.51</v>
       </c>
       <c r="L76" t="n">
-        <v>120.16</v>
+        <v>130.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-124.1</v>
+        <v>-136.25</v>
       </c>
       <c r="K77" t="n">
-        <v>57.04</v>
+        <v>62.62</v>
       </c>
       <c r="L77" t="n">
-        <v>136.58</v>
+        <v>149.95</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>95.04000000000001</v>
+        <v>100.68</v>
       </c>
       <c r="K78" t="n">
-        <v>-76.05</v>
+        <v>-80.56999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>121.72</v>
+        <v>128.95</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>44.69</v>
+        <v>47.27</v>
       </c>
       <c r="K79" t="n">
-        <v>129.78</v>
+        <v>137.29</v>
       </c>
       <c r="L79" t="n">
-        <v>137.26</v>
+        <v>145.2</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>85.72</v>
+        <v>93.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-135.77</v>
+        <v>-147.39</v>
       </c>
       <c r="L80" t="n">
-        <v>160.57</v>
+        <v>174.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-77.56</v>
+        <v>-84.23</v>
       </c>
       <c r="K81" t="n">
-        <v>-306.62</v>
+        <v>-332.97</v>
       </c>
       <c r="L81" t="n">
-        <v>316.28</v>
+        <v>343.46</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="K82" t="n">
-        <v>-2.1</v>
+        <v>-2.35</v>
       </c>
       <c r="L82" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>377.49</v>
+        <v>422.94</v>
       </c>
       <c r="K83" t="n">
-        <v>34.74</v>
+        <v>38.92</v>
       </c>
       <c r="L83" t="n">
-        <v>379.08</v>
+        <v>424.73</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>512.48</v>
+        <v>590.4400000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>37.08</v>
+        <v>42.72</v>
       </c>
       <c r="L84" t="n">
-        <v>513.8200000000001</v>
+        <v>591.98</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>124.4</v>
+        <v>139</v>
       </c>
       <c r="K85" t="n">
-        <v>-254.09</v>
+        <v>-283.92</v>
       </c>
       <c r="L85" t="n">
-        <v>282.91</v>
+        <v>316.12</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-189.72</v>
+        <v>-205.02</v>
       </c>
       <c r="K86" t="n">
-        <v>-564.88</v>
+        <v>-610.4400000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>595.89</v>
+        <v>643.95</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>422.3</v>
+        <v>464.82</v>
       </c>
       <c r="K87" t="n">
-        <v>314.77</v>
+        <v>346.46</v>
       </c>
       <c r="L87" t="n">
-        <v>526.71</v>
+        <v>579.73</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>528.77</v>
+        <v>582.85</v>
       </c>
       <c r="K88" t="n">
-        <v>-502.64</v>
+        <v>-554.05</v>
       </c>
       <c r="L88" t="n">
-        <v>729.55</v>
+        <v>804.17</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.31</v>
+        <v>5.35</v>
       </c>
       <c r="F14" t="n">
-        <v>9.16</v>
+        <v>14.59</v>
       </c>
       <c r="G14" t="n">
-        <v>155.5</v>
+        <v>151.9</v>
       </c>
       <c r="H14" t="n">
-        <v>68.90000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.029999999999999</v>
+        <v>-50.3</v>
       </c>
       <c r="K14" t="n">
-        <v>90.09999999999999</v>
+        <v>-72.94</v>
       </c>
       <c r="L14" t="n">
-        <v>90.45999999999999</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:46:31</t>
+          <t>04:45:50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4</v>
+        <v>4.97</v>
       </c>
       <c r="F15" t="n">
-        <v>12.74</v>
+        <v>12.01</v>
       </c>
       <c r="G15" t="n">
-        <v>163.4</v>
+        <v>170.6</v>
       </c>
       <c r="H15" t="n">
-        <v>74.3</v>
+        <v>56.1</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>74.86</v>
+        <v>-56.42</v>
       </c>
       <c r="K15" t="n">
-        <v>41.45</v>
+        <v>-87.23</v>
       </c>
       <c r="L15" t="n">
-        <v>85.58</v>
+        <v>103.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:47:21</t>
+          <t>04:47:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.23</v>
+        <v>5.39</v>
       </c>
       <c r="F16" t="n">
-        <v>12.65</v>
+        <v>15.53</v>
       </c>
       <c r="G16" t="n">
-        <v>143.1</v>
+        <v>161.2</v>
       </c>
       <c r="H16" t="n">
-        <v>70.40000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>123.28</v>
+        <v>38.3</v>
       </c>
       <c r="K16" t="n">
-        <v>37.4</v>
+        <v>-98.11</v>
       </c>
       <c r="L16" t="n">
-        <v>128.83</v>
+        <v>105.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:51:45</t>
+          <t>04:52:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.47</v>
+        <v>5.54</v>
       </c>
       <c r="F17" t="n">
-        <v>13.37</v>
+        <v>12.05</v>
       </c>
       <c r="G17" t="n">
-        <v>162.2</v>
+        <v>135.9</v>
       </c>
       <c r="H17" t="n">
-        <v>68.2</v>
+        <v>48.8</v>
       </c>
       <c r="I17" t="n">
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>138.05</v>
+        <v>42.62</v>
       </c>
       <c r="K17" t="n">
-        <v>13.93</v>
+        <v>-132.51</v>
       </c>
       <c r="L17" t="n">
-        <v>138.75</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:53:00</t>
+          <t>04:54:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.95</v>
+        <v>5.52</v>
       </c>
       <c r="F18" t="n">
-        <v>8.779999999999999</v>
+        <v>13.53</v>
       </c>
       <c r="G18" t="n">
-        <v>157.6</v>
+        <v>166.4</v>
       </c>
       <c r="H18" t="n">
-        <v>70</v>
+        <v>55.7</v>
       </c>
       <c r="I18" t="n">
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>12.79</v>
+        <v>-12.84</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.82</v>
+        <v>-153.51</v>
       </c>
       <c r="L18" t="n">
-        <v>13.35</v>
+        <v>154.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:54:47</t>
+          <t>04:55:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="F19" t="n">
-        <v>12.84</v>
+        <v>12.42</v>
       </c>
       <c r="G19" t="n">
-        <v>148.2</v>
+        <v>161</v>
       </c>
       <c r="H19" t="n">
-        <v>76.8</v>
+        <v>68.3</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-89.51000000000001</v>
+        <v>137.26</v>
       </c>
       <c r="K19" t="n">
-        <v>55.23</v>
+        <v>-34.76</v>
       </c>
       <c r="L19" t="n">
-        <v>105.18</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:59:13</t>
+          <t>04:59:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.49</v>
+        <v>5.55</v>
       </c>
       <c r="F20" t="n">
-        <v>11.82</v>
+        <v>16.09</v>
       </c>
       <c r="G20" t="n">
-        <v>154.8</v>
+        <v>151.9</v>
       </c>
       <c r="H20" t="n">
-        <v>75.7</v>
+        <v>50</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>224.78</v>
+        <v>181.11</v>
       </c>
       <c r="K20" t="n">
-        <v>-81.31</v>
+        <v>74.27</v>
       </c>
       <c r="L20" t="n">
-        <v>239.04</v>
+        <v>195.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:00:33</t>
+          <t>05:01:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.12</v>
+        <v>4.96</v>
       </c>
       <c r="F21" t="n">
-        <v>15.95</v>
+        <v>12.89</v>
       </c>
       <c r="G21" t="n">
-        <v>169.1</v>
+        <v>156.9</v>
       </c>
       <c r="H21" t="n">
-        <v>68.3</v>
+        <v>26.5</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>215.84</v>
+        <v>181.15</v>
       </c>
       <c r="K21" t="n">
-        <v>-35.61</v>
+        <v>124.15</v>
       </c>
       <c r="L21" t="n">
-        <v>218.76</v>
+        <v>219.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:02:19</t>
+          <t>05:02:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
       <c r="F22" t="n">
-        <v>10.64</v>
+        <v>11.4</v>
       </c>
       <c r="G22" t="n">
-        <v>156.9</v>
+        <v>170.5</v>
       </c>
       <c r="H22" t="n">
-        <v>77</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>156.37</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-105.74</v>
+        <v>-176.23</v>
       </c>
       <c r="L22" t="n">
-        <v>188.77</v>
+        <v>197.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:06:44</t>
+          <t>05:06:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.97</v>
+        <v>5.24</v>
       </c>
       <c r="F23" t="n">
-        <v>10.71</v>
+        <v>14.21</v>
       </c>
       <c r="G23" t="n">
-        <v>150.8</v>
+        <v>150.6</v>
       </c>
       <c r="H23" t="n">
-        <v>67</v>
+        <v>66.3</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>53.06</v>
+        <v>-204.31</v>
       </c>
       <c r="K23" t="n">
-        <v>-254.76</v>
+        <v>-187.78</v>
       </c>
       <c r="L23" t="n">
-        <v>260.22</v>
+        <v>277.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:09:22</t>
+          <t>05:08:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.63</v>
+        <v>5.66</v>
       </c>
       <c r="F24" t="n">
-        <v>14.14</v>
+        <v>15.09</v>
       </c>
       <c r="G24" t="n">
-        <v>168.2</v>
+        <v>151.2</v>
       </c>
       <c r="H24" t="n">
-        <v>65.90000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-129.01</v>
+        <v>105.74</v>
       </c>
       <c r="K24" t="n">
-        <v>-376.73</v>
+        <v>-276.69</v>
       </c>
       <c r="L24" t="n">
-        <v>398.21</v>
+        <v>296.21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:11:16</t>
+          <t>05:09:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.36</v>
+        <v>5.65</v>
       </c>
       <c r="F25" t="n">
-        <v>12.88</v>
+        <v>12.59</v>
       </c>
       <c r="G25" t="n">
-        <v>163.2</v>
+        <v>162</v>
       </c>
       <c r="H25" t="n">
-        <v>68.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>12.68</v>
+        <v>220.14</v>
       </c>
       <c r="K25" t="n">
-        <v>-205.17</v>
+        <v>-314.1</v>
       </c>
       <c r="L25" t="n">
-        <v>205.56</v>
+        <v>383.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:15:52</t>
+          <t>05:14:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.85</v>
+        <v>5.06</v>
       </c>
       <c r="F26" t="n">
-        <v>13.61</v>
+        <v>14.86</v>
       </c>
       <c r="G26" t="n">
-        <v>154.5</v>
+        <v>163.6</v>
       </c>
       <c r="H26" t="n">
-        <v>67.8</v>
+        <v>47.5</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>232.18</v>
+        <v>-121</v>
       </c>
       <c r="K26" t="n">
-        <v>-418.21</v>
+        <v>-273.68</v>
       </c>
       <c r="L26" t="n">
-        <v>478.34</v>
+        <v>299.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:18:08</t>
+          <t>05:16:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.8</v>
+        <v>4.68</v>
       </c>
       <c r="F27" t="n">
-        <v>12.32</v>
+        <v>11.55</v>
       </c>
       <c r="G27" t="n">
-        <v>164.1</v>
+        <v>174.1</v>
       </c>
       <c r="H27" t="n">
-        <v>65.09999999999999</v>
+        <v>45.4</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>224.23</v>
+        <v>57.36</v>
       </c>
       <c r="K27" t="n">
-        <v>316.22</v>
+        <v>-286.25</v>
       </c>
       <c r="L27" t="n">
-        <v>387.65</v>
+        <v>291.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:19:45</t>
+          <t>05:17:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.91</v>
+        <v>5.69</v>
       </c>
       <c r="F28" t="n">
-        <v>13.72</v>
+        <v>16.65</v>
       </c>
       <c r="G28" t="n">
-        <v>149.7</v>
+        <v>163.9</v>
       </c>
       <c r="H28" t="n">
-        <v>69.2</v>
+        <v>53.9</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>311.95</v>
+        <v>-212.89</v>
       </c>
       <c r="K28" t="n">
-        <v>222.35</v>
+        <v>-501.24</v>
       </c>
       <c r="L28" t="n">
-        <v>383.09</v>
+        <v>544.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:30:18</t>
+          <t>05:31:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.09</v>
+        <v>5.33</v>
       </c>
       <c r="F29" t="n">
-        <v>13.17</v>
+        <v>12.18</v>
       </c>
       <c r="G29" t="n">
-        <v>158.1</v>
+        <v>145.4</v>
       </c>
       <c r="H29" t="n">
-        <v>67.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>125.64</v>
+        <v>64.14</v>
       </c>
       <c r="K29" t="n">
-        <v>-31.13</v>
+        <v>-99.08</v>
       </c>
       <c r="L29" t="n">
-        <v>129.44</v>
+        <v>118.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:32:41</t>
+          <t>05:33:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.55</v>
+        <v>4.87</v>
       </c>
       <c r="F30" t="n">
-        <v>12.31</v>
+        <v>13.01</v>
       </c>
       <c r="G30" t="n">
-        <v>148.8</v>
+        <v>166.5</v>
       </c>
       <c r="H30" t="n">
-        <v>60.7</v>
+        <v>66.7</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>104.97</v>
+        <v>92.44</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.91</v>
+        <v>-53.89</v>
       </c>
       <c r="L30" t="n">
-        <v>120.38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:33:25</t>
+          <t>05:36:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="F31" t="n">
-        <v>11.8</v>
+        <v>13.5</v>
       </c>
       <c r="G31" t="n">
-        <v>167.2</v>
+        <v>153.9</v>
       </c>
       <c r="H31" t="n">
-        <v>75.2</v>
+        <v>34.2</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>-90.19</v>
+        <v>144.32</v>
       </c>
       <c r="K31" t="n">
-        <v>-70.06999999999999</v>
+        <v>6.87</v>
       </c>
       <c r="L31" t="n">
-        <v>114.21</v>
+        <v>144.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:38:29</t>
+          <t>05:40:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.06</v>
+        <v>5.4</v>
       </c>
       <c r="F32" t="n">
-        <v>14.78</v>
+        <v>13.09</v>
       </c>
       <c r="G32" t="n">
-        <v>165.7</v>
+        <v>156.3</v>
       </c>
       <c r="H32" t="n">
-        <v>68</v>
+        <v>42.3</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>3.85</v>
+        <v>141.12</v>
       </c>
       <c r="K32" t="n">
-        <v>-102.15</v>
+        <v>-69.76000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>102.22</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:40:27</t>
+          <t>05:41:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="F33" t="n">
-        <v>16.4</v>
+        <v>8.98</v>
       </c>
       <c r="G33" t="n">
-        <v>165.5</v>
+        <v>150.1</v>
       </c>
       <c r="H33" t="n">
-        <v>67.3</v>
+        <v>69</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-138.16</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-35.21</v>
+        <v>161.97</v>
       </c>
       <c r="L33" t="n">
-        <v>142.57</v>
+        <v>186.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:42:07</t>
+          <t>05:43:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>6.1</v>
+        <v>5.83</v>
       </c>
       <c r="F34" t="n">
-        <v>15.4</v>
+        <v>14.29</v>
       </c>
       <c r="G34" t="n">
-        <v>159.8</v>
+        <v>136.7</v>
       </c>
       <c r="H34" t="n">
-        <v>70.09999999999999</v>
+        <v>34.6</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>47.76</v>
+        <v>-64.02</v>
       </c>
       <c r="K34" t="n">
-        <v>74.67</v>
+        <v>-175.52</v>
       </c>
       <c r="L34" t="n">
-        <v>88.63</v>
+        <v>186.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:46:41</t>
+          <t>05:48:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.27</v>
+        <v>5.65</v>
       </c>
       <c r="F35" t="n">
-        <v>13.15</v>
+        <v>16.87</v>
       </c>
       <c r="G35" t="n">
-        <v>148.9</v>
+        <v>152.9</v>
       </c>
       <c r="H35" t="n">
-        <v>72.8</v>
+        <v>50.9</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-40.2</v>
+        <v>192.05</v>
       </c>
       <c r="K35" t="n">
-        <v>-191.36</v>
+        <v>55.09</v>
       </c>
       <c r="L35" t="n">
-        <v>195.53</v>
+        <v>199.79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:47:50</t>
+          <t>05:49:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>7.08</v>
+        <v>5.19</v>
       </c>
       <c r="F36" t="n">
-        <v>17.61</v>
+        <v>14.09</v>
       </c>
       <c r="G36" t="n">
-        <v>163.4</v>
+        <v>151.4</v>
       </c>
       <c r="H36" t="n">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.25</v>
+        <v>209.31</v>
       </c>
       <c r="K36" t="n">
-        <v>-185.97</v>
+        <v>100.33</v>
       </c>
       <c r="L36" t="n">
-        <v>186.68</v>
+        <v>232.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:49:45</t>
+          <t>05:52:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.6</v>
+        <v>5.21</v>
       </c>
       <c r="F37" t="n">
-        <v>13.67</v>
+        <v>16.48</v>
       </c>
       <c r="G37" t="n">
-        <v>161.1</v>
+        <v>150.1</v>
       </c>
       <c r="H37" t="n">
-        <v>69.5</v>
+        <v>56.9</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>81.06</v>
+        <v>165.73</v>
       </c>
       <c r="K37" t="n">
-        <v>-209.14</v>
+        <v>11.54</v>
       </c>
       <c r="L37" t="n">
-        <v>224.3</v>
+        <v>166.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:53:41</t>
+          <t>05:55:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.55</v>
+        <v>6.08</v>
       </c>
       <c r="F38" t="n">
-        <v>17.49</v>
+        <v>17.9</v>
       </c>
       <c r="G38" t="n">
-        <v>153.9</v>
+        <v>149.9</v>
       </c>
       <c r="H38" t="n">
-        <v>70</v>
+        <v>29.7</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-145.1</v>
+        <v>445.28</v>
       </c>
       <c r="K38" t="n">
-        <v>-197.6</v>
+        <v>97.44</v>
       </c>
       <c r="L38" t="n">
-        <v>245.15</v>
+        <v>455.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:55:06</t>
+          <t>05:56:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="F39" t="n">
-        <v>15.5</v>
+        <v>13.46</v>
       </c>
       <c r="G39" t="n">
-        <v>155.9</v>
+        <v>143.5</v>
       </c>
       <c r="H39" t="n">
-        <v>70.5</v>
+        <v>39.2</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>327.21</v>
+        <v>-62.31</v>
       </c>
       <c r="K39" t="n">
-        <v>68.15000000000001</v>
+        <v>-558.72</v>
       </c>
       <c r="L39" t="n">
-        <v>334.23</v>
+        <v>562.1799999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:56:46</t>
+          <t>05:59:02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.17</v>
+        <v>5.65</v>
       </c>
       <c r="F40" t="n">
-        <v>11.56</v>
+        <v>12.61</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4</v>
+        <v>162.9</v>
       </c>
       <c r="H40" t="n">
-        <v>66.7</v>
+        <v>57</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>111.3</v>
+        <v>-28.09</v>
       </c>
       <c r="K40" t="n">
-        <v>185.25</v>
+        <v>-303.77</v>
       </c>
       <c r="L40" t="n">
-        <v>216.12</v>
+        <v>305.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:00:26</t>
+          <t>06:03:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.91</v>
+        <v>5.23</v>
       </c>
       <c r="F41" t="n">
-        <v>17.44</v>
+        <v>12.71</v>
       </c>
       <c r="G41" t="n">
-        <v>156</v>
+        <v>152.3</v>
       </c>
       <c r="H41" t="n">
-        <v>66.7</v>
+        <v>8.9</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-49.8</v>
+        <v>44.97</v>
       </c>
       <c r="K41" t="n">
-        <v>-659.5700000000001</v>
+        <v>-468.3</v>
       </c>
       <c r="L41" t="n">
-        <v>661.45</v>
+        <v>470.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:01:12</t>
+          <t>06:05:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.6</v>
+        <v>5.23</v>
       </c>
       <c r="F42" t="n">
-        <v>11.57</v>
+        <v>13.82</v>
       </c>
       <c r="G42" t="n">
-        <v>148.2</v>
+        <v>163.3</v>
       </c>
       <c r="H42" t="n">
-        <v>65.8</v>
+        <v>39.6</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>366.81</v>
+        <v>-260.03</v>
       </c>
       <c r="K42" t="n">
-        <v>-49.96</v>
+        <v>317.48</v>
       </c>
       <c r="L42" t="n">
-        <v>370.2</v>
+        <v>410.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:03:08</t>
+          <t>06:07:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.85</v>
+        <v>5.63</v>
       </c>
       <c r="F43" t="n">
-        <v>18.63</v>
+        <v>16.1</v>
       </c>
       <c r="G43" t="n">
-        <v>153.8</v>
+        <v>161.1</v>
       </c>
       <c r="H43" t="n">
-        <v>69.5</v>
+        <v>44.9</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>594.16</v>
+        <v>205.48</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.2</v>
+        <v>-381.01</v>
       </c>
       <c r="L43" t="n">
-        <v>594.17</v>
+        <v>432.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:14:09</t>
+          <t>06:18:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.54</v>
+        <v>5.68</v>
       </c>
       <c r="F44" t="n">
-        <v>14.93</v>
+        <v>13.16</v>
       </c>
       <c r="G44" t="n">
-        <v>158.7</v>
+        <v>150.5</v>
       </c>
       <c r="H44" t="n">
-        <v>68.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>114.86</v>
+        <v>116.82</v>
       </c>
       <c r="K44" t="n">
-        <v>-54.82</v>
+        <v>181.59</v>
       </c>
       <c r="L44" t="n">
-        <v>127.27</v>
+        <v>215.92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:16:30</t>
+          <t>06:20:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.86</v>
+        <v>4.89</v>
       </c>
       <c r="F45" t="n">
-        <v>12.13</v>
+        <v>13.68</v>
       </c>
       <c r="G45" t="n">
-        <v>147.5</v>
+        <v>155.5</v>
       </c>
       <c r="H45" t="n">
-        <v>64.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>52.94</v>
+        <v>-63.27</v>
       </c>
       <c r="K45" t="n">
-        <v>-96.06</v>
+        <v>-98.45</v>
       </c>
       <c r="L45" t="n">
-        <v>109.69</v>
+        <v>117.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:17:54</t>
+          <t>06:21:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.76</v>
+        <v>6.11</v>
       </c>
       <c r="F46" t="n">
-        <v>14.02</v>
+        <v>14.61</v>
       </c>
       <c r="G46" t="n">
-        <v>150.8</v>
+        <v>151.2</v>
       </c>
       <c r="H46" t="n">
-        <v>70</v>
+        <v>74.8</v>
       </c>
       <c r="I46" t="n">
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>33.83</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-35.34</v>
+        <v>-118.14</v>
       </c>
       <c r="L46" t="n">
-        <v>48.92</v>
+        <v>150.44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:23:25</t>
+          <t>06:24:51</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.87</v>
+        <v>5.92</v>
       </c>
       <c r="F47" t="n">
-        <v>16.52</v>
+        <v>13.04</v>
       </c>
       <c r="G47" t="n">
-        <v>153.7</v>
+        <v>167.9</v>
       </c>
       <c r="H47" t="n">
-        <v>65.59999999999999</v>
+        <v>37.4</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>112.3</v>
+        <v>-184.09</v>
       </c>
       <c r="K47" t="n">
-        <v>61.34</v>
+        <v>-59.73</v>
       </c>
       <c r="L47" t="n">
-        <v>127.96</v>
+        <v>193.53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:25:13</t>
+          <t>06:25:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="F48" t="n">
-        <v>15.97</v>
+        <v>13.5</v>
       </c>
       <c r="G48" t="n">
-        <v>155.8</v>
+        <v>166.1</v>
       </c>
       <c r="H48" t="n">
-        <v>67.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>84.76000000000001</v>
+        <v>-189.55</v>
       </c>
       <c r="K48" t="n">
-        <v>-123.13</v>
+        <v>-104.24</v>
       </c>
       <c r="L48" t="n">
-        <v>149.48</v>
+        <v>216.32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:25:59</t>
+          <t>06:26:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.76</v>
+        <v>5.28</v>
       </c>
       <c r="F49" t="n">
-        <v>14.76</v>
+        <v>14.52</v>
       </c>
       <c r="G49" t="n">
-        <v>161.1</v>
+        <v>157.1</v>
       </c>
       <c r="H49" t="n">
-        <v>73.59999999999999</v>
+        <v>27.9</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-106.22</v>
+        <v>-19.38</v>
       </c>
       <c r="K49" t="n">
-        <v>0.19</v>
+        <v>-154.05</v>
       </c>
       <c r="L49" t="n">
-        <v>106.22</v>
+        <v>155.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:30:50</t>
+          <t>06:30:52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.9</v>
+        <v>5.57</v>
       </c>
       <c r="F50" t="n">
-        <v>18.4</v>
+        <v>14.06</v>
       </c>
       <c r="G50" t="n">
-        <v>148</v>
+        <v>162.9</v>
       </c>
       <c r="H50" t="n">
-        <v>69.8</v>
+        <v>34.1</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>81.27</v>
+        <v>-124.03</v>
       </c>
       <c r="K50" t="n">
-        <v>197.6</v>
+        <v>-228.04</v>
       </c>
       <c r="L50" t="n">
-        <v>213.66</v>
+        <v>259.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:32:39</t>
+          <t>06:32:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="F51" t="n">
-        <v>14.95</v>
+        <v>16.64</v>
       </c>
       <c r="G51" t="n">
-        <v>165.9</v>
+        <v>152.4</v>
       </c>
       <c r="H51" t="n">
-        <v>64.90000000000001</v>
+        <v>42.7</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-39.8</v>
+        <v>-100.15</v>
       </c>
       <c r="K51" t="n">
-        <v>191.09</v>
+        <v>-186.11</v>
       </c>
       <c r="L51" t="n">
-        <v>195.19</v>
+        <v>211.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:33:28</t>
+          <t>06:33:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.2</v>
+        <v>6.64</v>
       </c>
       <c r="F52" t="n">
-        <v>16.95</v>
+        <v>18.63</v>
       </c>
       <c r="G52" t="n">
-        <v>162.2</v>
+        <v>172.6</v>
       </c>
       <c r="H52" t="n">
-        <v>70.3</v>
+        <v>49.7</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.82</v>
+        <v>-193.94</v>
       </c>
       <c r="K52" t="n">
-        <v>-208.88</v>
+        <v>-116.23</v>
       </c>
       <c r="L52" t="n">
-        <v>208.89</v>
+        <v>226.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:38:05</t>
+          <t>06:38:28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.94</v>
+        <v>6.25</v>
       </c>
       <c r="F53" t="n">
-        <v>16.64</v>
+        <v>12.84</v>
       </c>
       <c r="G53" t="n">
-        <v>148.4</v>
+        <v>167.6</v>
       </c>
       <c r="H53" t="n">
-        <v>72</v>
+        <v>50.6</v>
       </c>
       <c r="I53" t="n">
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-124.79</v>
+        <v>-280.57</v>
       </c>
       <c r="K53" t="n">
-        <v>215.68</v>
+        <v>-456.26</v>
       </c>
       <c r="L53" t="n">
-        <v>249.18</v>
+        <v>535.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:40:25</t>
+          <t>06:40:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.03</v>
+        <v>7.17</v>
       </c>
       <c r="F54" t="n">
-        <v>18.27</v>
+        <v>17.5</v>
       </c>
       <c r="G54" t="n">
-        <v>152</v>
+        <v>172.6</v>
       </c>
       <c r="H54" t="n">
-        <v>61.9</v>
+        <v>53.8</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>265.61</v>
+        <v>330.18</v>
       </c>
       <c r="K54" t="n">
-        <v>120.64</v>
+        <v>-94.25</v>
       </c>
       <c r="L54" t="n">
-        <v>291.73</v>
+        <v>343.37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:41:05</t>
+          <t>06:42:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.79</v>
+        <v>5.81</v>
       </c>
       <c r="F55" t="n">
-        <v>16.6</v>
+        <v>16.98</v>
       </c>
       <c r="G55" t="n">
-        <v>154.4</v>
+        <v>147.2</v>
       </c>
       <c r="H55" t="n">
-        <v>63.5</v>
+        <v>36.3</v>
       </c>
       <c r="I55" t="n">
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>309.71</v>
+        <v>65.52</v>
       </c>
       <c r="K55" t="n">
-        <v>-245.89</v>
+        <v>-396.95</v>
       </c>
       <c r="L55" t="n">
-        <v>395.45</v>
+        <v>402.32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:46:14</t>
+          <t>06:47:09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.23</v>
+        <v>5.72</v>
       </c>
       <c r="F56" t="n">
-        <v>15.08</v>
+        <v>14.91</v>
       </c>
       <c r="G56" t="n">
-        <v>161.6</v>
+        <v>151.7</v>
       </c>
       <c r="H56" t="n">
-        <v>64.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-240.8</v>
+        <v>437.23</v>
       </c>
       <c r="K56" t="n">
-        <v>100.04</v>
+        <v>-234.61</v>
       </c>
       <c r="L56" t="n">
-        <v>260.75</v>
+        <v>496.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:47:23</t>
+          <t>06:48:53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.84</v>
+        <v>6.13</v>
       </c>
       <c r="F57" t="n">
-        <v>15.62</v>
+        <v>18.41</v>
       </c>
       <c r="G57" t="n">
-        <v>168</v>
+        <v>164.5</v>
       </c>
       <c r="H57" t="n">
-        <v>76.2</v>
+        <v>48.8</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-189.3</v>
+        <v>138.47</v>
       </c>
       <c r="K57" t="n">
-        <v>-445.36</v>
+        <v>-417.37</v>
       </c>
       <c r="L57" t="n">
-        <v>483.92</v>
+        <v>439.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:49:39</t>
+          <t>06:50:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.62</v>
+        <v>6.68</v>
       </c>
       <c r="F58" t="n">
-        <v>15.53</v>
+        <v>18.27</v>
       </c>
       <c r="G58" t="n">
-        <v>159.7</v>
+        <v>156.4</v>
       </c>
       <c r="H58" t="n">
-        <v>67.2</v>
+        <v>74.2</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-507.56</v>
+        <v>236.4</v>
       </c>
       <c r="K58" t="n">
-        <v>-102.6</v>
+        <v>-457.07</v>
       </c>
       <c r="L58" t="n">
-        <v>517.83</v>
+        <v>514.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:02:14</t>
+          <t>07:03:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.62</v>
+        <v>6.18</v>
       </c>
       <c r="F59" t="n">
-        <v>11.18</v>
+        <v>15.53</v>
       </c>
       <c r="G59" t="n">
-        <v>144.7</v>
+        <v>158.3</v>
       </c>
       <c r="H59" t="n">
-        <v>69.2</v>
+        <v>47.9</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>9.529999999999999</v>
+        <v>147.08</v>
       </c>
       <c r="K59" t="n">
-        <v>76.03</v>
+        <v>-55.97</v>
       </c>
       <c r="L59" t="n">
-        <v>76.62</v>
+        <v>157.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:02:54</t>
+          <t>07:05:28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.43</v>
+        <v>6.19</v>
       </c>
       <c r="F60" t="n">
-        <v>14.72</v>
+        <v>16.83</v>
       </c>
       <c r="G60" t="n">
-        <v>166.3</v>
+        <v>162.5</v>
       </c>
       <c r="H60" t="n">
-        <v>63.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-30.53</v>
+        <v>98.61</v>
       </c>
       <c r="K60" t="n">
-        <v>59.83</v>
+        <v>-129.75</v>
       </c>
       <c r="L60" t="n">
-        <v>67.17</v>
+        <v>162.97</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:03:59</t>
+          <t>07:06:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.09</v>
+        <v>5.81</v>
       </c>
       <c r="F61" t="n">
-        <v>15.92</v>
+        <v>13.93</v>
       </c>
       <c r="G61" t="n">
-        <v>154.2</v>
+        <v>153</v>
       </c>
       <c r="H61" t="n">
-        <v>71.2</v>
+        <v>72.2</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-78.98</v>
+        <v>96.73</v>
       </c>
       <c r="K61" t="n">
-        <v>-9.08</v>
+        <v>-79.38</v>
       </c>
       <c r="L61" t="n">
-        <v>79.5</v>
+        <v>125.13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:08:50</t>
+          <t>07:11:17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.79</v>
+        <v>6.18</v>
       </c>
       <c r="F62" t="n">
-        <v>18.63</v>
+        <v>18.03</v>
       </c>
       <c r="G62" t="n">
-        <v>160.6</v>
+        <v>165.8</v>
       </c>
       <c r="H62" t="n">
-        <v>69</v>
+        <v>73.3</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>132.71</v>
+        <v>117.68</v>
       </c>
       <c r="K62" t="n">
-        <v>-82.62</v>
+        <v>-112.57</v>
       </c>
       <c r="L62" t="n">
-        <v>156.33</v>
+        <v>162.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:09:38</t>
+          <t>07:12:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>7.56</v>
+        <v>6.92</v>
       </c>
       <c r="F63" t="n">
         <v>18.63</v>
       </c>
       <c r="G63" t="n">
-        <v>175.4</v>
+        <v>165.1</v>
       </c>
       <c r="H63" t="n">
-        <v>64.90000000000001</v>
+        <v>38.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-35.35</v>
+        <v>-205.19</v>
       </c>
       <c r="K63" t="n">
-        <v>-175.43</v>
+        <v>-164.74</v>
       </c>
       <c r="L63" t="n">
-        <v>178.96</v>
+        <v>263.14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:11:52</t>
+          <t>07:13:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.86</v>
+        <v>5.72</v>
       </c>
       <c r="F64" t="n">
-        <v>17.77</v>
+        <v>15.84</v>
       </c>
       <c r="G64" t="n">
-        <v>152.7</v>
+        <v>155.1</v>
       </c>
       <c r="H64" t="n">
-        <v>79.2</v>
+        <v>48.5</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>93.98</v>
+        <v>-177.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-89.36</v>
+        <v>-55.49</v>
       </c>
       <c r="L64" t="n">
-        <v>129.68</v>
+        <v>185.86</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:17:16</t>
+          <t>07:17:25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>18.09</v>
+        <v>18.3</v>
       </c>
       <c r="G65" t="n">
-        <v>154.6</v>
+        <v>145</v>
       </c>
       <c r="H65" t="n">
-        <v>71.90000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.24</v>
+        <v>293.35</v>
       </c>
       <c r="K65" t="n">
-        <v>249.37</v>
+        <v>-18.65</v>
       </c>
       <c r="L65" t="n">
-        <v>249.54</v>
+        <v>293.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:19:05</t>
+          <t>07:19:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.25</v>
+        <v>5.04</v>
       </c>
       <c r="F66" t="n">
-        <v>16.11</v>
+        <v>13.61</v>
       </c>
       <c r="G66" t="n">
-        <v>154.7</v>
+        <v>148.2</v>
       </c>
       <c r="H66" t="n">
-        <v>67.5</v>
+        <v>13.6</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-171.74</v>
+        <v>126.85</v>
       </c>
       <c r="K66" t="n">
-        <v>62.28</v>
+        <v>-118.77</v>
       </c>
       <c r="L66" t="n">
-        <v>182.68</v>
+        <v>173.77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:19:31</t>
+          <t>07:19:57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.96</v>
+        <v>6.54</v>
       </c>
       <c r="F67" t="n">
-        <v>18.05</v>
+        <v>18.63</v>
       </c>
       <c r="G67" t="n">
-        <v>164.8</v>
+        <v>156.8</v>
       </c>
       <c r="H67" t="n">
-        <v>69</v>
+        <v>41.6</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>176.32</v>
+        <v>-192.11</v>
       </c>
       <c r="K67" t="n">
-        <v>-50.32</v>
+        <v>162.17</v>
       </c>
       <c r="L67" t="n">
-        <v>183.36</v>
+        <v>251.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:23:28</t>
+          <t>07:23:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.58</v>
+        <v>5.76</v>
       </c>
       <c r="F68" t="n">
-        <v>16.08</v>
+        <v>16.65</v>
       </c>
       <c r="G68" t="n">
-        <v>157</v>
+        <v>155.6</v>
       </c>
       <c r="H68" t="n">
-        <v>67</v>
+        <v>28.7</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-242.63</v>
+        <v>229.45</v>
       </c>
       <c r="K68" t="n">
-        <v>-198.26</v>
+        <v>156.88</v>
       </c>
       <c r="L68" t="n">
-        <v>313.33</v>
+        <v>277.95</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:24:47</t>
+          <t>07:24:26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.8</v>
+        <v>6.63</v>
       </c>
       <c r="F69" t="n">
-        <v>18.4</v>
+        <v>18.63</v>
       </c>
       <c r="G69" t="n">
-        <v>147.3</v>
+        <v>154.9</v>
       </c>
       <c r="H69" t="n">
-        <v>65.7</v>
+        <v>35.6</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>343.25</v>
+        <v>126.51</v>
       </c>
       <c r="K69" t="n">
-        <v>-21.65</v>
+        <v>-363.92</v>
       </c>
       <c r="L69" t="n">
-        <v>343.94</v>
+        <v>385.28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:26:23</t>
+          <t>07:25:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.36</v>
+        <v>6.08</v>
       </c>
       <c r="F70" t="n">
-        <v>17.36</v>
+        <v>16.24</v>
       </c>
       <c r="G70" t="n">
-        <v>151.8</v>
+        <v>153.3</v>
       </c>
       <c r="H70" t="n">
-        <v>75.3</v>
+        <v>59.3</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>278.36</v>
+        <v>-373.24</v>
       </c>
       <c r="K70" t="n">
-        <v>-102.89</v>
+        <v>-94.91</v>
       </c>
       <c r="L70" t="n">
-        <v>296.76</v>
+        <v>385.12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:30:35</t>
+          <t>07:31:07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.09</v>
+        <v>6.47</v>
       </c>
       <c r="F71" t="n">
-        <v>17.37</v>
+        <v>16.09</v>
       </c>
       <c r="G71" t="n">
-        <v>158.9</v>
+        <v>147.8</v>
       </c>
       <c r="H71" t="n">
-        <v>74.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-322.71</v>
+        <v>432.28</v>
       </c>
       <c r="K71" t="n">
-        <v>847.73</v>
+        <v>54.07</v>
       </c>
       <c r="L71" t="n">
-        <v>907.08</v>
+        <v>435.64</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:31:40</t>
+          <t>07:31:59</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.2</v>
+        <v>6.06</v>
       </c>
       <c r="F72" t="n">
-        <v>13.74</v>
+        <v>15.53</v>
       </c>
       <c r="G72" t="n">
-        <v>152</v>
+        <v>150.9</v>
       </c>
       <c r="H72" t="n">
-        <v>77.8</v>
+        <v>22</v>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-129.32</v>
+        <v>367.51</v>
       </c>
       <c r="K72" t="n">
-        <v>-480.52</v>
+        <v>-25.24</v>
       </c>
       <c r="L72" t="n">
-        <v>497.62</v>
+        <v>368.37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:32:45</t>
+          <t>07:33:16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>6.32</v>
+        <v>5.59</v>
       </c>
       <c r="F73" t="n">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="G73" t="n">
-        <v>146.7</v>
+        <v>156.6</v>
       </c>
       <c r="H73" t="n">
-        <v>77</v>
+        <v>94.5</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>137.48</v>
+        <v>-366.62</v>
       </c>
       <c r="K73" t="n">
-        <v>-423.84</v>
+        <v>-212.9</v>
       </c>
       <c r="L73" t="n">
-        <v>445.58</v>
+        <v>423.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:44:16</t>
+          <t>07:46:21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7.41</v>
+        <v>6.1</v>
       </c>
       <c r="F74" t="n">
-        <v>16.87</v>
+        <v>15.8</v>
       </c>
       <c r="G74" t="n">
-        <v>155.9</v>
+        <v>161.3</v>
       </c>
       <c r="H74" t="n">
-        <v>68.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>-56.46</v>
+        <v>148.33</v>
       </c>
       <c r="K74" t="n">
-        <v>-116.98</v>
+        <v>17.3</v>
       </c>
       <c r="L74" t="n">
-        <v>129.89</v>
+        <v>149.34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:45:15</t>
+          <t>07:47:36</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>7.2</v>
+        <v>5.98</v>
       </c>
       <c r="F75" t="n">
-        <v>18.63</v>
+        <v>16.32</v>
       </c>
       <c r="G75" t="n">
-        <v>161.6</v>
+        <v>165.7</v>
       </c>
       <c r="H75" t="n">
-        <v>65.90000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>61.19</v>
+        <v>-101.16</v>
       </c>
       <c r="K75" t="n">
-        <v>-95.90000000000001</v>
+        <v>-110.71</v>
       </c>
       <c r="L75" t="n">
-        <v>113.76</v>
+        <v>149.97</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:45:58</t>
+          <t>07:48:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.33</v>
+        <v>5.74</v>
       </c>
       <c r="F76" t="n">
-        <v>18.16</v>
+        <v>14.47</v>
       </c>
       <c r="G76" t="n">
-        <v>157.1</v>
+        <v>143</v>
       </c>
       <c r="H76" t="n">
-        <v>60.6</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>72.36</v>
+        <v>10.19</v>
       </c>
       <c r="K76" t="n">
-        <v>108.51</v>
+        <v>-106.15</v>
       </c>
       <c r="L76" t="n">
-        <v>130.42</v>
+        <v>106.63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:51:03</t>
+          <t>07:54:14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.9</v>
+        <v>7.23</v>
       </c>
       <c r="F77" t="n">
-        <v>18.57</v>
+        <v>18.63</v>
       </c>
       <c r="G77" t="n">
-        <v>160.6</v>
+        <v>151.3</v>
       </c>
       <c r="H77" t="n">
-        <v>67.2</v>
+        <v>56</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-136.25</v>
+        <v>143.12</v>
       </c>
       <c r="K77" t="n">
-        <v>62.62</v>
+        <v>-151.54</v>
       </c>
       <c r="L77" t="n">
-        <v>149.95</v>
+        <v>208.44</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:52:53</t>
+          <t>07:56:25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.78</v>
+        <v>6.43</v>
       </c>
       <c r="F78" t="n">
-        <v>15.14</v>
+        <v>18.63</v>
       </c>
       <c r="G78" t="n">
-        <v>150.6</v>
+        <v>148.5</v>
       </c>
       <c r="H78" t="n">
-        <v>70.59999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>100.68</v>
+        <v>146.15</v>
       </c>
       <c r="K78" t="n">
-        <v>-80.56999999999999</v>
+        <v>-82.20999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>128.95</v>
+        <v>167.68</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:53:39</t>
+          <t>07:58:32</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.99</v>
+        <v>5.39</v>
       </c>
       <c r="F79" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="G79" t="n">
+        <v>156.7</v>
+      </c>
+      <c r="H79" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="I79" t="n">
         <v>18</v>
       </c>
-      <c r="G79" t="n">
-        <v>152.4</v>
-      </c>
-      <c r="H79" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="I79" t="n">
-        <v>19</v>
-      </c>
       <c r="J79" t="n">
-        <v>47.27</v>
+        <v>56.74</v>
       </c>
       <c r="K79" t="n">
-        <v>137.29</v>
+        <v>-122.13</v>
       </c>
       <c r="L79" t="n">
-        <v>145.2</v>
+        <v>134.67</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:56:54</t>
+          <t>08:04:20</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.29</v>
+        <v>5.8</v>
       </c>
       <c r="F80" t="n">
-        <v>18.42</v>
+        <v>17.18</v>
       </c>
       <c r="G80" t="n">
-        <v>140.8</v>
+        <v>147.5</v>
       </c>
       <c r="H80" t="n">
-        <v>68.7</v>
+        <v>41</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>93.06</v>
+        <v>-146.61</v>
       </c>
       <c r="K80" t="n">
-        <v>-147.39</v>
+        <v>-112.26</v>
       </c>
       <c r="L80" t="n">
-        <v>174.31</v>
+        <v>184.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:59:00</t>
+          <t>08:06:21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.99</v>
+        <v>6.37</v>
       </c>
       <c r="F81" t="n">
-        <v>15.58</v>
+        <v>17.83</v>
       </c>
       <c r="G81" t="n">
-        <v>151.9</v>
+        <v>152</v>
       </c>
       <c r="H81" t="n">
-        <v>66.09999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-84.23</v>
+        <v>195.95</v>
       </c>
       <c r="K81" t="n">
-        <v>-332.97</v>
+        <v>25.27</v>
       </c>
       <c r="L81" t="n">
-        <v>343.46</v>
+        <v>197.58</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:01:05</t>
+          <t>08:08:22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.82</v>
+        <v>5.8</v>
       </c>
       <c r="F82" t="n">
-        <v>11.92</v>
+        <v>15.81</v>
       </c>
       <c r="G82" t="n">
-        <v>161.8</v>
+        <v>154.1</v>
       </c>
       <c r="H82" t="n">
-        <v>61.4</v>
+        <v>65.3</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.32</v>
+        <v>116.93</v>
       </c>
       <c r="K82" t="n">
-        <v>-2.35</v>
+        <v>-205.04</v>
       </c>
       <c r="L82" t="n">
-        <v>2.37</v>
+        <v>236.04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:05:23</t>
+          <t>08:12:11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.31</v>
+        <v>5.56</v>
       </c>
       <c r="F83" t="n">
-        <v>18.63</v>
+        <v>15.31</v>
       </c>
       <c r="G83" t="n">
-        <v>153.3</v>
+        <v>150.3</v>
       </c>
       <c r="H83" t="n">
-        <v>76.7</v>
+        <v>67.5</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>422.94</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>38.92</v>
+        <v>-214.19</v>
       </c>
       <c r="L83" t="n">
-        <v>424.73</v>
+        <v>225.07</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:07:02</t>
+          <t>08:13:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.63</v>
+        <v>6.08</v>
       </c>
       <c r="F84" t="n">
-        <v>18.63</v>
+        <v>15.52</v>
       </c>
       <c r="G84" t="n">
-        <v>156.8</v>
+        <v>159.1</v>
       </c>
       <c r="H84" t="n">
-        <v>65.2</v>
+        <v>61.1</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>590.4400000000001</v>
+        <v>-204.57</v>
       </c>
       <c r="K84" t="n">
-        <v>42.72</v>
+        <v>-291.17</v>
       </c>
       <c r="L84" t="n">
-        <v>591.98</v>
+        <v>355.85</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:08:35</t>
+          <t>08:14:44</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.06</v>
+        <v>6.97</v>
       </c>
       <c r="F85" t="n">
-        <v>15.15</v>
+        <v>18.63</v>
       </c>
       <c r="G85" t="n">
-        <v>162.1</v>
+        <v>159.9</v>
       </c>
       <c r="H85" t="n">
-        <v>65</v>
+        <v>63.5</v>
       </c>
       <c r="I85" t="n">
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>139</v>
+        <v>-141.21</v>
       </c>
       <c r="K85" t="n">
-        <v>-283.92</v>
+        <v>-156.91</v>
       </c>
       <c r="L85" t="n">
-        <v>316.12</v>
+        <v>211.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:13:26</t>
+          <t>08:19:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.92</v>
+        <v>6.24</v>
       </c>
       <c r="F86" t="n">
-        <v>17.85</v>
+        <v>17.42</v>
       </c>
       <c r="G86" t="n">
-        <v>156.6</v>
+        <v>158.5</v>
       </c>
       <c r="H86" t="n">
-        <v>69.5</v>
+        <v>76</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-205.02</v>
+        <v>417.5</v>
       </c>
       <c r="K86" t="n">
-        <v>-610.4400000000001</v>
+        <v>-176.7</v>
       </c>
       <c r="L86" t="n">
-        <v>643.95</v>
+        <v>453.35</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:15:40</t>
+          <t>08:21:51</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.5</v>
+        <v>6.69</v>
       </c>
       <c r="F87" t="n">
-        <v>18.63</v>
+        <v>18.12</v>
       </c>
       <c r="G87" t="n">
-        <v>163.8</v>
+        <v>159.8</v>
       </c>
       <c r="H87" t="n">
-        <v>64.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="I87" t="n">
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>464.82</v>
+        <v>518.55</v>
       </c>
       <c r="K87" t="n">
-        <v>346.46</v>
+        <v>141.14</v>
       </c>
       <c r="L87" t="n">
-        <v>579.73</v>
+        <v>537.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:17:10</t>
+          <t>08:23:55</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>7.03</v>
+        <v>6.53</v>
       </c>
       <c r="F88" t="n">
-        <v>18.13</v>
+        <v>18.23</v>
       </c>
       <c r="G88" t="n">
-        <v>149.4</v>
+        <v>152.5</v>
       </c>
       <c r="H88" t="n">
-        <v>70</v>
+        <v>75.5</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>582.85</v>
+        <v>186.87</v>
       </c>
       <c r="K88" t="n">
-        <v>-554.05</v>
+        <v>-317.86</v>
       </c>
       <c r="L88" t="n">
-        <v>804.17</v>
+        <v>368.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.35</v>
+        <v>5.26</v>
       </c>
       <c r="F14" t="n">
-        <v>14.59</v>
+        <v>13.57</v>
       </c>
       <c r="G14" t="n">
-        <v>151.9</v>
+        <v>157.8</v>
       </c>
       <c r="H14" t="n">
-        <v>40.6</v>
+        <v>49.2</v>
       </c>
       <c r="I14" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-50.3</v>
+        <v>-121.53</v>
       </c>
       <c r="K14" t="n">
-        <v>-72.94</v>
+        <v>-51.78</v>
       </c>
       <c r="L14" t="n">
-        <v>88.59999999999999</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:45:50</t>
+          <t>04:46:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.97</v>
+        <v>4.75</v>
       </c>
       <c r="F15" t="n">
-        <v>12.01</v>
+        <v>13.23</v>
       </c>
       <c r="G15" t="n">
-        <v>170.6</v>
+        <v>156.4</v>
       </c>
       <c r="H15" t="n">
-        <v>56.1</v>
+        <v>50.1</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-56.42</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-87.23</v>
+        <v>-88.08</v>
       </c>
       <c r="L15" t="n">
-        <v>103.89</v>
+        <v>117.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:47:57</t>
+          <t>04:48:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.39</v>
+        <v>5.09</v>
       </c>
       <c r="F16" t="n">
-        <v>15.53</v>
+        <v>14.11</v>
       </c>
       <c r="G16" t="n">
-        <v>161.2</v>
+        <v>155.5</v>
       </c>
       <c r="H16" t="n">
-        <v>34.5</v>
+        <v>19.9</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>38.3</v>
+        <v>-102.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-98.11</v>
+        <v>81.38</v>
       </c>
       <c r="L16" t="n">
-        <v>105.32</v>
+        <v>130.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:39</t>
+          <t>04:53:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.54</v>
+        <v>6.6</v>
       </c>
       <c r="F17" t="n">
-        <v>12.05</v>
+        <v>14.98</v>
       </c>
       <c r="G17" t="n">
-        <v>135.9</v>
+        <v>144.1</v>
       </c>
       <c r="H17" t="n">
-        <v>48.8</v>
+        <v>68</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>42.62</v>
+        <v>228.59</v>
       </c>
       <c r="K17" t="n">
-        <v>-132.51</v>
+        <v>-100.67</v>
       </c>
       <c r="L17" t="n">
-        <v>139.2</v>
+        <v>249.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:17</t>
+          <t>04:56:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.52</v>
+        <v>3.89</v>
       </c>
       <c r="F18" t="n">
-        <v>13.53</v>
+        <v>11.04</v>
       </c>
       <c r="G18" t="n">
-        <v>166.4</v>
+        <v>164.8</v>
       </c>
       <c r="H18" t="n">
-        <v>55.7</v>
+        <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-12.84</v>
+        <v>-18.21</v>
       </c>
       <c r="K18" t="n">
-        <v>-153.51</v>
+        <v>-114.04</v>
       </c>
       <c r="L18" t="n">
-        <v>154.04</v>
+        <v>115.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:55:36</t>
+          <t>04:58:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="F19" t="n">
-        <v>12.42</v>
+        <v>15.92</v>
       </c>
       <c r="G19" t="n">
-        <v>161</v>
+        <v>162.2</v>
       </c>
       <c r="H19" t="n">
-        <v>68.3</v>
+        <v>26.5</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>137.26</v>
+        <v>133.44</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.76</v>
+        <v>-162.77</v>
       </c>
       <c r="L19" t="n">
-        <v>141.6</v>
+        <v>210.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:59:02</t>
+          <t>05:02:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.55</v>
+        <v>5.82</v>
       </c>
       <c r="F20" t="n">
-        <v>16.09</v>
+        <v>12.86</v>
       </c>
       <c r="G20" t="n">
-        <v>151.9</v>
+        <v>161.2</v>
       </c>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>57.2</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>181.11</v>
+        <v>2.65</v>
       </c>
       <c r="K20" t="n">
-        <v>74.27</v>
+        <v>-210.47</v>
       </c>
       <c r="L20" t="n">
-        <v>195.75</v>
+        <v>210.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:01:04</t>
+          <t>05:03:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.96</v>
+        <v>5.63</v>
       </c>
       <c r="F21" t="n">
-        <v>12.89</v>
+        <v>15.53</v>
       </c>
       <c r="G21" t="n">
-        <v>156.9</v>
+        <v>156.5</v>
       </c>
       <c r="H21" t="n">
-        <v>26.5</v>
+        <v>69.2</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>181.15</v>
+        <v>62.39</v>
       </c>
       <c r="K21" t="n">
-        <v>124.15</v>
+        <v>-240.23</v>
       </c>
       <c r="L21" t="n">
-        <v>219.61</v>
+        <v>248.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:02:37</t>
+          <t>05:05:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.97</v>
+        <v>5.15</v>
       </c>
       <c r="F22" t="n">
-        <v>11.4</v>
+        <v>11.25</v>
       </c>
       <c r="G22" t="n">
-        <v>170.5</v>
+        <v>150.8</v>
       </c>
       <c r="H22" t="n">
-        <v>91.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>88.09999999999999</v>
+        <v>216.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-176.23</v>
+        <v>-141.34</v>
       </c>
       <c r="L22" t="n">
-        <v>197.02</v>
+        <v>258.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:06:11</t>
+          <t>05:09:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.24</v>
+        <v>5.95</v>
       </c>
       <c r="F23" t="n">
-        <v>14.21</v>
+        <v>16.88</v>
       </c>
       <c r="G23" t="n">
-        <v>150.6</v>
+        <v>160.1</v>
       </c>
       <c r="H23" t="n">
-        <v>66.3</v>
+        <v>41.5</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-204.31</v>
+        <v>386.57</v>
       </c>
       <c r="K23" t="n">
-        <v>-187.78</v>
+        <v>-23.71</v>
       </c>
       <c r="L23" t="n">
-        <v>277.5</v>
+        <v>387.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:08:06</t>
+          <t>05:11:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.66</v>
+        <v>6.16</v>
       </c>
       <c r="F24" t="n">
-        <v>15.09</v>
+        <v>14.74</v>
       </c>
       <c r="G24" t="n">
-        <v>151.2</v>
+        <v>143.9</v>
       </c>
       <c r="H24" t="n">
-        <v>47.6</v>
+        <v>56.2</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>105.74</v>
+        <v>429.39</v>
       </c>
       <c r="K24" t="n">
-        <v>-276.69</v>
+        <v>53.32</v>
       </c>
       <c r="L24" t="n">
-        <v>296.21</v>
+        <v>432.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:09:12</t>
+          <t>05:12:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.65</v>
+        <v>5.34</v>
       </c>
       <c r="F25" t="n">
-        <v>12.59</v>
+        <v>15.32</v>
       </c>
       <c r="G25" t="n">
-        <v>162</v>
+        <v>142.1</v>
       </c>
       <c r="H25" t="n">
-        <v>75.8</v>
+        <v>32.8</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>220.14</v>
+        <v>-56.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-314.1</v>
+        <v>-294.71</v>
       </c>
       <c r="L25" t="n">
-        <v>383.56</v>
+        <v>300.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:14:47</t>
+          <t>05:18:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5.06</v>
+        <v>5.7</v>
       </c>
       <c r="F26" t="n">
-        <v>14.86</v>
+        <v>14.03</v>
       </c>
       <c r="G26" t="n">
-        <v>163.6</v>
+        <v>161.6</v>
       </c>
       <c r="H26" t="n">
-        <v>47.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-121</v>
+        <v>370.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-273.68</v>
+        <v>-299.98</v>
       </c>
       <c r="L26" t="n">
-        <v>299.23</v>
+        <v>476.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:16:21</t>
+          <t>05:20:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.68</v>
+        <v>4.53</v>
       </c>
       <c r="F27" t="n">
-        <v>11.55</v>
+        <v>10.96</v>
       </c>
       <c r="G27" t="n">
-        <v>174.1</v>
+        <v>157.2</v>
       </c>
       <c r="H27" t="n">
-        <v>45.4</v>
+        <v>39.3</v>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>57.36</v>
+        <v>287.92</v>
       </c>
       <c r="K27" t="n">
-        <v>-286.25</v>
+        <v>-136.54</v>
       </c>
       <c r="L27" t="n">
-        <v>291.94</v>
+        <v>318.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:17:26</t>
+          <t>05:21:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.69</v>
+        <v>4.96</v>
       </c>
       <c r="F28" t="n">
-        <v>16.65</v>
+        <v>12.48</v>
       </c>
       <c r="G28" t="n">
-        <v>163.9</v>
+        <v>157.5</v>
       </c>
       <c r="H28" t="n">
-        <v>53.9</v>
+        <v>34</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-212.89</v>
+        <v>-218.69</v>
       </c>
       <c r="K28" t="n">
-        <v>-501.24</v>
+        <v>-252.02</v>
       </c>
       <c r="L28" t="n">
-        <v>544.58</v>
+        <v>333.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:31:28</t>
+          <t>05:31:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.33</v>
+        <v>5.42</v>
       </c>
       <c r="F29" t="n">
-        <v>12.18</v>
+        <v>12.83</v>
       </c>
       <c r="G29" t="n">
-        <v>145.4</v>
+        <v>149.4</v>
       </c>
       <c r="H29" t="n">
-        <v>86.3</v>
+        <v>87</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>64.14</v>
+        <v>50.18</v>
       </c>
       <c r="K29" t="n">
-        <v>-99.08</v>
+        <v>-113.85</v>
       </c>
       <c r="L29" t="n">
-        <v>118.02</v>
+        <v>124.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:33:34</t>
+          <t>05:34:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.87</v>
+        <v>5.05</v>
       </c>
       <c r="F30" t="n">
-        <v>13.01</v>
+        <v>13.15</v>
       </c>
       <c r="G30" t="n">
-        <v>166.5</v>
+        <v>161.2</v>
       </c>
       <c r="H30" t="n">
-        <v>66.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>92.44</v>
+        <v>-109.36</v>
       </c>
       <c r="K30" t="n">
-        <v>-53.89</v>
+        <v>-15.06</v>
       </c>
       <c r="L30" t="n">
-        <v>107</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:36:11</t>
+          <t>05:35:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.92</v>
+        <v>5.69</v>
       </c>
       <c r="F31" t="n">
-        <v>13.5</v>
+        <v>10.15</v>
       </c>
       <c r="G31" t="n">
-        <v>153.9</v>
+        <v>155.2</v>
       </c>
       <c r="H31" t="n">
-        <v>34.2</v>
+        <v>67.5</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>144.32</v>
+        <v>-120.5</v>
       </c>
       <c r="K31" t="n">
-        <v>6.87</v>
+        <v>-81.76000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>144.48</v>
+        <v>145.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:40:10</t>
+          <t>05:39:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.4</v>
+        <v>6.55</v>
       </c>
       <c r="F32" t="n">
-        <v>13.09</v>
+        <v>18.63</v>
       </c>
       <c r="G32" t="n">
-        <v>156.3</v>
+        <v>167.5</v>
       </c>
       <c r="H32" t="n">
-        <v>42.3</v>
+        <v>45.1</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>141.12</v>
+        <v>-110.72</v>
       </c>
       <c r="K32" t="n">
-        <v>-69.76000000000001</v>
+        <v>-208.2</v>
       </c>
       <c r="L32" t="n">
-        <v>157.42</v>
+        <v>235.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:41:50</t>
+          <t>05:41:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.75</v>
+        <v>5.53</v>
       </c>
       <c r="F33" t="n">
-        <v>8.98</v>
+        <v>14.95</v>
       </c>
       <c r="G33" t="n">
-        <v>150.1</v>
+        <v>142.5</v>
       </c>
       <c r="H33" t="n">
-        <v>69</v>
+        <v>62.3</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>92.20999999999999</v>
+        <v>157.38</v>
       </c>
       <c r="K33" t="n">
-        <v>161.97</v>
+        <v>109.51</v>
       </c>
       <c r="L33" t="n">
-        <v>186.38</v>
+        <v>191.73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:43:59</t>
+          <t>05:43:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.83</v>
+        <v>5.97</v>
       </c>
       <c r="F34" t="n">
-        <v>14.29</v>
+        <v>14.91</v>
       </c>
       <c r="G34" t="n">
-        <v>136.7</v>
+        <v>159.9</v>
       </c>
       <c r="H34" t="n">
-        <v>34.6</v>
+        <v>80.3</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-64.02</v>
+        <v>-183.65</v>
       </c>
       <c r="K34" t="n">
-        <v>-175.52</v>
+        <v>45.29</v>
       </c>
       <c r="L34" t="n">
-        <v>186.83</v>
+        <v>189.15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:48:47</t>
+          <t>05:48:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.65</v>
+        <v>5.33</v>
       </c>
       <c r="F35" t="n">
-        <v>16.87</v>
+        <v>14.14</v>
       </c>
       <c r="G35" t="n">
-        <v>152.9</v>
+        <v>145.3</v>
       </c>
       <c r="H35" t="n">
-        <v>50.9</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>192.05</v>
+        <v>206.11</v>
       </c>
       <c r="K35" t="n">
-        <v>55.09</v>
+        <v>-146.8</v>
       </c>
       <c r="L35" t="n">
-        <v>199.79</v>
+        <v>253.05</v>
       </c>
     </row>
     <row r="36">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="F36" t="n">
-        <v>14.09</v>
+        <v>13.06</v>
       </c>
       <c r="G36" t="n">
-        <v>151.4</v>
+        <v>145.7</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="I36" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>209.31</v>
+        <v>-181.09</v>
       </c>
       <c r="K36" t="n">
-        <v>100.33</v>
+        <v>-57.33</v>
       </c>
       <c r="L36" t="n">
-        <v>232.11</v>
+        <v>189.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:52:08</t>
+          <t>05:51:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.21</v>
+        <v>5.69</v>
       </c>
       <c r="F37" t="n">
-        <v>16.48</v>
+        <v>14.18</v>
       </c>
       <c r="G37" t="n">
-        <v>150.1</v>
+        <v>164.2</v>
       </c>
       <c r="H37" t="n">
-        <v>56.9</v>
+        <v>48.5</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>165.73</v>
+        <v>-146.44</v>
       </c>
       <c r="K37" t="n">
-        <v>11.54</v>
+        <v>190.52</v>
       </c>
       <c r="L37" t="n">
-        <v>166.13</v>
+        <v>240.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:55:17</t>
+          <t>05:56:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.08</v>
+        <v>5.53</v>
       </c>
       <c r="F38" t="n">
-        <v>17.9</v>
+        <v>18.63</v>
       </c>
       <c r="G38" t="n">
-        <v>149.9</v>
+        <v>150.1</v>
       </c>
       <c r="H38" t="n">
-        <v>29.7</v>
+        <v>66</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>445.28</v>
+        <v>-380.82</v>
       </c>
       <c r="K38" t="n">
-        <v>97.44</v>
+        <v>-171.21</v>
       </c>
       <c r="L38" t="n">
-        <v>455.81</v>
+        <v>417.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:56:50</t>
+          <t>05:57:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.19</v>
+        <v>5.38</v>
       </c>
       <c r="F39" t="n">
-        <v>13.46</v>
+        <v>15.89</v>
       </c>
       <c r="G39" t="n">
-        <v>143.5</v>
+        <v>159.2</v>
       </c>
       <c r="H39" t="n">
-        <v>39.2</v>
+        <v>13.8</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-62.31</v>
+        <v>-310.97</v>
       </c>
       <c r="K39" t="n">
-        <v>-558.72</v>
+        <v>-45.48</v>
       </c>
       <c r="L39" t="n">
-        <v>562.1799999999999</v>
+        <v>314.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:59:02</t>
+          <t>05:58:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.65</v>
+        <v>4.67</v>
       </c>
       <c r="F40" t="n">
-        <v>12.61</v>
+        <v>13.11</v>
       </c>
       <c r="G40" t="n">
-        <v>162.9</v>
+        <v>153.2</v>
       </c>
       <c r="H40" t="n">
-        <v>57</v>
+        <v>53.4</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-28.09</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-303.77</v>
+        <v>295.09</v>
       </c>
       <c r="L40" t="n">
-        <v>305.07</v>
+        <v>295.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:03:34</t>
+          <t>06:03:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.23</v>
+        <v>5.87</v>
       </c>
       <c r="F41" t="n">
-        <v>12.71</v>
+        <v>15.44</v>
       </c>
       <c r="G41" t="n">
-        <v>152.3</v>
+        <v>159.5</v>
       </c>
       <c r="H41" t="n">
-        <v>8.9</v>
+        <v>19.7</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>44.97</v>
+        <v>363.48</v>
       </c>
       <c r="K41" t="n">
-        <v>-468.3</v>
+        <v>-197.2</v>
       </c>
       <c r="L41" t="n">
-        <v>470.46</v>
+        <v>413.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:05:19</t>
+          <t>06:05:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.23</v>
+        <v>5.52</v>
       </c>
       <c r="F42" t="n">
-        <v>13.82</v>
+        <v>14.36</v>
       </c>
       <c r="G42" t="n">
-        <v>163.3</v>
+        <v>156.9</v>
       </c>
       <c r="H42" t="n">
-        <v>39.6</v>
+        <v>66.7</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-260.03</v>
+        <v>-365.53</v>
       </c>
       <c r="K42" t="n">
-        <v>317.48</v>
+        <v>261.56</v>
       </c>
       <c r="L42" t="n">
-        <v>410.37</v>
+        <v>449.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:07:44</t>
+          <t>06:06:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.63</v>
+        <v>4.98</v>
       </c>
       <c r="F43" t="n">
-        <v>16.1</v>
+        <v>13.31</v>
       </c>
       <c r="G43" t="n">
-        <v>161.1</v>
+        <v>155.9</v>
       </c>
       <c r="H43" t="n">
-        <v>44.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>205.48</v>
+        <v>414.11</v>
       </c>
       <c r="K43" t="n">
-        <v>-381.01</v>
+        <v>-260.18</v>
       </c>
       <c r="L43" t="n">
-        <v>432.88</v>
+        <v>489.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:18:22</t>
+          <t>06:17:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.68</v>
+        <v>6.26</v>
       </c>
       <c r="F44" t="n">
-        <v>13.16</v>
+        <v>15.26</v>
       </c>
       <c r="G44" t="n">
-        <v>150.5</v>
+        <v>158.1</v>
       </c>
       <c r="H44" t="n">
-        <v>69.7</v>
+        <v>71.8</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>116.82</v>
+        <v>143.98</v>
       </c>
       <c r="K44" t="n">
-        <v>181.59</v>
+        <v>116.91</v>
       </c>
       <c r="L44" t="n">
-        <v>215.92</v>
+        <v>185.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:20:49</t>
+          <t>06:19:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.89</v>
+        <v>4.86</v>
       </c>
       <c r="F45" t="n">
-        <v>13.68</v>
+        <v>12.09</v>
       </c>
       <c r="G45" t="n">
-        <v>155.5</v>
+        <v>165.1</v>
       </c>
       <c r="H45" t="n">
-        <v>71.59999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-63.27</v>
+        <v>3.45</v>
       </c>
       <c r="K45" t="n">
-        <v>-98.45</v>
+        <v>-105.61</v>
       </c>
       <c r="L45" t="n">
-        <v>117.03</v>
+        <v>105.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:21:59</t>
+          <t>06:21:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.11</v>
+        <v>5.81</v>
       </c>
       <c r="F46" t="n">
-        <v>14.61</v>
+        <v>14.79</v>
       </c>
       <c r="G46" t="n">
-        <v>151.2</v>
+        <v>157</v>
       </c>
       <c r="H46" t="n">
-        <v>74.8</v>
+        <v>27.1</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>93.15000000000001</v>
+        <v>-134.47</v>
       </c>
       <c r="K46" t="n">
-        <v>-118.14</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>150.44</v>
+        <v>157.85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:24:51</t>
+          <t>06:25:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.92</v>
+        <v>6.96</v>
       </c>
       <c r="F47" t="n">
-        <v>13.04</v>
+        <v>18.63</v>
       </c>
       <c r="G47" t="n">
-        <v>167.9</v>
+        <v>149.7</v>
       </c>
       <c r="H47" t="n">
-        <v>37.4</v>
+        <v>92.5</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-184.09</v>
+        <v>75.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-59.73</v>
+        <v>-187.48</v>
       </c>
       <c r="L47" t="n">
-        <v>193.53</v>
+        <v>202.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:25:45</t>
+          <t>06:26:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.37</v>
+        <v>5.65</v>
       </c>
       <c r="F48" t="n">
-        <v>13.5</v>
+        <v>16.02</v>
       </c>
       <c r="G48" t="n">
-        <v>166.1</v>
+        <v>161.4</v>
       </c>
       <c r="H48" t="n">
-        <v>77.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-189.55</v>
+        <v>-2.7</v>
       </c>
       <c r="K48" t="n">
-        <v>-104.24</v>
+        <v>149.85</v>
       </c>
       <c r="L48" t="n">
-        <v>216.32</v>
+        <v>149.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:26:27</t>
+          <t>06:29:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.28</v>
+        <v>5.58</v>
       </c>
       <c r="F49" t="n">
-        <v>14.52</v>
+        <v>18.19</v>
       </c>
       <c r="G49" t="n">
-        <v>157.1</v>
+        <v>151.2</v>
       </c>
       <c r="H49" t="n">
-        <v>27.9</v>
+        <v>47.6</v>
       </c>
       <c r="I49" t="n">
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-19.38</v>
+        <v>56.45</v>
       </c>
       <c r="K49" t="n">
-        <v>-154.05</v>
+        <v>-176.47</v>
       </c>
       <c r="L49" t="n">
-        <v>155.26</v>
+        <v>185.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:30:52</t>
+          <t>06:33:24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.57</v>
+        <v>6.08</v>
       </c>
       <c r="F50" t="n">
-        <v>14.06</v>
+        <v>14.53</v>
       </c>
       <c r="G50" t="n">
-        <v>162.9</v>
+        <v>165.2</v>
       </c>
       <c r="H50" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-124.03</v>
+        <v>210.94</v>
       </c>
       <c r="K50" t="n">
-        <v>-228.04</v>
+        <v>148.26</v>
       </c>
       <c r="L50" t="n">
-        <v>259.59</v>
+        <v>257.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:32:48</t>
+          <t>06:34:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.95</v>
+        <v>5.68</v>
       </c>
       <c r="F51" t="n">
-        <v>16.64</v>
+        <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>152.4</v>
+        <v>163.6</v>
       </c>
       <c r="H51" t="n">
-        <v>42.7</v>
+        <v>47.5</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-100.15</v>
+        <v>-124.63</v>
       </c>
       <c r="K51" t="n">
-        <v>-186.11</v>
+        <v>-173.75</v>
       </c>
       <c r="L51" t="n">
-        <v>211.35</v>
+        <v>213.83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:33:44</t>
+          <t>06:35:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.64</v>
+        <v>5.09</v>
       </c>
       <c r="F52" t="n">
-        <v>18.63</v>
+        <v>13.28</v>
       </c>
       <c r="G52" t="n">
-        <v>172.6</v>
+        <v>153</v>
       </c>
       <c r="H52" t="n">
-        <v>49.7</v>
+        <v>51.4</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-193.94</v>
+        <v>137.3</v>
       </c>
       <c r="K52" t="n">
-        <v>-116.23</v>
+        <v>-201.9</v>
       </c>
       <c r="L52" t="n">
-        <v>226.1</v>
+        <v>244.16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:38:28</t>
+          <t>06:41:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="F53" t="n">
-        <v>12.84</v>
+        <v>18.6</v>
       </c>
       <c r="G53" t="n">
-        <v>167.6</v>
+        <v>141.8</v>
       </c>
       <c r="H53" t="n">
-        <v>50.6</v>
+        <v>72.5</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-280.57</v>
+        <v>375.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-456.26</v>
+        <v>166.22</v>
       </c>
       <c r="L53" t="n">
-        <v>535.62</v>
+        <v>410.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:40:36</t>
+          <t>06:42:35</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>7.17</v>
+        <v>5.67</v>
       </c>
       <c r="F54" t="n">
-        <v>17.5</v>
+        <v>16.21</v>
       </c>
       <c r="G54" t="n">
-        <v>172.6</v>
+        <v>145.4</v>
       </c>
       <c r="H54" t="n">
-        <v>53.8</v>
+        <v>86.3</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>330.18</v>
+        <v>184.24</v>
       </c>
       <c r="K54" t="n">
-        <v>-94.25</v>
+        <v>-291.35</v>
       </c>
       <c r="L54" t="n">
-        <v>343.37</v>
+        <v>344.72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:42:32</t>
+          <t>06:43:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.81</v>
+        <v>5.22</v>
       </c>
       <c r="F55" t="n">
-        <v>16.98</v>
+        <v>14.52</v>
       </c>
       <c r="G55" t="n">
-        <v>147.2</v>
+        <v>141.4</v>
       </c>
       <c r="H55" t="n">
-        <v>36.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>65.52</v>
+        <v>-385.56</v>
       </c>
       <c r="K55" t="n">
-        <v>-396.95</v>
+        <v>108.75</v>
       </c>
       <c r="L55" t="n">
-        <v>402.32</v>
+        <v>400.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:47:09</t>
+          <t>06:49:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.72</v>
+        <v>6.04</v>
       </c>
       <c r="F56" t="n">
-        <v>14.91</v>
+        <v>16.43</v>
       </c>
       <c r="G56" t="n">
-        <v>151.7</v>
+        <v>153.9</v>
       </c>
       <c r="H56" t="n">
-        <v>86.2</v>
+        <v>34.2</v>
       </c>
       <c r="I56" t="n">
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>437.23</v>
+        <v>-469.08</v>
       </c>
       <c r="K56" t="n">
-        <v>-234.61</v>
+        <v>456.05</v>
       </c>
       <c r="L56" t="n">
-        <v>496.2</v>
+        <v>654.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:48:53</t>
+          <t>06:49:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.13</v>
+        <v>6.83</v>
       </c>
       <c r="F57" t="n">
-        <v>18.41</v>
+        <v>18.63</v>
       </c>
       <c r="G57" t="n">
-        <v>164.5</v>
+        <v>159.9</v>
       </c>
       <c r="H57" t="n">
-        <v>48.8</v>
+        <v>51.7</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>138.47</v>
+        <v>140.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-417.37</v>
+        <v>-498.8</v>
       </c>
       <c r="L57" t="n">
-        <v>439.74</v>
+        <v>518.21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:50:43</t>
+          <t>06:51:22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.68</v>
+        <v>5.98</v>
       </c>
       <c r="F58" t="n">
-        <v>18.27</v>
+        <v>16.74</v>
       </c>
       <c r="G58" t="n">
-        <v>156.4</v>
+        <v>149.8</v>
       </c>
       <c r="H58" t="n">
-        <v>74.2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>236.4</v>
+        <v>-470.29</v>
       </c>
       <c r="K58" t="n">
-        <v>-457.07</v>
+        <v>-331.88</v>
       </c>
       <c r="L58" t="n">
-        <v>514.59</v>
+        <v>575.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:03:12</t>
+          <t>07:01:05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.18</v>
+        <v>5.89</v>
       </c>
       <c r="F59" t="n">
-        <v>15.53</v>
+        <v>17.42</v>
       </c>
       <c r="G59" t="n">
-        <v>158.3</v>
+        <v>148.7</v>
       </c>
       <c r="H59" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>147.08</v>
+        <v>124.66</v>
       </c>
       <c r="K59" t="n">
-        <v>-55.97</v>
+        <v>19.56</v>
       </c>
       <c r="L59" t="n">
-        <v>157.37</v>
+        <v>126.19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:05:28</t>
+          <t>07:02:28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.19</v>
+        <v>5.76</v>
       </c>
       <c r="F60" t="n">
-        <v>16.83</v>
+        <v>16.61</v>
       </c>
       <c r="G60" t="n">
-        <v>162.5</v>
+        <v>165.4</v>
       </c>
       <c r="H60" t="n">
-        <v>64.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>98.61</v>
+        <v>-145.36</v>
       </c>
       <c r="K60" t="n">
-        <v>-129.75</v>
+        <v>-7.33</v>
       </c>
       <c r="L60" t="n">
-        <v>162.97</v>
+        <v>145.55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:06:34</t>
+          <t>07:04:18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.81</v>
+        <v>6.02</v>
       </c>
       <c r="F61" t="n">
-        <v>13.93</v>
+        <v>13.92</v>
       </c>
       <c r="G61" t="n">
-        <v>153</v>
+        <v>157.9</v>
       </c>
       <c r="H61" t="n">
-        <v>72.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>96.73</v>
+        <v>-46.74</v>
       </c>
       <c r="K61" t="n">
-        <v>-79.38</v>
+        <v>-189.04</v>
       </c>
       <c r="L61" t="n">
-        <v>125.13</v>
+        <v>194.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:11:17</t>
+          <t>07:10:03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.18</v>
+        <v>6.02</v>
       </c>
       <c r="F62" t="n">
-        <v>18.03</v>
+        <v>15.75</v>
       </c>
       <c r="G62" t="n">
-        <v>165.8</v>
+        <v>169.1</v>
       </c>
       <c r="H62" t="n">
-        <v>73.3</v>
+        <v>66.3</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>117.68</v>
+        <v>193.96</v>
       </c>
       <c r="K62" t="n">
-        <v>-112.57</v>
+        <v>22.87</v>
       </c>
       <c r="L62" t="n">
-        <v>162.85</v>
+        <v>195.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:12:26</t>
+          <t>07:10:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.92</v>
+        <v>6.33</v>
       </c>
       <c r="F63" t="n">
         <v>18.63</v>
       </c>
       <c r="G63" t="n">
-        <v>165.1</v>
+        <v>149.9</v>
       </c>
       <c r="H63" t="n">
-        <v>38.3</v>
+        <v>29.7</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-205.19</v>
+        <v>239.95</v>
       </c>
       <c r="K63" t="n">
-        <v>-164.74</v>
+        <v>145.26</v>
       </c>
       <c r="L63" t="n">
-        <v>263.14</v>
+        <v>280.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:13:48</t>
+          <t>07:11:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.72</v>
+        <v>5.55</v>
       </c>
       <c r="F64" t="n">
-        <v>15.84</v>
+        <v>15.06</v>
       </c>
       <c r="G64" t="n">
-        <v>155.1</v>
+        <v>150.6</v>
       </c>
       <c r="H64" t="n">
-        <v>48.5</v>
+        <v>63.8</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-177.38</v>
+        <v>-86.37</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.49</v>
+        <v>-160.48</v>
       </c>
       <c r="L64" t="n">
-        <v>185.86</v>
+        <v>182.25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:17:25</t>
+          <t>07:15:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>5.46</v>
       </c>
       <c r="F65" t="n">
-        <v>18.3</v>
+        <v>12.74</v>
       </c>
       <c r="G65" t="n">
-        <v>145</v>
+        <v>166.4</v>
       </c>
       <c r="H65" t="n">
-        <v>40.6</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>293.35</v>
+        <v>-33.34</v>
       </c>
       <c r="K65" t="n">
-        <v>-18.65</v>
+        <v>-193.42</v>
       </c>
       <c r="L65" t="n">
-        <v>293.94</v>
+        <v>196.28</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:19:15</t>
+          <t>07:17:25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.04</v>
+        <v>5.72</v>
       </c>
       <c r="F66" t="n">
-        <v>13.61</v>
+        <v>18.63</v>
       </c>
       <c r="G66" t="n">
-        <v>148.2</v>
+        <v>152.3</v>
       </c>
       <c r="H66" t="n">
-        <v>13.6</v>
+        <v>8.9</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>126.85</v>
+        <v>-10.57</v>
       </c>
       <c r="K66" t="n">
-        <v>-118.77</v>
+        <v>-309.45</v>
       </c>
       <c r="L66" t="n">
-        <v>173.77</v>
+        <v>309.63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:19:57</t>
+          <t>07:19:33</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.54</v>
+        <v>5.58</v>
       </c>
       <c r="F67" t="n">
-        <v>18.63</v>
+        <v>15.39</v>
       </c>
       <c r="G67" t="n">
-        <v>156.8</v>
+        <v>160.9</v>
       </c>
       <c r="H67" t="n">
-        <v>41.6</v>
+        <v>71</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-192.11</v>
+        <v>-86.64</v>
       </c>
       <c r="K67" t="n">
-        <v>162.17</v>
+        <v>-262.85</v>
       </c>
       <c r="L67" t="n">
-        <v>251.41</v>
+        <v>276.76</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:23:21</t>
+          <t>07:24:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.76</v>
+        <v>5.94</v>
       </c>
       <c r="F68" t="n">
-        <v>16.65</v>
+        <v>15.65</v>
       </c>
       <c r="G68" t="n">
-        <v>155.6</v>
+        <v>161.1</v>
       </c>
       <c r="H68" t="n">
-        <v>28.7</v>
+        <v>44.9</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>229.45</v>
+        <v>202.61</v>
       </c>
       <c r="K68" t="n">
-        <v>156.88</v>
+        <v>-325.94</v>
       </c>
       <c r="L68" t="n">
-        <v>277.95</v>
+        <v>383.78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:24:26</t>
+          <t>07:26:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.63</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>18.63</v>
+        <v>14.64</v>
       </c>
       <c r="G69" t="n">
-        <v>154.9</v>
+        <v>150.8</v>
       </c>
       <c r="H69" t="n">
-        <v>35.6</v>
+        <v>39.2</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>126.51</v>
+        <v>285.82</v>
       </c>
       <c r="K69" t="n">
-        <v>-363.92</v>
+        <v>456.52</v>
       </c>
       <c r="L69" t="n">
-        <v>385.28</v>
+        <v>538.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:25:23</t>
+          <t>07:28:10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.08</v>
+        <v>7.07</v>
       </c>
       <c r="F70" t="n">
-        <v>16.24</v>
+        <v>18.63</v>
       </c>
       <c r="G70" t="n">
-        <v>153.3</v>
+        <v>163.9</v>
       </c>
       <c r="H70" t="n">
-        <v>59.3</v>
+        <v>51.5</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-373.24</v>
+        <v>-91.03</v>
       </c>
       <c r="K70" t="n">
-        <v>-94.91</v>
+        <v>330.94</v>
       </c>
       <c r="L70" t="n">
-        <v>385.12</v>
+        <v>343.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:31:07</t>
+          <t>07:32:58</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.47</v>
+        <v>5.29</v>
       </c>
       <c r="F71" t="n">
-        <v>16.09</v>
+        <v>15.85</v>
       </c>
       <c r="G71" t="n">
-        <v>147.8</v>
+        <v>151.2</v>
       </c>
       <c r="H71" t="n">
-        <v>64.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>432.28</v>
+        <v>291.47</v>
       </c>
       <c r="K71" t="n">
-        <v>54.07</v>
+        <v>-315.82</v>
       </c>
       <c r="L71" t="n">
-        <v>435.64</v>
+        <v>429.76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:31:59</t>
+          <t>07:34:35</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.06</v>
+        <v>6.24</v>
       </c>
       <c r="F72" t="n">
-        <v>15.53</v>
+        <v>14.54</v>
       </c>
       <c r="G72" t="n">
-        <v>150.9</v>
+        <v>149.8</v>
       </c>
       <c r="H72" t="n">
-        <v>22</v>
+        <v>52.4</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>367.51</v>
+        <v>-36.99</v>
       </c>
       <c r="K72" t="n">
-        <v>-25.24</v>
+        <v>612.5599999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>368.37</v>
+        <v>613.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:33:16</t>
+          <t>07:36:19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.59</v>
+        <v>5.88</v>
       </c>
       <c r="F73" t="n">
-        <v>15.7</v>
+        <v>18.63</v>
       </c>
       <c r="G73" t="n">
-        <v>156.6</v>
+        <v>166.1</v>
       </c>
       <c r="H73" t="n">
-        <v>94.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-366.62</v>
+        <v>-623.49</v>
       </c>
       <c r="K73" t="n">
-        <v>-212.9</v>
+        <v>-128.7</v>
       </c>
       <c r="L73" t="n">
-        <v>423.95</v>
+        <v>636.63</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:46:21</t>
+          <t>07:46:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.1</v>
+        <v>5.64</v>
       </c>
       <c r="F74" t="n">
-        <v>15.8</v>
+        <v>16.15</v>
       </c>
       <c r="G74" t="n">
-        <v>161.3</v>
+        <v>146</v>
       </c>
       <c r="H74" t="n">
-        <v>67.09999999999999</v>
+        <v>58.5</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>148.33</v>
+        <v>120.5</v>
       </c>
       <c r="K74" t="n">
-        <v>17.3</v>
+        <v>-83.8</v>
       </c>
       <c r="L74" t="n">
-        <v>149.34</v>
+        <v>146.77</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:47:36</t>
+          <t>07:48:09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.98</v>
+        <v>6.04</v>
       </c>
       <c r="F75" t="n">
-        <v>16.32</v>
+        <v>16.09</v>
       </c>
       <c r="G75" t="n">
-        <v>165.7</v>
+        <v>151.1</v>
       </c>
       <c r="H75" t="n">
-        <v>36.4</v>
+        <v>67.5</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-101.16</v>
+        <v>150.56</v>
       </c>
       <c r="K75" t="n">
-        <v>-110.71</v>
+        <v>49.07</v>
       </c>
       <c r="L75" t="n">
-        <v>149.97</v>
+        <v>158.36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:48:30</t>
+          <t>07:49:55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.74</v>
+        <v>5.99</v>
       </c>
       <c r="F76" t="n">
-        <v>14.47</v>
+        <v>17.69</v>
       </c>
       <c r="G76" t="n">
-        <v>143</v>
+        <v>158.5</v>
       </c>
       <c r="H76" t="n">
-        <v>90.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>10.19</v>
+        <v>-64.64</v>
       </c>
       <c r="K76" t="n">
-        <v>-106.15</v>
+        <v>140.86</v>
       </c>
       <c r="L76" t="n">
-        <v>106.63</v>
+        <v>154.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:54:14</t>
+          <t>07:55:10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.23</v>
+        <v>5.05</v>
       </c>
       <c r="F77" t="n">
-        <v>18.63</v>
+        <v>14.87</v>
       </c>
       <c r="G77" t="n">
-        <v>151.3</v>
+        <v>154.7</v>
       </c>
       <c r="H77" t="n">
-        <v>56</v>
+        <v>90.8</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>143.12</v>
+        <v>-178.28</v>
       </c>
       <c r="K77" t="n">
-        <v>-151.54</v>
+        <v>59.2</v>
       </c>
       <c r="L77" t="n">
-        <v>208.44</v>
+        <v>187.85</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:56:25</t>
+          <t>07:57:43</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.43</v>
+        <v>5.78</v>
       </c>
       <c r="F78" t="n">
-        <v>18.63</v>
+        <v>16.77</v>
       </c>
       <c r="G78" t="n">
-        <v>148.5</v>
+        <v>167.6</v>
       </c>
       <c r="H78" t="n">
-        <v>37.6</v>
+        <v>50.6</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>146.15</v>
+        <v>-181.37</v>
       </c>
       <c r="K78" t="n">
-        <v>-82.20999999999999</v>
+        <v>-161.9</v>
       </c>
       <c r="L78" t="n">
-        <v>167.68</v>
+        <v>243.12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:58:32</t>
+          <t>07:59:23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.39</v>
+        <v>7.52</v>
       </c>
       <c r="F79" t="n">
-        <v>14.29</v>
+        <v>18.63</v>
       </c>
       <c r="G79" t="n">
-        <v>156.7</v>
+        <v>162.7</v>
       </c>
       <c r="H79" t="n">
-        <v>54.1</v>
+        <v>94.3</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>56.74</v>
+        <v>71.03</v>
       </c>
       <c r="K79" t="n">
-        <v>-122.13</v>
+        <v>-169.81</v>
       </c>
       <c r="L79" t="n">
-        <v>134.67</v>
+        <v>184.07</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:04:20</t>
+          <t>08:04:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="F80" t="n">
-        <v>17.18</v>
+        <v>16.16</v>
       </c>
       <c r="G80" t="n">
-        <v>147.5</v>
+        <v>147.2</v>
       </c>
       <c r="H80" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-146.61</v>
+        <v>3.91</v>
       </c>
       <c r="K80" t="n">
-        <v>-112.26</v>
+        <v>-324.07</v>
       </c>
       <c r="L80" t="n">
-        <v>184.66</v>
+        <v>324.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:06:21</t>
+          <t>08:05:39</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.37</v>
+        <v>6.06</v>
       </c>
       <c r="F81" t="n">
-        <v>17.83</v>
+        <v>16.51</v>
       </c>
       <c r="G81" t="n">
-        <v>152</v>
+        <v>150.4</v>
       </c>
       <c r="H81" t="n">
-        <v>20.9</v>
+        <v>42.2</v>
       </c>
       <c r="I81" t="n">
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>195.95</v>
+        <v>57.3</v>
       </c>
       <c r="K81" t="n">
-        <v>25.27</v>
+        <v>-265.25</v>
       </c>
       <c r="L81" t="n">
-        <v>197.58</v>
+        <v>271.37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:08:22</t>
+          <t>08:08:11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.8</v>
+        <v>6.29</v>
       </c>
       <c r="F82" t="n">
-        <v>15.81</v>
+        <v>14.96</v>
       </c>
       <c r="G82" t="n">
-        <v>154.1</v>
+        <v>164.5</v>
       </c>
       <c r="H82" t="n">
-        <v>65.3</v>
+        <v>48.8</v>
       </c>
       <c r="I82" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>116.93</v>
+        <v>88.37</v>
       </c>
       <c r="K82" t="n">
-        <v>-205.04</v>
+        <v>-249.46</v>
       </c>
       <c r="L82" t="n">
-        <v>236.04</v>
+        <v>264.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:12:11</t>
+          <t>08:12:15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.56</v>
+        <v>7.03</v>
       </c>
       <c r="F83" t="n">
-        <v>15.31</v>
+        <v>18.63</v>
       </c>
       <c r="G83" t="n">
-        <v>150.3</v>
+        <v>157.8</v>
       </c>
       <c r="H83" t="n">
-        <v>67.5</v>
+        <v>53.8</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>69.15000000000001</v>
+        <v>-268.08</v>
       </c>
       <c r="K83" t="n">
-        <v>-214.19</v>
+        <v>-332.56</v>
       </c>
       <c r="L83" t="n">
-        <v>225.07</v>
+        <v>427.16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:13:07</t>
+          <t>08:14:32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.08</v>
+        <v>6.96</v>
       </c>
       <c r="F84" t="n">
-        <v>15.52</v>
+        <v>18.63</v>
       </c>
       <c r="G84" t="n">
-        <v>159.1</v>
+        <v>158.3</v>
       </c>
       <c r="H84" t="n">
-        <v>61.1</v>
+        <v>47.9</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-204.57</v>
+        <v>415.98</v>
       </c>
       <c r="K84" t="n">
-        <v>-291.17</v>
+        <v>-46.34</v>
       </c>
       <c r="L84" t="n">
-        <v>355.85</v>
+        <v>418.56</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:14:44</t>
+          <t>08:15:54</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.97</v>
+        <v>6.49</v>
       </c>
       <c r="F85" t="n">
-        <v>18.63</v>
+        <v>18.28</v>
       </c>
       <c r="G85" t="n">
-        <v>159.9</v>
+        <v>156</v>
       </c>
       <c r="H85" t="n">
-        <v>63.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-141.21</v>
+        <v>456.46</v>
       </c>
       <c r="K85" t="n">
-        <v>-156.91</v>
+        <v>-5.31</v>
       </c>
       <c r="L85" t="n">
-        <v>211.1</v>
+        <v>456.49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:19:41</t>
+          <t>08:20:01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.24</v>
+        <v>5.09</v>
       </c>
       <c r="F86" t="n">
-        <v>17.42</v>
+        <v>13.52</v>
       </c>
       <c r="G86" t="n">
-        <v>158.5</v>
+        <v>153</v>
       </c>
       <c r="H86" t="n">
-        <v>76</v>
+        <v>72.2</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>417.5</v>
+        <v>332.82</v>
       </c>
       <c r="K86" t="n">
-        <v>-176.7</v>
+        <v>-185.23</v>
       </c>
       <c r="L86" t="n">
-        <v>453.35</v>
+        <v>380.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:21:51</t>
+          <t>08:22:32</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.69</v>
+        <v>6.47</v>
       </c>
       <c r="F87" t="n">
-        <v>18.12</v>
+        <v>18.63</v>
       </c>
       <c r="G87" t="n">
-        <v>159.8</v>
+        <v>158.2</v>
       </c>
       <c r="H87" t="n">
-        <v>71.3</v>
+        <v>77.3</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>518.55</v>
+        <v>336.52</v>
       </c>
       <c r="K87" t="n">
-        <v>141.14</v>
+        <v>-256.13</v>
       </c>
       <c r="L87" t="n">
-        <v>537.42</v>
+        <v>422.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:23:55</t>
+          <t>08:23:23</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.53</v>
+        <v>6.34</v>
       </c>
       <c r="F88" t="n">
-        <v>18.23</v>
+        <v>18.63</v>
       </c>
       <c r="G88" t="n">
-        <v>152.5</v>
+        <v>165.1</v>
       </c>
       <c r="H88" t="n">
-        <v>75.5</v>
+        <v>38.3</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>186.87</v>
+        <v>-638.53</v>
       </c>
       <c r="K88" t="n">
-        <v>-317.86</v>
+        <v>-195.91</v>
       </c>
       <c r="L88" t="n">
-        <v>368.72</v>
+        <v>667.91</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-70.03</v>
+        <v>-78.38</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.08</v>
+        <v>-11.28</v>
       </c>
       <c r="L14" t="n">
-        <v>70.75</v>
+        <v>79.19</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>71.66</v>
+        <v>76.91</v>
       </c>
       <c r="K15" t="n">
-        <v>56.06</v>
+        <v>60.17</v>
       </c>
       <c r="L15" t="n">
-        <v>90.98</v>
+        <v>97.65000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-54.23</v>
+        <v>-67.15000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>24.26</v>
+        <v>30.04</v>
       </c>
       <c r="L16" t="n">
-        <v>59.41</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-26.34</v>
+        <v>-29.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-97.86</v>
+        <v>-109.12</v>
       </c>
       <c r="L17" t="n">
-        <v>101.34</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>108.32</v>
+        <v>116.91</v>
       </c>
       <c r="K18" t="n">
-        <v>-49.81</v>
+        <v>-53.76</v>
       </c>
       <c r="L18" t="n">
-        <v>119.22</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>73.45</v>
+        <v>90.44</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.95</v>
+        <v>-1.17</v>
       </c>
       <c r="L19" t="n">
-        <v>73.45999999999999</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-217.27</v>
+        <v>-249.35</v>
       </c>
       <c r="K20" t="n">
-        <v>-150.34</v>
+        <v>-172.54</v>
       </c>
       <c r="L20" t="n">
-        <v>264.21</v>
+        <v>303.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>169.42</v>
+        <v>196.39</v>
       </c>
       <c r="K21" t="n">
-        <v>197.3</v>
+        <v>228.71</v>
       </c>
       <c r="L21" t="n">
-        <v>260.06</v>
+        <v>301.45</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-99.93000000000001</v>
+        <v>-118.32</v>
       </c>
       <c r="K22" t="n">
-        <v>-139.23</v>
+        <v>-164.84</v>
       </c>
       <c r="L22" t="n">
-        <v>171.38</v>
+        <v>202.91</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>112.26</v>
+        <v>158.59</v>
       </c>
       <c r="K23" t="n">
-        <v>-257.17</v>
+        <v>-363.3</v>
       </c>
       <c r="L23" t="n">
-        <v>280.6</v>
+        <v>396.4</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>-38.47</v>
+        <v>-51.18</v>
       </c>
       <c r="K24" t="n">
-        <v>-178.94</v>
+        <v>-238.04</v>
       </c>
       <c r="L24" t="n">
-        <v>183.02</v>
+        <v>243.48</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>246.41</v>
+        <v>329.84</v>
       </c>
       <c r="K25" t="n">
-        <v>-61.66</v>
+        <v>-82.53</v>
       </c>
       <c r="L25" t="n">
-        <v>254</v>
+        <v>340.01</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>262.71</v>
+        <v>373.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-247.73</v>
+        <v>-352.32</v>
       </c>
       <c r="L26" t="n">
-        <v>361.1</v>
+        <v>513.54</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>118.13</v>
+        <v>158.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-337.92</v>
+        <v>-453.44</v>
       </c>
       <c r="L27" t="n">
-        <v>357.97</v>
+        <v>480.35</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>290.71</v>
+        <v>427.03</v>
       </c>
       <c r="K28" t="n">
-        <v>-141.71</v>
+        <v>-208.17</v>
       </c>
       <c r="L28" t="n">
-        <v>323.41</v>
+        <v>475.06</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>67.48</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.05</v>
+        <v>-45.34</v>
       </c>
       <c r="L29" t="n">
-        <v>78.47</v>
+        <v>88.84</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-62.86</v>
+        <v>-66.44</v>
       </c>
       <c r="K30" t="n">
-        <v>-99.53</v>
+        <v>-105.21</v>
       </c>
       <c r="L30" t="n">
-        <v>117.71</v>
+        <v>124.43</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.9</v>
+        <v>-21.88</v>
       </c>
       <c r="K31" t="n">
-        <v>80.79000000000001</v>
+        <v>88.83</v>
       </c>
       <c r="L31" t="n">
-        <v>83.2</v>
+        <v>91.48999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-83.06999999999999</v>
+        <v>-103.58</v>
       </c>
       <c r="K32" t="n">
-        <v>-46.07</v>
+        <v>-57.44</v>
       </c>
       <c r="L32" t="n">
-        <v>94.98999999999999</v>
+        <v>118.44</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>29.7</v>
+        <v>37.88</v>
       </c>
       <c r="K33" t="n">
-        <v>-78.33</v>
+        <v>-99.93000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>83.77</v>
+        <v>106.87</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-73.76000000000001</v>
+        <v>-95.62</v>
       </c>
       <c r="K34" t="n">
-        <v>18.94</v>
+        <v>24.56</v>
       </c>
       <c r="L34" t="n">
-        <v>76.15000000000001</v>
+        <v>98.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-131.62</v>
+        <v>-164.74</v>
       </c>
       <c r="K35" t="n">
-        <v>105.22</v>
+        <v>131.7</v>
       </c>
       <c r="L35" t="n">
-        <v>168.51</v>
+        <v>210.91</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-78.92</v>
+        <v>-97.7</v>
       </c>
       <c r="K36" t="n">
-        <v>-113.22</v>
+        <v>-140.17</v>
       </c>
       <c r="L36" t="n">
-        <v>138</v>
+        <v>170.86</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-82.51000000000001</v>
+        <v>-99.65000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>154.57</v>
+        <v>186.66</v>
       </c>
       <c r="L37" t="n">
-        <v>175.21</v>
+        <v>211.59</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>306.66</v>
+        <v>376.82</v>
       </c>
       <c r="K38" t="n">
-        <v>181.65</v>
+        <v>223.21</v>
       </c>
       <c r="L38" t="n">
-        <v>356.42</v>
+        <v>437.97</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>130.69</v>
+        <v>172.42</v>
       </c>
       <c r="K39" t="n">
-        <v>-220.36</v>
+        <v>-290.7</v>
       </c>
       <c r="L39" t="n">
-        <v>256.2</v>
+        <v>337.99</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>93.34999999999999</v>
+        <v>120.6</v>
       </c>
       <c r="K40" t="n">
-        <v>-269.63</v>
+        <v>-348.35</v>
       </c>
       <c r="L40" t="n">
-        <v>285.33</v>
+        <v>368.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>222.25</v>
+        <v>287.03</v>
       </c>
       <c r="K41" t="n">
-        <v>-427.95</v>
+        <v>-552.6900000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>482.22</v>
+        <v>622.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>17.15</v>
+        <v>24.73</v>
       </c>
       <c r="K42" t="n">
-        <v>-296.14</v>
+        <v>-426.99</v>
       </c>
       <c r="L42" t="n">
-        <v>296.63</v>
+        <v>427.7</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>155.19</v>
+        <v>212.9</v>
       </c>
       <c r="K43" t="n">
-        <v>323.48</v>
+        <v>443.78</v>
       </c>
       <c r="L43" t="n">
-        <v>358.78</v>
+        <v>492.21</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.57</v>
+        <v>-14.01</v>
       </c>
       <c r="K44" t="n">
-        <v>-89.42</v>
+        <v>-99.66</v>
       </c>
       <c r="L44" t="n">
-        <v>90.29000000000001</v>
+        <v>100.64</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-72.45999999999999</v>
+        <v>-82.95999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-43.09</v>
+        <v>-49.33</v>
       </c>
       <c r="L45" t="n">
-        <v>84.31</v>
+        <v>96.52</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-91.76000000000001</v>
+        <v>-103.61</v>
       </c>
       <c r="K46" t="n">
-        <v>-43.37</v>
+        <v>-48.97</v>
       </c>
       <c r="L46" t="n">
-        <v>101.49</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-51.09</v>
+        <v>-58.92</v>
       </c>
       <c r="K47" t="n">
-        <v>129.93</v>
+        <v>149.85</v>
       </c>
       <c r="L47" t="n">
-        <v>139.62</v>
+        <v>161.02</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-48.23</v>
+        <v>-57.05</v>
       </c>
       <c r="K48" t="n">
-        <v>89.55</v>
+        <v>105.92</v>
       </c>
       <c r="L48" t="n">
-        <v>101.71</v>
+        <v>120.31</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
       <c r="K49" t="n">
-        <v>-86.43000000000001</v>
+        <v>-110.96</v>
       </c>
       <c r="L49" t="n">
-        <v>86.45</v>
+        <v>110.98</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>56.57</v>
+        <v>72.8</v>
       </c>
       <c r="K50" t="n">
-        <v>132.84</v>
+        <v>170.95</v>
       </c>
       <c r="L50" t="n">
-        <v>144.39</v>
+        <v>185.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>-167.55</v>
+        <v>-208.56</v>
       </c>
       <c r="K51" t="n">
-        <v>91.95999999999999</v>
+        <v>114.46</v>
       </c>
       <c r="L51" t="n">
-        <v>191.13</v>
+        <v>237.91</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-108.75</v>
+        <v>-129.97</v>
       </c>
       <c r="K52" t="n">
-        <v>-148.48</v>
+        <v>-177.46</v>
       </c>
       <c r="L52" t="n">
-        <v>184.04</v>
+        <v>219.96</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>104.4</v>
+        <v>146.78</v>
       </c>
       <c r="K53" t="n">
-        <v>277.75</v>
+        <v>390.5</v>
       </c>
       <c r="L53" t="n">
-        <v>296.73</v>
+        <v>417.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>66.38</v>
+        <v>93.08</v>
       </c>
       <c r="K54" t="n">
-        <v>233.72</v>
+        <v>327.77</v>
       </c>
       <c r="L54" t="n">
-        <v>242.97</v>
+        <v>340.73</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>143.43</v>
+        <v>203.22</v>
       </c>
       <c r="K55" t="n">
-        <v>-13.01</v>
+        <v>-18.44</v>
       </c>
       <c r="L55" t="n">
-        <v>144.02</v>
+        <v>204.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-238.49</v>
+        <v>-312.33</v>
       </c>
       <c r="K56" t="n">
-        <v>-350.17</v>
+        <v>-458.59</v>
       </c>
       <c r="L56" t="n">
-        <v>423.67</v>
+        <v>554.85</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-63.5</v>
+        <v>-86.37</v>
       </c>
       <c r="K57" t="n">
-        <v>-364.48</v>
+        <v>-495.76</v>
       </c>
       <c r="L57" t="n">
-        <v>369.97</v>
+        <v>503.22</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>502.75</v>
+        <v>706.88</v>
       </c>
       <c r="K58" t="n">
-        <v>-93.8</v>
+        <v>-131.89</v>
       </c>
       <c r="L58" t="n">
-        <v>511.43</v>
+        <v>719.0700000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-104.63</v>
+        <v>-108.67</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.48</v>
+        <v>-37.89</v>
       </c>
       <c r="L59" t="n">
-        <v>110.81</v>
+        <v>115.09</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-36.61</v>
+        <v>-47.41</v>
       </c>
       <c r="K60" t="n">
-        <v>-41.7</v>
+        <v>-54</v>
       </c>
       <c r="L60" t="n">
-        <v>55.49</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>71.69</v>
+        <v>81.88</v>
       </c>
       <c r="K61" t="n">
-        <v>7.07</v>
+        <v>8.08</v>
       </c>
       <c r="L61" t="n">
-        <v>72.04000000000001</v>
+        <v>82.28</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="K62" t="n">
-        <v>98.75</v>
+        <v>122.65</v>
       </c>
       <c r="L62" t="n">
-        <v>98.75</v>
+        <v>122.65</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-103.59</v>
+        <v>-116.02</v>
       </c>
       <c r="K63" t="n">
-        <v>129.66</v>
+        <v>145.21</v>
       </c>
       <c r="L63" t="n">
-        <v>165.96</v>
+        <v>185.86</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-22.05</v>
+        <v>-29.71</v>
       </c>
       <c r="K64" t="n">
-        <v>-25.32</v>
+        <v>-34.11</v>
       </c>
       <c r="L64" t="n">
-        <v>33.58</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="K65" t="n">
-        <v>-149.03</v>
+        <v>-188.59</v>
       </c>
       <c r="L65" t="n">
-        <v>149.05</v>
+        <v>188.61</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-126.69</v>
+        <v>-146.53</v>
       </c>
       <c r="K66" t="n">
-        <v>-175.12</v>
+        <v>-202.54</v>
       </c>
       <c r="L66" t="n">
-        <v>216.14</v>
+        <v>249.99</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-163.05</v>
+        <v>-204.05</v>
       </c>
       <c r="K67" t="n">
-        <v>109.54</v>
+        <v>137.08</v>
       </c>
       <c r="L67" t="n">
-        <v>196.43</v>
+        <v>245.82</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-124.87</v>
+        <v>-163.26</v>
       </c>
       <c r="K68" t="n">
-        <v>346.37</v>
+        <v>452.85</v>
       </c>
       <c r="L68" t="n">
-        <v>368.19</v>
+        <v>481.38</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>-144.94</v>
+        <v>-195.03</v>
       </c>
       <c r="K69" t="n">
-        <v>225.13</v>
+        <v>302.94</v>
       </c>
       <c r="L69" t="n">
-        <v>267.75</v>
+        <v>360.29</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>153.64</v>
+        <v>205.12</v>
       </c>
       <c r="K70" t="n">
-        <v>161.17</v>
+        <v>215.18</v>
       </c>
       <c r="L70" t="n">
-        <v>222.67</v>
+        <v>297.28</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>384.98</v>
+        <v>537.33</v>
       </c>
       <c r="K71" t="n">
-        <v>-44.87</v>
+        <v>-62.63</v>
       </c>
       <c r="L71" t="n">
-        <v>387.59</v>
+        <v>540.97</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-324.89</v>
+        <v>-475.64</v>
       </c>
       <c r="K72" t="n">
-        <v>-173.01</v>
+        <v>-253.29</v>
       </c>
       <c r="L72" t="n">
-        <v>368.08</v>
+        <v>538.88</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-286.73</v>
+        <v>-402.59</v>
       </c>
       <c r="K73" t="n">
-        <v>108.64</v>
+        <v>152.54</v>
       </c>
       <c r="L73" t="n">
-        <v>306.62</v>
+        <v>430.52</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="K74" t="n">
-        <v>130.22</v>
+        <v>146.01</v>
       </c>
       <c r="L74" t="n">
-        <v>130.23</v>
+        <v>146.02</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>106.58</v>
+        <v>119.12</v>
       </c>
       <c r="K75" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="L75" t="n">
-        <v>107.44</v>
+        <v>120.09</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-77.25</v>
+        <v>-91.94</v>
       </c>
       <c r="K76" t="n">
-        <v>29.52</v>
+        <v>35.14</v>
       </c>
       <c r="L76" t="n">
-        <v>82.7</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>131.85</v>
+        <v>156.77</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.16</v>
+        <v>-21.6</v>
       </c>
       <c r="L77" t="n">
-        <v>133.09</v>
+        <v>158.25</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>59.52</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.51000000000001</v>
+        <v>-89.66</v>
       </c>
       <c r="L78" t="n">
-        <v>93.81999999999999</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-24.36</v>
+        <v>-30.73</v>
       </c>
       <c r="K79" t="n">
-        <v>-91.59999999999999</v>
+        <v>-115.55</v>
       </c>
       <c r="L79" t="n">
-        <v>94.78</v>
+        <v>119.56</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>206.32</v>
+        <v>250.8</v>
       </c>
       <c r="K80" t="n">
-        <v>21.11</v>
+        <v>25.66</v>
       </c>
       <c r="L80" t="n">
-        <v>207.4</v>
+        <v>252.11</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-37.83</v>
+        <v>-48.4</v>
       </c>
       <c r="K81" t="n">
-        <v>140.24</v>
+        <v>179.43</v>
       </c>
       <c r="L81" t="n">
-        <v>145.26</v>
+        <v>185.84</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-175.62</v>
+        <v>-194.64</v>
       </c>
       <c r="K82" t="n">
-        <v>-227.89</v>
+        <v>-252.57</v>
       </c>
       <c r="L82" t="n">
-        <v>287.71</v>
+        <v>318.87</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>52.15</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-413.6</v>
+        <v>-521.14</v>
       </c>
       <c r="L83" t="n">
-        <v>416.87</v>
+        <v>525.27</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>179.86</v>
+        <v>254.31</v>
       </c>
       <c r="K84" t="n">
-        <v>193.01</v>
+        <v>272.9</v>
       </c>
       <c r="L84" t="n">
-        <v>263.82</v>
+        <v>373.03</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-336.34</v>
+        <v>-429.06</v>
       </c>
       <c r="K85" t="n">
-        <v>-32.22</v>
+        <v>-41.1</v>
       </c>
       <c r="L85" t="n">
-        <v>337.88</v>
+        <v>431.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-374.47</v>
+        <v>-522.5599999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>-298.25</v>
+        <v>-416.2</v>
       </c>
       <c r="L86" t="n">
-        <v>478.73</v>
+        <v>668.0599999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>250.26</v>
+        <v>343.34</v>
       </c>
       <c r="K87" t="n">
-        <v>489.02</v>
+        <v>670.9</v>
       </c>
       <c r="L87" t="n">
-        <v>549.34</v>
+        <v>753.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>364.13</v>
+        <v>491.48</v>
       </c>
       <c r="K88" t="n">
-        <v>444.07</v>
+        <v>599.39</v>
       </c>
       <c r="L88" t="n">
-        <v>574.27</v>
+        <v>775.13</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-05-26.xlsx
+++ b/output/2025-05-26.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-78.38</v>
+        <v>-105.88</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.28</v>
+        <v>-15.24</v>
       </c>
       <c r="L14" t="n">
-        <v>79.19</v>
+        <v>106.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>76.91</v>
+        <v>115.68</v>
       </c>
       <c r="K15" t="n">
-        <v>60.17</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>97.65000000000001</v>
+        <v>146.88</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-67.15000000000001</v>
+        <v>-111.25</v>
       </c>
       <c r="K16" t="n">
-        <v>30.04</v>
+        <v>49.77</v>
       </c>
       <c r="L16" t="n">
-        <v>73.56</v>
+        <v>121.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-29.37</v>
+        <v>-35.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-109.12</v>
+        <v>-132.11</v>
       </c>
       <c r="L17" t="n">
-        <v>113</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>116.91</v>
+        <v>158.54</v>
       </c>
       <c r="K18" t="n">
-        <v>-53.76</v>
+        <v>-72.91</v>
       </c>
       <c r="L18" t="n">
-        <v>128.68</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>90.44</v>
+        <v>127.31</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.17</v>
+        <v>-1.65</v>
       </c>
       <c r="L19" t="n">
-        <v>90.45</v>
+        <v>127.32</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>76.40000000000001</v>
+        <v>112.53</v>
       </c>
       <c r="K29" t="n">
-        <v>-45.34</v>
+        <v>-66.78</v>
       </c>
       <c r="L29" t="n">
-        <v>88.84</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-66.44</v>
+        <v>-108.69</v>
       </c>
       <c r="K30" t="n">
-        <v>-105.21</v>
+        <v>-172.1</v>
       </c>
       <c r="L30" t="n">
-        <v>124.43</v>
+        <v>203.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.88</v>
+        <v>-31.98</v>
       </c>
       <c r="K31" t="n">
-        <v>88.83</v>
+        <v>129.83</v>
       </c>
       <c r="L31" t="n">
-        <v>91.48999999999999</v>
+        <v>133.71</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-103.58</v>
+        <v>-164.6</v>
       </c>
       <c r="K32" t="n">
-        <v>-57.44</v>
+        <v>-91.28</v>
       </c>
       <c r="L32" t="n">
-        <v>118.44</v>
+        <v>188.21</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>37.88</v>
+        <v>59.45</v>
       </c>
       <c r="K33" t="n">
-        <v>-99.93000000000001</v>
+        <v>-156.81</v>
       </c>
       <c r="L33" t="n">
-        <v>106.87</v>
+        <v>167.7</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-95.62</v>
+        <v>-150.04</v>
       </c>
       <c r="K34" t="n">
-        <v>24.56</v>
+        <v>38.53</v>
       </c>
       <c r="L34" t="n">
-        <v>98.72</v>
+        <v>154.91</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-14.01</v>
+        <v>-23.12</v>
       </c>
       <c r="K44" t="n">
-        <v>-99.66</v>
+        <v>-164.52</v>
       </c>
       <c r="L44" t="n">
-        <v>100.64</v>
+        <v>166.13</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-82.95999999999999</v>
+        <v>-138.44</v>
       </c>
       <c r="K45" t="n">
-        <v>-49.33</v>
+        <v>-82.31999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>96.52</v>
+        <v>161.07</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>-103.61</v>
+        <v>-191.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-48.97</v>
+        <v>-90.73</v>
       </c>
       <c r="L46" t="n">
-        <v>114.6</v>
+        <v>212.34</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-58.92</v>
+        <v>-92.33</v>
       </c>
       <c r="K47" t="n">
-        <v>149.85</v>
+        <v>234.81</v>
       </c>
       <c r="L47" t="n">
-        <v>161.02</v>
+        <v>252.31</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.05</v>
+        <v>-83.08</v>
       </c>
       <c r="K48" t="n">
-        <v>105.92</v>
+        <v>154.25</v>
       </c>
       <c r="L48" t="n">
-        <v>120.31</v>
+        <v>175.21</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.06</v>
+        <v>-3.27</v>
       </c>
       <c r="K49" t="n">
-        <v>-110.96</v>
+        <v>-176.34</v>
       </c>
       <c r="L49" t="n">
-        <v>110.98</v>
+        <v>176.37</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-108.67</v>
+        <v>-180.37</v>
       </c>
       <c r="K59" t="n">
-        <v>-37.89</v>
+        <v>-62.89</v>
       </c>
       <c r="L59" t="n">
-        <v>115.09</v>
+        <v>191.02</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.41</v>
+        <v>-82.56</v>
       </c>
       <c r="K60" t="n">
-        <v>-54</v>
+        <v>-94.04000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>71.84999999999999</v>
+        <v>125.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>81.88</v>
+        <v>123.87</v>
       </c>
       <c r="K61" t="n">
-        <v>8.08</v>
+        <v>12.22</v>
       </c>
       <c r="L61" t="n">
-        <v>82.28</v>
+        <v>124.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.09</v>
+        <v>-0.15</v>
       </c>
       <c r="K62" t="n">
-        <v>122.65</v>
+        <v>195.45</v>
       </c>
       <c r="L62" t="n">
-        <v>122.65</v>
+        <v>195.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-116.02</v>
+        <v>-208.74</v>
       </c>
       <c r="K63" t="n">
-        <v>145.21</v>
+        <v>261.26</v>
       </c>
       <c r="L63" t="n">
-        <v>185.86</v>
+        <v>334.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>17</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.71</v>
+        <v>-49.28</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.11</v>
+        <v>-56.57</v>
       </c>
       <c r="L64" t="n">
-        <v>45.23</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>1.57</v>
+        <v>3.02</v>
       </c>
       <c r="K74" t="n">
-        <v>146.01</v>
+        <v>280.67</v>
       </c>
       <c r="L74" t="n">
-        <v>146.02</v>
+        <v>280.68</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>119.12</v>
+        <v>211.84</v>
       </c>
       <c r="K75" t="n">
-        <v>15.2</v>
+        <v>27.03</v>
       </c>
       <c r="L75" t="n">
-        <v>120.09</v>
+        <v>213.56</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-91.94</v>
+        <v>-163.51</v>
       </c>
       <c r="K76" t="n">
-        <v>35.14</v>
+        <v>62.49</v>
       </c>
       <c r="L76" t="n">
-        <v>98.43000000000001</v>
+        <v>175.05</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>156.77</v>
+        <v>284.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-21.6</v>
+        <v>-39.16</v>
       </c>
       <c r="L77" t="n">
-        <v>158.25</v>
+        <v>286.95</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>73.59999999999999</v>
+        <v>110.98</v>
       </c>
       <c r="K78" t="n">
-        <v>-89.66</v>
+        <v>-135.2</v>
       </c>
       <c r="L78" t="n">
-        <v>116</v>
+        <v>174.92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>-30.73</v>
+        <v>-50</v>
       </c>
       <c r="K79" t="n">
-        <v>-115.55</v>
+        <v>-188.01</v>
       </c>
       <c r="L79" t="n">
-        <v>119.56</v>
+        <v>194.55</v>
       </c>
     </row>
     <row r="80">
